--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44459</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 9277-2023</t>
+          <t>A 30080-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44980</v>
+        <v>45110</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,20 +1706,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1730,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1746,35 +1746,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         <v>45772</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>46135</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30080-2023</t>
+          <t>A 23455-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45110</v>
+        <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2130,11 +2130,16 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2143,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2155,10 +2160,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2167,46 +2172,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23455-2026</t>
+          <t>A 9277-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,14 +2221,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46163</v>
+        <v>44980</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2235,13 +2240,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2277,46 +2277,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52041-2023</t>
+          <t>A 31736-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2326,14 +2326,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45223</v>
+        <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2346,16 +2346,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2382,39 +2382,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
         <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31736-2026</t>
+          <t>A 52041-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2536,14 +2536,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46227</v>
+        <v>45223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2556,17 +2556,17 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2592,39 +2592,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44536</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>44467</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44595</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44659</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>44818</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45272</v>
+        <v>45469</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45335</v>
+        <v>45420</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,8 +4167,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4211,7 +4216,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4225,10 +4230,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45398</v>
+        <v>45435</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4240,13 +4245,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44856</v>
+        <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4362,7 +4362,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44860</v>
+        <v>45180</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44895</v>
+        <v>45554</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4508,7 +4508,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45288</v>
+        <v>44908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44496</v>
+        <v>45110</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45469</v>
+        <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44895</v>
+        <v>45113</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45469</v>
+        <v>44978</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45086</v>
+        <v>44937</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44587</v>
+        <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4973,11 +4973,6 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -5024,7 +5019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5038,10 +5033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44937</v>
+        <v>45824</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5054,7 +5049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5097,7 +5092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5111,10 +5106,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44946</v>
+        <v>45800</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5127,7 +5122,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5170,7 +5165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5184,10 +5179,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45408</v>
+        <v>46008</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5201,11 +5196,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5248,7 +5243,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5262,10 +5257,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45820</v>
+        <v>45309</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5277,13 +5272,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5326,7 +5316,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5340,10 +5330,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44973</v>
+        <v>45699</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5355,8 +5345,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5399,7 +5394,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45824</v>
+        <v>45889</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5428,8 +5423,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5472,7 +5472,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45763</v>
+        <v>45889</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5501,8 +5501,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5545,7 +5550,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5559,10 +5564,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45874</v>
+        <v>45890</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5574,8 +5579,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5635,7 +5645,7 @@
         <v>45890</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5696,7 +5706,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5706,14 +5716,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45839</v>
+        <v>44946</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5726,7 +5736,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>7.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5769,7 +5779,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5783,10 +5793,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45839</v>
+        <v>45462</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5842,7 +5852,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5856,10 +5866,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45554</v>
+        <v>45398</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5871,8 +5881,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5915,7 +5930,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5929,10 +5944,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45889</v>
+        <v>45817</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5944,13 +5959,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5993,7 +6003,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6007,10 +6017,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45889</v>
+        <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6028,7 +6038,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6071,7 +6081,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6085,10 +6095,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45890</v>
+        <v>44895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6100,13 +6110,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6149,7 +6154,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6163,10 +6168,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44953</v>
+        <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6179,7 +6184,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6222,7 +6227,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6236,10 +6241,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45840</v>
+        <v>44887</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6252,7 +6257,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6295,7 +6300,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6309,10 +6314,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44615</v>
+        <v>45272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6325,7 +6330,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6368,7 +6373,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6382,10 +6387,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45776</v>
+        <v>45687</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6398,7 +6403,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6441,7 +6446,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6455,10 +6460,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44687</v>
+        <v>45111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6470,13 +6475,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6529,14 +6529,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45258</v>
+        <v>45839</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6592,7 +6592,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6606,10 +6606,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44894</v>
+        <v>45918</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6621,8 +6621,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6665,7 +6670,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 5897-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6679,10 +6684,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6695,7 +6700,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6738,7 +6743,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6752,10 +6757,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45713</v>
+        <v>45839</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6768,7 +6773,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6811,7 +6816,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6825,10 +6830,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45099</v>
+        <v>44953</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6841,7 +6846,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6884,7 +6889,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6898,10 +6903,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45918</v>
+        <v>45840</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6913,13 +6918,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6962,7 +6962,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44497</v>
+        <v>44973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7035,7 +7035,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44957</v>
+        <v>45924</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7064,8 +7064,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7108,7 +7113,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7125,7 +7130,7 @@
         <v>45924</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7143,7 +7148,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7186,7 +7191,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7203,7 +7208,7 @@
         <v>45924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7221,7 +7226,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7264,7 +7269,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7278,10 +7283,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45924</v>
+        <v>45469</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7293,13 +7298,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7342,7 +7342,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7359,7 +7359,7 @@
         <v>45924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45642</v>
+        <v>46059</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7493,7 +7493,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45929</v>
+        <v>46059</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7566,7 +7566,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44970</v>
+        <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7639,7 +7639,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45932</v>
+        <v>45929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7712,7 +7712,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45514</v>
+        <v>45258</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7785,7 +7785,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45113</v>
+        <v>45776</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7858,7 +7858,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46087</v>
+        <v>45932</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7931,7 +7931,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7945,10 +7945,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45945</v>
+        <v>44687</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7962,11 +7962,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8009,7 +8009,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46093</v>
+        <v>46072</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45699</v>
+        <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8160,7 +8160,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8170,14 +8170,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8189,13 +8189,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8238,7 +8233,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8252,10 +8247,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46101</v>
+        <v>45874</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8311,7 +8306,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8325,10 +8320,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46101</v>
+        <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8341,7 +8336,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8384,7 +8379,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46100</v>
+        <v>45492</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8413,13 +8408,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8462,7 +8452,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8476,10 +8466,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44990</v>
+        <v>45667</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8491,8 +8481,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8535,7 +8530,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8549,10 +8544,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45098</v>
+        <v>46093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8564,13 +8559,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8613,7 +8603,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8623,14 +8613,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44832</v>
+        <v>46093</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8642,8 +8632,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8686,7 +8681,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8700,10 +8695,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45091</v>
+        <v>46100</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8715,8 +8710,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8759,7 +8759,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45958</v>
+        <v>46101</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8832,7 +8832,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45667</v>
+        <v>46101</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8861,13 +8861,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8910,7 +8905,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8924,10 +8919,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45960</v>
+        <v>46106</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8941,11 +8936,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8988,7 +8983,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9005,7 +9000,7 @@
         <v>46106</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9023,7 +9018,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9066,7 +9061,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9080,10 +9075,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46106</v>
+        <v>45958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9095,13 +9090,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9144,7 +9134,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9161,7 +9151,7 @@
         <v>46106</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9179,7 +9169,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9239,7 +9229,7 @@
         <v>46108</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9312,7 +9302,7 @@
         <v>46111</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9385,7 +9375,7 @@
         <v>46111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9441,7 +9431,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9458,7 +9448,7 @@
         <v>46111</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9471,7 +9461,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9514,7 +9504,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9528,10 +9518,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45288</v>
+        <v>45960</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9543,8 +9533,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9587,7 +9582,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9604,7 +9599,7 @@
         <v>46111</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9617,7 +9612,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9677,7 +9672,7 @@
         <v>46113</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9738,7 +9733,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9752,10 +9747,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45110</v>
+        <v>45299</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9768,7 +9763,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9811,7 +9806,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9825,10 +9820,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45043</v>
+        <v>45281</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9841,7 +9836,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9884,7 +9879,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9898,10 +9893,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45974</v>
+        <v>46119</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9914,7 +9909,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9957,7 +9952,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9971,10 +9966,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46119</v>
+        <v>45539</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9986,8 +9981,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10030,7 +10030,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10044,10 +10044,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45539</v>
+        <v>46129</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45180</v>
+        <v>44615</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10181,7 +10181,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45492</v>
+        <v>45974</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10254,7 +10254,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10268,10 +10268,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46129</v>
+        <v>44970</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10283,13 +10283,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10332,7 +10327,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10346,10 +10341,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44908</v>
+        <v>44856</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10362,7 +10357,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10405,7 +10400,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10419,10 +10414,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46001</v>
+        <v>44860</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10434,13 +10429,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10483,7 +10473,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10497,10 +10487,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45110</v>
+        <v>45883</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10513,7 +10503,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10556,7 +10546,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10570,10 +10560,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45149</v>
+        <v>45763</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10586,7 +10576,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10629,7 +10619,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10639,14 +10629,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45149</v>
+        <v>45091</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10659,7 +10649,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10702,7 +10692,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10716,10 +10706,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46008</v>
+        <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10731,13 +10721,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10780,7 +10765,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10794,10 +10779,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45883</v>
+        <v>45196</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10810,7 +10795,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10853,7 +10838,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10863,14 +10848,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45109</v>
+        <v>46001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10882,8 +10867,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10926,7 +10916,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10940,10 +10930,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45110</v>
+        <v>45800</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10956,7 +10946,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10999,7 +10989,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11013,10 +11003,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45110</v>
+        <v>45713</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11029,7 +11019,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11072,7 +11062,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11086,10 +11076,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45111</v>
+        <v>44827</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11102,7 +11092,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11145,7 +11135,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11159,10 +11149,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45763</v>
+        <v>45492</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11218,7 +11208,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11232,10 +11222,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45800</v>
+        <v>45098</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11247,8 +11237,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11291,7 +11286,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11305,10 +11300,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45309</v>
+        <v>44990</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11321,7 +11316,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11364,7 +11359,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 5897-2026</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11378,10 +11373,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46052</v>
+        <v>45621</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11394,7 +11389,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11437,7 +11432,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11451,10 +11446,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45492</v>
+        <v>45628</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11467,7 +11462,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11510,7 +11505,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11524,10 +11519,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45096</v>
+        <v>45086</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11540,7 +11535,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11583,7 +11578,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11597,10 +11592,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46059</v>
+        <v>45758</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11612,8 +11607,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11656,7 +11656,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11670,10 +11670,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46059</v>
+        <v>45758</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11685,8 +11685,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11729,7 +11734,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11743,10 +11748,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45719</v>
+        <v>44937</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11759,7 +11764,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11802,7 +11807,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11816,10 +11821,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45175</v>
+        <v>45713</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11831,13 +11836,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11880,7 +11880,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11894,10 +11894,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45022</v>
+        <v>46163</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11909,8 +11909,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11953,7 +11958,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11967,10 +11972,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45462</v>
+        <v>46163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11982,8 +11987,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12026,7 +12036,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12040,10 +12050,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45469</v>
+        <v>46168</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12056,7 +12066,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12099,7 +12109,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12113,10 +12123,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45469</v>
+        <v>46168</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12129,7 +12139,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12172,7 +12182,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12186,10 +12196,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45713</v>
+        <v>46168</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12202,7 +12212,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12245,7 +12255,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12259,10 +12269,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45196</v>
+        <v>46182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12275,7 +12285,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12318,7 +12328,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12328,14 +12338,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44844</v>
+        <v>46189</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12348,7 +12358,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12391,7 +12401,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12405,10 +12415,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45091</v>
+        <v>44587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12418,6 +12428,11 @@
       <c r="G152" t="inlineStr">
         <is>
           <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -12464,7 +12479,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12478,10 +12493,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46163</v>
+        <v>46246</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12495,11 +12510,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12542,7 +12557,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12556,10 +12571,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46163</v>
+        <v>46246</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12577,7 +12592,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12620,7 +12635,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12634,10 +12649,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46168</v>
+        <v>46247</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12649,8 +12664,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12693,7 +12713,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12707,10 +12727,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46168</v>
+        <v>45299</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12723,7 +12743,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12766,7 +12786,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12780,10 +12800,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45420</v>
+        <v>45196</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12795,13 +12815,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12844,7 +12859,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12858,10 +12873,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46168</v>
+        <v>46258</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12874,7 +12889,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12917,7 +12932,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12931,10 +12946,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44701</v>
+        <v>46203</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12946,8 +12961,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12990,7 +13010,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13004,10 +13024,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44698</v>
+        <v>46168</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13020,7 +13040,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13063,7 +13083,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13077,10 +13097,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45299</v>
+        <v>44701</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13093,7 +13113,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13136,7 +13156,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13150,10 +13170,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45370</v>
+        <v>44698</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13166,7 +13186,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13209,7 +13229,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13223,10 +13243,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46182</v>
+        <v>44497</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13239,7 +13259,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13282,7 +13302,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13296,10 +13316,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45313</v>
+        <v>45224</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13312,7 +13332,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13355,7 +13375,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13365,14 +13385,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46189</v>
+        <v>45145</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13385,7 +13405,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13428,7 +13448,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13442,10 +13462,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45448</v>
+        <v>45408</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13463,7 +13483,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13506,7 +13526,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13516,14 +13536,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44687</v>
+        <v>45356</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13536,7 +13556,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13579,7 +13599,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13593,10 +13613,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45196</v>
+        <v>45149</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13609,7 +13629,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13652,7 +13672,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13662,14 +13682,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44827</v>
+        <v>45149</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13682,7 +13702,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13725,7 +13745,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13739,10 +13759,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45314</v>
+        <v>45281</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13755,7 +13775,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13798,7 +13818,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13812,10 +13832,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45687</v>
+        <v>44895</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13828,7 +13848,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13871,7 +13891,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13885,10 +13905,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44909</v>
+        <v>44844</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13901,7 +13921,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13944,7 +13964,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13954,14 +13974,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45385</v>
+        <v>44832</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13974,7 +13994,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14017,7 +14037,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14031,10 +14051,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44995</v>
+        <v>45469</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14047,7 +14067,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>13.5</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14090,7 +14110,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14104,10 +14124,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44887</v>
+        <v>45469</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14120,7 +14140,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14163,7 +14183,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14177,10 +14197,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45215</v>
+        <v>45313</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14193,7 +14213,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14236,7 +14256,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14246,14 +14266,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46246</v>
+        <v>44687</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14265,13 +14285,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14314,7 +14329,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14328,10 +14343,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46246</v>
+        <v>45043</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14343,13 +14358,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14392,7 +14402,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14406,10 +14416,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45281</v>
+        <v>45215</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14422,7 +14432,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14465,7 +14475,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14479,10 +14489,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44812</v>
+        <v>44957</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14495,7 +14505,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14538,7 +14548,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14552,10 +14562,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45140</v>
+        <v>45022</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14568,7 +14578,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14611,7 +14621,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14625,10 +14635,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46247</v>
+        <v>44496</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14640,13 +14650,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14689,7 +14694,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14703,10 +14708,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44995</v>
+        <v>45096</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14719,7 +14724,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14762,7 +14767,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14776,10 +14781,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45224</v>
+        <v>45110</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14792,7 +14797,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14835,7 +14840,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14849,10 +14854,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45281</v>
+        <v>45110</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14865,7 +14870,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14908,7 +14913,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14922,10 +14927,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44937</v>
+        <v>45140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14938,7 +14943,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14981,7 +14986,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14995,10 +15000,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45145</v>
+        <v>45314</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15011,7 +15016,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15054,7 +15059,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15068,10 +15073,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45435</v>
+        <v>44995</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15084,7 +15089,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.7</v>
+        <v>13.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15127,7 +15132,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15141,10 +15146,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46258</v>
+        <v>45370</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15157,7 +15162,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15200,7 +15205,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15214,10 +15219,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44642</v>
+        <v>44743</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15230,7 +15235,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15273,7 +15278,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15287,10 +15292,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45091</v>
+        <v>45099</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15303,7 +15308,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>21.6</v>
+        <v>3.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15346,7 +15351,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15360,10 +15365,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45224</v>
+        <v>44812</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15376,7 +15381,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15419,7 +15424,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15433,10 +15438,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45156</v>
+        <v>45621</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15449,7 +15454,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15492,7 +15497,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15506,10 +15511,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46203</v>
+        <v>45091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15521,13 +15526,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>21.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15570,7 +15570,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15584,10 +15584,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46168</v>
+        <v>44894</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15657,10 +15657,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45621</v>
+        <v>44909</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15716,7 +15716,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15730,10 +15730,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45621</v>
+        <v>45288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15803,10 +15803,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45299</v>
+        <v>45224</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15862,7 +15862,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15876,10 +15876,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45356</v>
+        <v>45448</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15891,8 +15891,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15935,7 +15940,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15949,10 +15954,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44887</v>
+        <v>45175</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15964,8 +15969,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16008,7 +16018,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16022,10 +16032,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44743</v>
+        <v>45110</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16038,7 +16048,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16081,7 +16091,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16095,10 +16105,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45628</v>
+        <v>45514</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16111,7 +16121,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16154,7 +16164,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16168,10 +16178,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44978</v>
+        <v>45156</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16184,7 +16194,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16227,7 +16237,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16241,10 +16251,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45758</v>
+        <v>44995</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16256,13 +16266,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16305,7 +16310,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16319,10 +16324,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45758</v>
+        <v>44642</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16334,13 +16339,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16383,7 +16383,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16397,10 +16397,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45313</v>
+        <v>45109</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16456,7 +16456,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16466,14 +16466,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45639</v>
+        <v>45313</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.1</v>
+        <v>11.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16529,7 +16529,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45595</v>
+        <v>45288</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16602,7 +16602,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16616,10 +16616,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>9.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16675,7 +16675,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16685,14 +16685,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45800</v>
+        <v>45635</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16748,7 +16748,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16762,10 +16762,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45817</v>
+        <v>45595</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16836,7 +16836,7 @@
         <v>44623</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45372</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE213"/>
+  <dimension ref="A1:AE214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 18736-2023</t>
+          <t>A 4312-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45043</v>
+        <v>44953</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1204,145 +1204,145 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Hartmansstarr
+Klasefibbla</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 4312-2023 artfynd.xlsx", "A 4312-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 4312-2023 karta.png", "A 4312-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 4312-2023 georefererad karta.tif", "A 4312-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 4312-2023 FSC-klagomål.docx", "A 4312-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 4312-2023 FSC-klagomål mail.docx", "A 4312-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 4312-2023 tillsynsbegäran.docx", "A 4312-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 4312-2023 tillsynsbegäran mail.docx", "A 4312-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 18736-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Slåttergubbe
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 18736-2023 artfynd.xlsx", "A 18736-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 18736-2023 karta.png", "A 18736-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 18736-2023 georefererad karta.tif", "A 18736-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 18736-2023 FSC-klagomål.docx", "A 18736-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 18736-2023 FSC-klagomål mail.docx", "A 18736-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 18736-2023 tillsynsbegäran.docx", "A 18736-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 18736-2023 tillsynsbegäran mail.docx", "A 18736-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4312-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Hartmansstarr
-Klasefibbla</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 4312-2023 artfynd.xlsx", "A 4312-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 4312-2023 karta.png", "A 4312-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 4312-2023 georefererad karta.tif", "A 4312-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 4312-2023 FSC-klagomål.docx", "A 4312-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 4312-2023 FSC-klagomål mail.docx", "A 4312-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 4312-2023 tillsynsbegäran.docx", "A 4312-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 4312-2023 tillsynsbegäran mail.docx", "A 4312-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44459</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30080-2023</t>
+          <t>A 52041-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45110</v>
+        <v>45223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1746,42 +1746,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20063-2025</t>
+          <t>A 9277-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45772</v>
+        <v>44980</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1847,46 +1847,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skinntagging</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55928-2025</t>
+          <t>A 19729-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45973</v>
+        <v>46135</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,22 +1915,17 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1945,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1954,150 +1949,155 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 19729-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 9277-2023</t>
+          <t>A 30080-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2221,14 +2221,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44980</v>
+        <v>45110</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2241,20 +2241,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2265,10 +2265,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2281,35 +2281,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52041-2023</t>
+          <t>A 20063-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2536,14 +2536,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45223</v>
+        <v>45772</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2592,39 +2592,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skinntagging</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44536</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>44467</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44595</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15415-2022</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44659</v>
+        <v>45335</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3505,13 +3505,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3554,7 +3549,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 72213-2021</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3568,10 +3563,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44544</v>
+        <v>45398</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3583,8 +3578,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24976-2022</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44728</v>
+        <v>44856</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50741-2021</t>
+          <t>A 15415-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44460</v>
+        <v>44659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3729,8 +3729,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3773,7 +3778,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4409-2022</t>
+          <t>A 72213-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3787,10 +3792,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44589</v>
+        <v>44544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3803,7 +3808,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3846,7 +3851,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38210-2022</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3860,10 +3865,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44812</v>
+        <v>44701</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3876,7 +3881,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3919,7 +3924,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3933,10 +3938,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44530</v>
+        <v>44698</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3949,7 +3954,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3992,7 +3997,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 24976-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4006,10 +4011,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44818</v>
+        <v>44728</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4022,7 +4027,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4065,7 +4070,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 50741-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4079,10 +4084,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45469</v>
+        <v>44460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4095,7 +4100,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4138,7 +4143,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 38210-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4152,10 +4157,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45420</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,13 +4172,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4216,7 +4216,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 4409-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45435</v>
+        <v>44589</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45763</v>
+        <v>44530</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4362,7 +4362,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45180</v>
+        <v>44818</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45554</v>
+        <v>44860</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4508,7 +4508,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44908</v>
+        <v>45272</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45110</v>
+        <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45642</v>
+        <v>45299</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45113</v>
+        <v>45370</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44978</v>
+        <v>45288</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44937</v>
+        <v>45313</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45091</v>
+        <v>44496</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45824</v>
+        <v>45448</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5048,8 +5048,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5092,7 +5097,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5102,14 +5107,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45800</v>
+        <v>45469</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5122,7 +5127,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5165,7 +5170,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5179,10 +5184,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46008</v>
+        <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5194,13 +5199,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45309</v>
+        <v>45824</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45699</v>
+        <v>45874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5345,13 +5345,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5394,7 +5389,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5404,14 +5399,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45889</v>
+        <v>46087</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5423,13 +5418,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5472,7 +5462,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5486,10 +5476,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5507,7 +5497,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5550,7 +5540,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5564,10 +5554,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45890</v>
+        <v>45889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5585,7 +5575,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5628,7 +5618,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5642,10 +5632,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45890</v>
+        <v>45889</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5663,7 +5653,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5706,7 +5696,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5716,14 +5706,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44946</v>
+        <v>45890</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5735,8 +5725,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5779,7 +5774,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45462</v>
+        <v>45469</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45398</v>
+        <v>46093</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5881,13 +5876,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5930,7 +5920,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5944,10 +5934,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45817</v>
+        <v>46093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5959,8 +5949,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6003,7 +5998,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6017,10 +6012,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45820</v>
+        <v>46101</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6032,13 +6027,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6081,7 +6071,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6095,10 +6085,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44895</v>
+        <v>45086</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6111,7 +6101,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6154,7 +6144,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6168,10 +6158,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44887</v>
+        <v>46101</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6184,7 +6174,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6227,7 +6217,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6241,10 +6231,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44887</v>
+        <v>46100</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6256,8 +6246,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6300,7 +6295,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6310,14 +6305,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45272</v>
+        <v>44687</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6330,7 +6325,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6373,7 +6368,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6387,10 +6382,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45687</v>
+        <v>44587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6402,8 +6397,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45111</v>
+        <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6475,8 +6475,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6519,7 +6524,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6533,10 +6538,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45839</v>
+        <v>46106</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6548,8 +6553,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6592,7 +6602,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6606,10 +6616,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45918</v>
+        <v>46106</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6627,7 +6637,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6670,7 +6680,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5897-2026</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6684,10 +6694,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46052</v>
+        <v>46108</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6700,7 +6710,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6743,7 +6753,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6757,10 +6767,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45839</v>
+        <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6772,8 +6782,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6816,7 +6831,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6830,10 +6845,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44953</v>
+        <v>45196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6846,7 +6861,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6889,7 +6904,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6903,10 +6918,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45840</v>
+        <v>46111</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6919,7 +6934,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6962,7 +6977,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6976,10 +6991,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44973</v>
+        <v>46111</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6992,7 +7007,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7035,7 +7050,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7049,10 +7064,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45924</v>
+        <v>46111</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7064,13 +7079,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7113,7 +7123,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7127,10 +7137,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45924</v>
+        <v>46111</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7142,13 +7152,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7191,7 +7196,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7205,10 +7210,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45924</v>
+        <v>44827</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7220,13 +7225,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7269,7 +7269,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7283,10 +7283,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45469</v>
+        <v>44937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7342,7 +7342,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45924</v>
+        <v>46113</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7373,11 +7373,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46059</v>
+        <v>45314</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7493,7 +7493,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46059</v>
+        <v>46119</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7566,7 +7566,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45719</v>
+        <v>45408</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7595,8 +7595,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7639,7 +7644,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7653,10 +7658,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45929</v>
+        <v>45924</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7668,8 +7673,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7712,7 +7722,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7722,14 +7732,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45258</v>
+        <v>45924</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7741,8 +7751,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7785,7 +7800,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7799,10 +7814,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45776</v>
+        <v>45924</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7814,8 +7829,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7858,7 +7878,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7872,10 +7892,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45932</v>
+        <v>45924</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7887,8 +7907,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7931,7 +7956,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7945,10 +7970,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44687</v>
+        <v>45539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7962,11 +7987,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8009,7 +8034,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8023,10 +8048,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46072</v>
+        <v>45929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8039,7 +8064,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8082,7 +8107,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8096,10 +8121,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45945</v>
+        <v>45687</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8111,13 +8136,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8160,7 +8180,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8170,14 +8190,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46087</v>
+        <v>46129</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8189,8 +8209,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8233,7 +8258,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8247,10 +8272,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45874</v>
+        <v>45932</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8263,7 +8288,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8306,7 +8331,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8320,10 +8345,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45385</v>
+        <v>44973</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8336,7 +8361,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8379,7 +8404,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8393,10 +8418,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45492</v>
+        <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8409,7 +8434,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8452,7 +8477,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8466,10 +8491,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45667</v>
+        <v>44909</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8481,13 +8506,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8530,7 +8550,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8544,10 +8564,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46093</v>
+        <v>45554</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8560,7 +8580,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8603,7 +8623,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8617,10 +8637,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46093</v>
+        <v>45945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8638,7 +8658,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8681,7 +8701,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8695,10 +8715,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46100</v>
+        <v>45883</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8710,13 +8730,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8759,7 +8774,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8773,10 +8788,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46101</v>
+        <v>45385</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8789,7 +8804,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8832,7 +8847,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8846,10 +8861,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46101</v>
+        <v>44995</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8862,7 +8877,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8905,7 +8920,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8919,10 +8934,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46106</v>
+        <v>44887</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8932,11 +8947,6 @@
       <c r="G105" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -8983,7 +8993,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8997,10 +9007,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46106</v>
+        <v>44615</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9012,13 +9022,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9061,7 +9066,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9075,10 +9080,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45958</v>
+        <v>45763</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9091,7 +9096,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9134,7 +9139,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9148,10 +9153,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46106</v>
+        <v>44894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9163,13 +9168,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9212,7 +9212,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46108</v>
+        <v>45958</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9285,7 +9285,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9299,10 +9299,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46111</v>
+        <v>45960</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9314,8 +9314,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9358,7 +9363,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9372,10 +9377,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46111</v>
+        <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9388,7 +9393,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9431,7 +9436,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9445,10 +9450,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46111</v>
+        <v>45800</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9461,7 +9466,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9504,7 +9509,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9518,10 +9523,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45960</v>
+        <v>45099</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9533,13 +9538,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9582,7 +9582,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46111</v>
+        <v>44497</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9655,7 +9655,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46113</v>
+        <v>44957</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9684,13 +9684,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9733,7 +9728,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9747,10 +9742,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45299</v>
+        <v>45974</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9763,7 +9758,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9806,7 +9801,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9820,10 +9815,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45281</v>
+        <v>45642</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9836,7 +9831,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9879,7 +9874,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9893,10 +9888,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46119</v>
+        <v>44970</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9909,7 +9904,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9952,7 +9947,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9966,10 +9961,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45539</v>
+        <v>45215</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9981,13 +9976,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10030,7 +10020,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10044,10 +10034,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46129</v>
+        <v>45281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10059,13 +10049,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10108,7 +10093,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10122,10 +10107,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44615</v>
+        <v>45514</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10138,7 +10123,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10181,7 +10166,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10195,10 +10180,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45974</v>
+        <v>44812</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10211,7 +10196,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10254,7 +10239,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10268,10 +10253,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44970</v>
+        <v>45140</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10284,7 +10269,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10327,7 +10312,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10341,10 +10326,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44856</v>
+        <v>45113</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10357,7 +10342,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10400,7 +10385,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10414,10 +10399,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44860</v>
+        <v>45699</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10429,8 +10414,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10473,7 +10463,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10487,10 +10477,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45883</v>
+        <v>44990</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10503,7 +10493,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.9</v>
+        <v>0.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10546,7 +10536,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10560,10 +10550,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45763</v>
+        <v>45098</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10575,8 +10565,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10619,7 +10614,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10629,14 +10624,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45091</v>
+        <v>44832</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10649,7 +10644,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10692,7 +10687,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10706,10 +10701,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45335</v>
+        <v>46001</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10721,8 +10716,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10765,7 +10765,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45196</v>
+        <v>45091</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46001</v>
+        <v>45667</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45800</v>
+        <v>44995</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10989,7 +10989,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45713</v>
+        <v>46008</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11018,8 +11018,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11062,7 +11067,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11076,10 +11081,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44827</v>
+        <v>45288</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11092,7 +11097,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11135,7 +11140,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11149,10 +11154,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45492</v>
+        <v>45224</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11165,7 +11170,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11208,7 +11213,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11222,10 +11227,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45098</v>
+        <v>45110</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11237,13 +11242,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11286,7 +11286,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44990</v>
+        <v>45043</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11359,7 +11359,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11373,10 +11373,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45621</v>
+        <v>45281</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11446,10 +11446,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45628</v>
+        <v>46163</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11461,8 +11461,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11505,7 +11510,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11519,10 +11524,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45086</v>
+        <v>46163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11534,8 +11539,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11578,7 +11588,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11592,10 +11602,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45758</v>
+        <v>45180</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11607,13 +11617,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11656,7 +11661,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11670,10 +11675,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45758</v>
+        <v>46168</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11685,13 +11690,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11734,7 +11734,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11748,10 +11748,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44937</v>
+        <v>46168</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11807,7 +11807,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11821,10 +11821,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45713</v>
+        <v>45492</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11880,7 +11880,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11894,10 +11894,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11909,13 +11909,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11958,7 +11953,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11972,10 +11967,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46163</v>
+        <v>44937</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11987,13 +11982,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12036,7 +12026,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12050,10 +12040,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46168</v>
+        <v>44908</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12066,7 +12056,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12109,7 +12099,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12123,10 +12113,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46168</v>
+        <v>45110</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12139,7 +12129,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12182,7 +12172,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12196,10 +12186,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46168</v>
+        <v>45149</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12212,7 +12202,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12255,7 +12245,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12265,14 +12255,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46182</v>
+        <v>45149</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12285,7 +12275,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12328,7 +12318,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 5897-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12338,14 +12328,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46189</v>
+        <v>46052</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12358,7 +12348,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12401,7 +12391,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12411,14 +12401,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44587</v>
+        <v>45109</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12430,13 +12420,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12479,7 +12464,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12493,10 +12478,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46246</v>
+        <v>45110</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12508,13 +12493,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12557,7 +12537,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12571,10 +12551,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46246</v>
+        <v>45110</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12586,13 +12566,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12635,7 +12610,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12649,10 +12624,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46247</v>
+        <v>46059</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12664,13 +12639,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12713,7 +12683,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12727,10 +12697,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45299</v>
+        <v>46059</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12743,7 +12713,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12786,7 +12756,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12800,10 +12770,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45196</v>
+        <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12816,7 +12786,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12859,7 +12829,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12873,10 +12843,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46258</v>
+        <v>45719</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12889,7 +12859,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12932,7 +12902,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12946,10 +12916,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46203</v>
+        <v>45111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12961,13 +12931,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13010,7 +12975,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13024,10 +12989,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46168</v>
+        <v>45435</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13040,7 +13005,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13083,7 +13048,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13097,10 +13062,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44701</v>
+        <v>46182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13113,7 +13078,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13156,7 +13121,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13170,10 +13135,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44698</v>
+        <v>46072</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13186,7 +13151,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13229,7 +13194,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13239,14 +13204,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44497</v>
+        <v>46189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13259,7 +13224,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13302,7 +13267,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13316,10 +13281,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45224</v>
+        <v>45309</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13332,7 +13297,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13375,7 +13340,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13389,10 +13354,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45145</v>
+        <v>45492</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13405,7 +13370,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13448,7 +13413,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13462,10 +13427,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45408</v>
+        <v>44642</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13477,13 +13442,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13526,7 +13486,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13540,10 +13500,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45356</v>
+        <v>45091</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13556,7 +13516,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>21.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13599,7 +13559,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13613,10 +13573,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45149</v>
+        <v>45224</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13629,7 +13589,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13672,7 +13632,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13682,14 +13642,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45149</v>
+        <v>45096</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13702,7 +13662,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13745,7 +13705,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13759,10 +13719,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45281</v>
+        <v>45156</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13775,7 +13735,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13818,7 +13778,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13832,10 +13792,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44895</v>
+        <v>45175</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13847,8 +13807,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13891,7 +13856,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13905,10 +13870,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44844</v>
+        <v>46246</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13920,8 +13885,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13964,7 +13934,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13974,14 +13944,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44832</v>
+        <v>46246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13993,8 +13963,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14037,7 +14012,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14051,10 +14026,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45469</v>
+        <v>45022</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14067,7 +14042,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14110,7 +14085,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14124,10 +14099,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45469</v>
+        <v>45462</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14140,7 +14115,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14183,7 +14158,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14197,10 +14172,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45313</v>
+        <v>45469</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14213,7 +14188,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14256,7 +14231,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14266,14 +14241,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44687</v>
+        <v>45469</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14286,7 +14261,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14329,7 +14304,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14343,10 +14318,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45043</v>
+        <v>46247</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14358,8 +14333,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14402,7 +14382,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14416,10 +14396,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45215</v>
+        <v>45621</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14432,7 +14412,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14475,7 +14455,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14489,10 +14469,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44957</v>
+        <v>45621</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14505,7 +14485,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14548,7 +14528,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14562,10 +14542,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45022</v>
+        <v>45713</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14578,7 +14558,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14621,7 +14601,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14635,10 +14615,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44496</v>
+        <v>45196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14651,7 +14631,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14694,7 +14674,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14708,10 +14688,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45096</v>
+        <v>44844</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14724,7 +14704,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14767,7 +14747,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14781,10 +14761,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45110</v>
+        <v>45091</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14797,7 +14777,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14840,7 +14820,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14854,10 +14834,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45110</v>
+        <v>46258</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14870,7 +14850,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14913,7 +14893,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14927,10 +14907,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45140</v>
+        <v>46203</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14942,8 +14922,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14986,7 +14971,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15000,10 +14985,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45314</v>
+        <v>46168</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15016,7 +15001,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15059,7 +15044,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15073,10 +15058,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44995</v>
+        <v>45299</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15089,7 +15074,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>13.5</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15132,7 +15117,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15146,10 +15131,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45370</v>
+        <v>45420</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15161,8 +15146,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15205,7 +15195,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15219,10 +15209,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44743</v>
+        <v>45356</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15235,7 +15225,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15278,7 +15268,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15292,10 +15282,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45099</v>
+        <v>44887</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15308,7 +15298,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15351,7 +15341,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15365,10 +15355,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44812</v>
+        <v>44743</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15381,7 +15371,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15424,7 +15414,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15438,10 +15428,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45621</v>
+        <v>45628</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15454,7 +15444,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15497,7 +15487,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15511,10 +15501,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45091</v>
+        <v>44978</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15527,7 +15517,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>21.6</v>
+        <v>1.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15570,7 +15560,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15584,10 +15574,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44894</v>
+        <v>45758</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15597,6 +15587,11 @@
       <c r="G195" t="inlineStr">
         <is>
           <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -15643,7 +15638,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15657,10 +15652,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44909</v>
+        <v>45758</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15672,8 +15667,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15716,7 +15716,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15726,14 +15726,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45288</v>
+        <v>45313</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.2</v>
+        <v>11.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15803,10 +15803,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45224</v>
+        <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15862,7 +15862,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15876,10 +15876,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45448</v>
+        <v>46280</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15891,13 +15891,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15940,7 +15935,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15954,10 +15949,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45175</v>
+        <v>45595</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15969,13 +15964,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16018,7 +16008,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16032,10 +16022,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45110</v>
+        <v>45635</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16048,7 +16038,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16091,7 +16081,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16101,14 +16091,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45514</v>
+        <v>45800</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16121,7 +16111,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16164,7 +16154,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16178,10 +16168,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45156</v>
+        <v>45817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16194,7 +16184,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16237,7 +16227,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16247,14 +16237,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44995</v>
+        <v>44946</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16267,7 +16257,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16310,7 +16300,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16324,10 +16314,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44642</v>
+        <v>45820</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16339,8 +16329,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16383,7 +16378,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16393,14 +16388,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45109</v>
+        <v>45839</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16413,7 +16408,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16456,7 +16451,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16466,14 +16461,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45313</v>
+        <v>45839</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16486,7 +16481,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16529,7 +16524,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16543,10 +16538,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45288</v>
+        <v>44953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16559,7 +16554,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16602,7 +16597,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16616,10 +16611,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45639</v>
+        <v>45840</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16632,7 +16627,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16675,7 +16670,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16689,10 +16684,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45635</v>
+        <v>45776</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16705,7 +16700,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>9.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16748,7 +16743,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16762,10 +16757,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45595</v>
+        <v>44687</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16777,8 +16772,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16821,146 +16821,219 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
+          <t>A 60233-2023</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="E212" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213" ht="15" customHeight="1">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>S 1236-2022</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C212" t="n">
+      <c r="C213" t="n">
         <v/>
       </c>
-      <c r="D212" s="1" t="n">
+      <c r="D213" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="E212" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I212" t="n">
+      <c r="E213" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
         <v>0.1</v>
       </c>
-      <c r="J212" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>0</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="n">
-        <v>0</v>
-      </c>
-      <c r="T212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="n">
-        <v>0</v>
-      </c>
-      <c r="V212" s="2" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>S 839-2024</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D213" s="1" t="n">
+      <c r="D214" s="1" t="n">
         <v>45372</v>
       </c>
-      <c r="E213" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I213" t="n">
+      <c r="E214" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
         <v>19.6</v>
       </c>
-      <c r="J213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" t="n">
-        <v>0</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="n">
-        <v>0</v>
-      </c>
-      <c r="T213" t="n">
-        <v>0</v>
-      </c>
-      <c r="U213" t="n">
-        <v>0</v>
-      </c>
-      <c r="V213" s="2" t="inlineStr"/>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE214"/>
+  <dimension ref="A1:AE216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4312-2023</t>
+          <t>A 18736-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44953</v>
+        <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1204,145 +1204,145 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Slåttergubbe
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 18736-2023 artfynd.xlsx", "A 18736-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 18736-2023 karta.png", "A 18736-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 18736-2023 georefererad karta.tif", "A 18736-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 18736-2023 FSC-klagomål.docx", "A 18736-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 18736-2023 FSC-klagomål mail.docx", "A 18736-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 18736-2023 tillsynsbegäran.docx", "A 18736-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 18736-2023 tillsynsbegäran mail.docx", "A 18736-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4312-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44953</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Hartmansstarr
 Klasefibbla</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 4312-2023 artfynd.xlsx", "A 4312-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 4312-2023 karta.png", "A 4312-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 4312-2023 georefererad karta.tif", "A 4312-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 4312-2023 FSC-klagomål.docx", "A 4312-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 4312-2023 FSC-klagomål mail.docx", "A 4312-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 4312-2023 tillsynsbegäran.docx", "A 4312-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 4312-2023 tillsynsbegäran mail.docx", "A 4312-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 18736-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45043</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 18736-2023 artfynd.xlsx", "A 18736-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 18736-2023 karta.png", "A 18736-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 18736-2023 georefererad karta.tif", "A 18736-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 18736-2023 FSC-klagomål.docx", "A 18736-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 18736-2023 FSC-klagomål mail.docx", "A 18736-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 18736-2023 tillsynsbegäran.docx", "A 18736-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 18736-2023 tillsynsbegäran mail.docx", "A 18736-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44459</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52041-2023</t>
+          <t>A 30080-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45223</v>
+        <v>45110</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1746,888 +1746,888 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 20063-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45772</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Skinntagging</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 19729-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9277-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44980</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 23455-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 52041-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45223</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 9277-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44980</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J13" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 31736-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 19729-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 55928-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 23455-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30080-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45110</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 31736-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Dvärghäxört</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 36670-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>2.3</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Almrostöra</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 20063-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45772</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skinntagging</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44536</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>44467</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44595</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 15415-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45335</v>
+        <v>44659</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3505,8 +3505,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3549,7 +3554,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 72213-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3563,10 +3568,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45398</v>
+        <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3578,13 +3583,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 24976-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44856</v>
+        <v>44728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15415-2022</t>
+          <t>A 50741-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44659</v>
+        <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3729,13 +3729,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3778,7 +3773,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 72213-2021</t>
+          <t>A 4409-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3792,10 +3787,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44544</v>
+        <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3808,7 +3803,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3851,7 +3846,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 38210-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3865,10 +3860,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44701</v>
+        <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3881,7 +3876,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3924,7 +3919,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3938,10 +3933,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44698</v>
+        <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3954,7 +3949,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3997,7 +3992,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24976-2022</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4011,10 +4006,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44728</v>
+        <v>44818</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4027,7 +4022,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4070,7 +4065,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50741-2021</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4084,10 +4079,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44460</v>
+        <v>45469</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4100,7 +4095,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4143,7 +4138,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38210-2022</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4157,10 +4152,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45420</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4172,8 +4167,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4216,7 +4216,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4409-2022</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44589</v>
+        <v>45435</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44530</v>
+        <v>45554</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4362,7 +4362,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44818</v>
+        <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44860</v>
+        <v>44908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4508,7 +4508,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45272</v>
+        <v>45113</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44895</v>
+        <v>45642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45299</v>
+        <v>44978</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45370</v>
+        <v>44937</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45288</v>
+        <v>45091</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45313</v>
+        <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44496</v>
+        <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45448</v>
+        <v>45309</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5048,13 +5048,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5097,7 +5092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5111,10 +5106,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45469</v>
+        <v>45699</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5126,8 +5121,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5170,7 +5170,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44895</v>
+        <v>45462</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45824</v>
+        <v>45398</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5272,8 +5272,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5316,7 +5321,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5330,10 +5335,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45874</v>
+        <v>45824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5346,7 +5351,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5389,7 +5394,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5403,10 +5408,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46087</v>
+        <v>45800</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5419,7 +5424,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5462,7 +5467,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5476,10 +5481,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45890</v>
+        <v>44895</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5491,13 +5496,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45889</v>
+        <v>44887</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5569,13 +5569,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5618,7 +5613,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5632,10 +5627,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45889</v>
+        <v>44887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5647,13 +5642,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5696,7 +5686,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5710,10 +5700,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45890</v>
+        <v>45272</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5725,13 +5715,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5774,7 +5759,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5788,10 +5773,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45469</v>
+        <v>45687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5804,7 +5789,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5847,7 +5832,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5861,10 +5846,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46093</v>
+        <v>45889</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5876,8 +5861,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5920,7 +5910,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5934,10 +5924,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46093</v>
+        <v>45889</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5955,7 +5945,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5998,7 +5988,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6008,14 +5998,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46101</v>
+        <v>44946</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6028,7 +6018,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6071,7 +6061,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6085,10 +6075,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45086</v>
+        <v>45890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6100,8 +6090,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6158,10 +6153,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46101</v>
+        <v>45111</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6174,7 +6169,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6217,7 +6212,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46100</v>
+        <v>45890</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6252,7 +6247,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6295,7 +6290,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6305,14 +6300,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44687</v>
+        <v>45817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6325,7 +6320,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6368,7 +6363,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6382,10 +6377,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44587</v>
+        <v>45820</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6403,7 +6398,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6446,7 +6441,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6460,10 +6455,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46106</v>
+        <v>44973</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6475,13 +6470,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6524,7 +6514,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6538,10 +6528,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46106</v>
+        <v>45469</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6553,13 +6543,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6602,7 +6587,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6616,10 +6601,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46106</v>
+        <v>45839</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6631,13 +6616,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6680,7 +6660,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6694,10 +6674,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46108</v>
+        <v>45839</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6710,7 +6690,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6753,7 +6733,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6767,10 +6747,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45918</v>
+        <v>44953</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6782,13 +6762,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6831,7 +6806,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6845,10 +6820,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45196</v>
+        <v>45840</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6861,7 +6836,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6904,7 +6879,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6918,10 +6893,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46111</v>
+        <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6933,8 +6908,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6977,7 +6957,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6991,10 +6971,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46111</v>
+        <v>45924</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7006,8 +6986,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7050,7 +7035,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7064,10 +7049,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46111</v>
+        <v>45924</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7079,8 +7064,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7123,7 +7113,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7137,10 +7127,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46111</v>
+        <v>45924</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7152,8 +7142,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7196,7 +7191,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7210,10 +7205,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44827</v>
+        <v>45924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7225,8 +7220,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7269,7 +7269,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44937</v>
+        <v>45258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7342,7 +7342,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46113</v>
+        <v>45776</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7371,13 +7371,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7420,7 +7415,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7434,10 +7429,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45314</v>
+        <v>45929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7450,7 +7445,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7493,7 +7488,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7507,10 +7502,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46119</v>
+        <v>44687</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7522,8 +7517,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7566,7 +7566,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45408</v>
+        <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7595,13 +7595,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7644,7 +7639,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7658,10 +7653,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45924</v>
+        <v>45385</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7673,13 +7668,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7722,7 +7712,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7736,10 +7726,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45924</v>
+        <v>45945</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7753,11 +7743,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7800,7 +7790,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7814,10 +7804,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45924</v>
+        <v>45492</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7829,13 +7819,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7878,7 +7863,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7892,10 +7877,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45924</v>
+        <v>45667</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7909,11 +7894,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7956,7 +7941,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 5897-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7970,10 +7955,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45539</v>
+        <v>46052</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7985,13 +7970,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8034,7 +8014,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8048,10 +8028,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45929</v>
+        <v>45299</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8064,7 +8044,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8107,7 +8087,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8121,10 +8101,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45687</v>
+        <v>45958</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8137,7 +8117,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8180,7 +8160,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8194,10 +8174,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46129</v>
+        <v>45874</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8209,13 +8189,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8258,7 +8233,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8272,10 +8247,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45932</v>
+        <v>45281</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8288,7 +8263,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8331,7 +8306,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8345,10 +8320,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44973</v>
+        <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8361,7 +8336,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8404,7 +8379,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8418,10 +8393,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45763</v>
+        <v>45960</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8433,8 +8408,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8477,7 +8457,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8491,10 +8471,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44909</v>
+        <v>46059</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8507,7 +8487,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8550,7 +8530,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8564,10 +8544,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45554</v>
+        <v>45719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8580,7 +8560,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8623,7 +8603,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8637,10 +8617,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45945</v>
+        <v>44615</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8652,13 +8632,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8701,7 +8676,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8715,10 +8690,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45883</v>
+        <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8731,7 +8706,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8774,7 +8749,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8788,10 +8763,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45385</v>
+        <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8804,7 +8779,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8847,7 +8822,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8861,10 +8836,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44995</v>
+        <v>44856</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8877,7 +8852,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>13.5</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8920,7 +8895,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8934,10 +8909,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44887</v>
+        <v>44860</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8950,7 +8925,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8993,7 +8968,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9007,10 +8982,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44615</v>
+        <v>46072</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9023,7 +8998,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9066,7 +9041,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9080,10 +9055,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45763</v>
+        <v>45091</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9096,7 +9071,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9139,7 +9114,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9153,10 +9128,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44894</v>
+        <v>45335</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9169,7 +9144,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9212,7 +9187,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9226,10 +9201,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45958</v>
+        <v>45196</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9242,7 +9217,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9285,7 +9260,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9299,10 +9274,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45960</v>
+        <v>46001</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9316,11 +9291,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9363,7 +9338,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9373,14 +9348,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45713</v>
+        <v>46087</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9393,7 +9368,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9436,7 +9411,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9450,10 +9425,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45800</v>
+        <v>45713</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9466,7 +9441,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9509,7 +9484,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9523,10 +9498,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45099</v>
+        <v>44827</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9539,7 +9514,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9582,7 +9557,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9596,10 +9571,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44497</v>
+        <v>46008</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9611,8 +9586,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9655,7 +9635,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9669,10 +9649,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44957</v>
+        <v>45492</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9685,7 +9665,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9728,7 +9708,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9742,10 +9722,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45974</v>
+        <v>46093</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9758,7 +9738,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9801,7 +9781,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9815,10 +9795,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45642</v>
+        <v>46093</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9830,8 +9810,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9874,7 +9859,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9888,10 +9873,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44970</v>
+        <v>45098</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9903,8 +9888,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9947,7 +9937,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9961,10 +9951,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45215</v>
+        <v>44990</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9977,7 +9967,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10020,7 +10010,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10034,10 +10024,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45281</v>
+        <v>45621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10050,7 +10040,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10093,7 +10083,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10107,10 +10097,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45514</v>
+        <v>46100</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10122,8 +10112,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10166,7 +10161,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10180,10 +10175,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44812</v>
+        <v>45628</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10196,7 +10191,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10239,7 +10234,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10253,10 +10248,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45140</v>
+        <v>46101</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10269,7 +10264,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10312,7 +10307,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10326,10 +10321,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45113</v>
+        <v>46101</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10342,7 +10337,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10385,7 +10380,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10399,10 +10394,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45699</v>
+        <v>46106</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10420,7 +10415,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10463,7 +10458,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10477,10 +10472,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44990</v>
+        <v>46106</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10492,8 +10487,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45098</v>
+        <v>45086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10565,13 +10565,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10614,7 +10609,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10624,14 +10619,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44832</v>
+        <v>46106</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10643,8 +10638,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10687,7 +10687,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10701,10 +10701,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46001</v>
+        <v>46108</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10716,13 +10716,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10765,7 +10760,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10779,10 +10774,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45091</v>
+        <v>45758</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10794,8 +10789,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45667</v>
+        <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44995</v>
+        <v>44937</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10989,7 +10989,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46008</v>
+        <v>46111</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11018,13 +11018,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11067,7 +11062,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11081,10 +11076,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45288</v>
+        <v>46111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11097,7 +11092,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11140,7 +11135,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11154,10 +11149,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45224</v>
+        <v>46111</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11170,7 +11165,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11213,7 +11208,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11227,10 +11222,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45110</v>
+        <v>45713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11243,7 +11238,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11286,7 +11281,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11300,10 +11295,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45043</v>
+        <v>46111</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11316,7 +11311,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11359,7 +11354,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11373,10 +11368,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45281</v>
+        <v>46113</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11388,8 +11383,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11446,10 +11446,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46163</v>
+        <v>46119</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11461,13 +11461,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11510,7 +11505,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11524,10 +11519,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46163</v>
+        <v>45539</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11545,7 +11540,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11588,7 +11583,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11602,10 +11597,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45180</v>
+        <v>46129</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11617,8 +11612,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11661,7 +11661,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46168</v>
+        <v>44587</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11690,8 +11690,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11734,7 +11739,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11748,10 +11753,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46168</v>
+        <v>45299</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11764,7 +11769,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11807,7 +11812,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11821,10 +11826,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45492</v>
+        <v>45196</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11837,7 +11842,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11880,7 +11885,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11894,10 +11899,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46168</v>
+        <v>45883</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11910,7 +11915,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11953,7 +11958,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11967,10 +11972,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44937</v>
+        <v>45763</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11983,7 +11988,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12026,7 +12031,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12040,10 +12045,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44908</v>
+        <v>44701</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12056,7 +12061,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12099,7 +12104,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12113,10 +12118,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45110</v>
+        <v>44698</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12129,7 +12134,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12172,7 +12177,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12186,10 +12191,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45149</v>
+        <v>45800</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12202,7 +12207,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12245,7 +12250,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12255,14 +12260,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45149</v>
+        <v>44497</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12275,7 +12280,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12318,7 +12323,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 5897-2026</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12332,10 +12337,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46052</v>
+        <v>45224</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12348,7 +12353,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12391,7 +12396,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12401,14 +12406,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45109</v>
+        <v>45145</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12421,7 +12426,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12464,7 +12469,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12478,10 +12483,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45110</v>
+        <v>45408</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12493,8 +12498,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12537,7 +12547,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12551,10 +12561,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45110</v>
+        <v>45356</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12567,7 +12577,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12610,7 +12620,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12624,10 +12634,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46059</v>
+        <v>45149</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12640,7 +12650,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12683,7 +12693,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12693,14 +12703,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46059</v>
+        <v>45149</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12713,7 +12723,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12756,7 +12766,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12770,10 +12780,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45145</v>
+        <v>45281</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12786,7 +12796,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12829,7 +12839,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12843,10 +12853,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45719</v>
+        <v>44895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12859,7 +12869,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12902,7 +12912,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12916,10 +12926,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45111</v>
+        <v>44844</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12932,7 +12942,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12975,7 +12985,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12985,14 +12995,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45435</v>
+        <v>44832</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13005,7 +13015,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13048,7 +13058,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13062,10 +13072,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46182</v>
+        <v>45469</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13078,7 +13088,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13121,7 +13131,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13135,10 +13145,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46072</v>
+        <v>45469</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13151,7 +13161,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13194,7 +13204,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13204,14 +13214,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46189</v>
+        <v>45313</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13224,7 +13234,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13267,7 +13277,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13281,10 +13291,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45309</v>
+        <v>46163</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13296,8 +13306,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13340,7 +13355,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13354,10 +13369,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45492</v>
+        <v>46163</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13369,8 +13384,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13413,7 +13433,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13427,10 +13447,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44642</v>
+        <v>46168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13443,7 +13463,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13486,7 +13506,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13496,14 +13516,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45091</v>
+        <v>44687</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13516,7 +13536,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>21.6</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13559,7 +13579,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13573,10 +13593,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45224</v>
+        <v>45043</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13589,7 +13609,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13632,7 +13652,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13646,10 +13666,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45096</v>
+        <v>46168</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13662,7 +13682,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13705,7 +13725,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13719,10 +13739,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45156</v>
+        <v>46168</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13735,7 +13755,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13778,7 +13798,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13792,10 +13812,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45175</v>
+        <v>45215</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13807,13 +13827,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13856,7 +13871,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13870,10 +13885,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46246</v>
+        <v>44957</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13885,13 +13900,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13934,7 +13944,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13948,10 +13958,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46246</v>
+        <v>45022</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13963,13 +13973,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14012,7 +14017,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14026,10 +14031,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45022</v>
+        <v>44496</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14042,7 +14047,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14085,7 +14090,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14099,10 +14104,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45462</v>
+        <v>45096</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14115,7 +14120,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14158,7 +14163,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14172,10 +14177,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45469</v>
+        <v>45110</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14188,7 +14193,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14231,7 +14236,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14245,10 +14250,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45469</v>
+        <v>45110</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14261,7 +14266,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14304,7 +14309,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14318,10 +14323,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46247</v>
+        <v>46182</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14333,13 +14338,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14382,7 +14382,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14392,14 +14392,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45621</v>
+        <v>46189</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14455,7 +14455,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14469,10 +14469,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45621</v>
+        <v>45140</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14528,7 +14528,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45713</v>
+        <v>45314</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14601,7 +14601,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14615,10 +14615,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45196</v>
+        <v>44995</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>13.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14674,7 +14674,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14688,10 +14688,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44844</v>
+        <v>46246</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14703,8 +14703,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14747,7 +14752,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14761,10 +14766,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45091</v>
+        <v>45370</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14777,7 +14782,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14820,7 +14825,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14834,10 +14839,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14849,8 +14854,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14893,7 +14903,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14907,10 +14917,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46203</v>
+        <v>46247</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14924,11 +14934,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14971,7 +14981,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14985,10 +14995,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46168</v>
+        <v>44743</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15001,7 +15011,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15044,7 +15054,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15058,10 +15068,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45299</v>
+        <v>45099</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15074,7 +15084,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15117,7 +15127,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15131,10 +15141,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45420</v>
+        <v>44812</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15146,13 +15156,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15195,7 +15200,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15209,10 +15214,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45356</v>
+        <v>45621</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15225,7 +15230,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15268,7 +15273,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15282,10 +15287,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44887</v>
+        <v>45091</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15298,7 +15303,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>21.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15341,7 +15346,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15355,10 +15360,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44743</v>
+        <v>44894</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15371,7 +15376,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15414,7 +15419,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15428,10 +15433,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45628</v>
+        <v>46258</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15444,7 +15449,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15487,7 +15492,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15501,10 +15506,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44978</v>
+        <v>44909</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15517,7 +15522,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15560,7 +15565,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15574,10 +15579,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45758</v>
+        <v>46203</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15591,11 +15596,11 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15638,7 +15643,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15652,10 +15657,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45758</v>
+        <v>45288</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15667,13 +15672,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15716,7 +15716,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15726,14 +15726,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45313</v>
+        <v>45224</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>11.7</v>
+        <v>0.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15803,10 +15803,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45639</v>
+        <v>46168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15862,7 +15862,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15876,10 +15876,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46280</v>
+        <v>45448</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15891,8 +15891,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15935,7 +15940,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15949,10 +15954,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45595</v>
+        <v>45175</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15964,8 +15969,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16008,7 +16018,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16022,10 +16032,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45635</v>
+        <v>45110</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16038,7 +16048,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>9.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16081,7 +16091,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16091,14 +16101,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45800</v>
+        <v>45514</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16111,7 +16121,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16154,7 +16164,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16168,10 +16178,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45817</v>
+        <v>45156</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16184,7 +16194,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16227,7 +16237,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16237,14 +16247,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44946</v>
+        <v>44995</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16257,7 +16267,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16300,7 +16310,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16314,10 +16324,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45820</v>
+        <v>44642</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16329,13 +16339,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16378,7 +16383,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16388,14 +16393,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45839</v>
+        <v>45109</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16408,7 +16413,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16451,7 +16456,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16461,14 +16466,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45839</v>
+        <v>45313</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16481,7 +16486,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.8</v>
+        <v>11.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16524,7 +16529,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16538,10 +16543,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44953</v>
+        <v>45288</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16554,7 +16559,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16597,7 +16602,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16611,10 +16616,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45840</v>
+        <v>45639</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16627,7 +16632,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16670,7 +16675,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16684,10 +16689,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45776</v>
+        <v>46280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16700,7 +16705,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16743,7 +16748,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16757,10 +16762,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44687</v>
+        <v>46281</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16772,13 +16777,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16821,7 +16821,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16831,14 +16831,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45258</v>
+        <v>45635</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16894,146 +16894,292 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
+          <t>A 38149-2026</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E213" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214" ht="15" customHeight="1">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>A 49435-2024</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>45595</v>
+      </c>
+      <c r="E214" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215" ht="15" customHeight="1">
+      <c r="A215" t="inlineStr">
+        <is>
           <t>S 1236-2022</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C213" t="n">
+      <c r="C215" t="n">
         <v/>
       </c>
-      <c r="D213" s="1" t="n">
+      <c r="D215" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="E213" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I213" t="n">
+      <c r="E215" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
         <v>0.1</v>
       </c>
-      <c r="J213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" t="n">
-        <v>0</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="n">
-        <v>0</v>
-      </c>
-      <c r="T213" t="n">
-        <v>0</v>
-      </c>
-      <c r="U213" t="n">
-        <v>0</v>
-      </c>
-      <c r="V213" s="2" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0</v>
+      </c>
+      <c r="V215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>S 839-2024</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D214" s="1" t="n">
+      <c r="D216" s="1" t="n">
         <v>45372</v>
       </c>
-      <c r="E214" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
+      <c r="E216" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
         <v>19.6</v>
       </c>
-      <c r="J214" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" t="n">
-        <v>0</v>
-      </c>
-      <c r="L214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M214" t="n">
-        <v>0</v>
-      </c>
-      <c r="N214" t="n">
-        <v>0</v>
-      </c>
-      <c r="O214" t="n">
-        <v>0</v>
-      </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0</v>
-      </c>
-      <c r="S214" t="n">
-        <v>0</v>
-      </c>
-      <c r="T214" t="n">
-        <v>0</v>
-      </c>
-      <c r="U214" t="n">
-        <v>0</v>
-      </c>
-      <c r="V214" s="2" t="inlineStr"/>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44459</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30080-2023</t>
+          <t>A 9277-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45110</v>
+        <v>44980</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1730,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1746,35 +1746,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         <v>45772</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55928-2025</t>
+          <t>A 19729-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45973</v>
+        <v>46135</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1915,22 +1915,17 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1945,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1954,365 +1949,370 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 30080-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45110</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 23455-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 19729-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9277-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44980</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 23455-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>45223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46227</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>46272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44536</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>44467</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44595</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44659</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>44818</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45469</v>
+        <v>45272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45420</v>
+        <v>45398</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4169,11 +4169,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4216,7 +4216,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45435</v>
+        <v>44856</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45554</v>
+        <v>45335</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4362,7 +4362,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45110</v>
+        <v>44860</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44908</v>
+        <v>44895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4508,7 +4508,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45113</v>
+        <v>45288</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45642</v>
+        <v>44496</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44978</v>
+        <v>45469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44937</v>
+        <v>44895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45091</v>
+        <v>45469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45763</v>
+        <v>45086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45180</v>
+        <v>44587</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4975,8 +4975,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5019,7 +5024,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5033,10 +5038,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45309</v>
+        <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5049,7 +5054,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5092,7 +5097,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5106,10 +5111,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45699</v>
+        <v>45408</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5127,7 +5132,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5170,7 +5175,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5180,14 +5185,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45462</v>
+        <v>44946</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5200,7 +5205,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5243,7 +5248,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5257,10 +5262,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45398</v>
+        <v>45820</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5274,7 +5279,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -5338,7 +5343,7 @@
         <v>45824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5394,7 +5399,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5404,14 +5409,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45800</v>
+        <v>46072</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5424,7 +5429,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5467,7 +5472,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5481,10 +5486,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44895</v>
+        <v>44973</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5497,7 +5502,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5540,7 +5545,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5554,10 +5559,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44887</v>
+        <v>45763</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5570,7 +5575,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5613,7 +5618,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5627,10 +5632,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44887</v>
+        <v>45554</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5643,7 +5648,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5686,7 +5691,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5700,10 +5705,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45272</v>
+        <v>45839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5716,7 +5721,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5759,7 +5764,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5773,10 +5778,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45687</v>
+        <v>45839</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5789,7 +5794,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5832,7 +5837,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5846,10 +5851,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45889</v>
+        <v>44953</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5859,11 +5864,6 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -5910,7 +5910,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45889</v>
+        <v>46087</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5939,13 +5939,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5988,7 +5983,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5998,14 +5993,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44946</v>
+        <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6018,7 +6013,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6061,7 +6056,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45890</v>
+        <v>45840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6090,13 +6085,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6139,7 +6129,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6153,10 +6143,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45111</v>
+        <v>46093</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6169,7 +6159,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6212,7 +6202,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6226,10 +6216,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45890</v>
+        <v>45874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6241,13 +6231,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6290,7 +6275,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6304,10 +6289,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45817</v>
+        <v>46093</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6319,8 +6304,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6363,7 +6353,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6377,10 +6367,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45820</v>
+        <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6392,13 +6382,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6441,7 +6426,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6455,10 +6440,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44973</v>
+        <v>45713</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6471,7 +6456,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6514,7 +6499,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6528,10 +6513,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45469</v>
+        <v>45776</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6544,7 +6529,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6587,7 +6572,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6601,10 +6586,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45839</v>
+        <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6617,7 +6602,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6660,7 +6645,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6674,10 +6659,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45839</v>
+        <v>46101</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6690,7 +6675,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6733,7 +6718,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6747,10 +6732,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44953</v>
+        <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6762,8 +6747,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6806,7 +6796,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6820,10 +6810,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45840</v>
+        <v>44687</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6835,8 +6825,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6879,7 +6874,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6889,14 +6884,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45918</v>
+        <v>45258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6908,13 +6903,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6957,7 +6947,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6971,10 +6961,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45924</v>
+        <v>45099</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6986,13 +6976,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7035,7 +7020,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7049,10 +7034,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45924</v>
+        <v>45890</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7066,11 +7051,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7113,7 +7098,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7127,10 +7112,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45924</v>
+        <v>44497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7142,13 +7127,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7191,7 +7171,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7205,10 +7185,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45924</v>
+        <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7222,11 +7202,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7269,7 +7249,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7279,14 +7259,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45258</v>
+        <v>44957</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7299,7 +7279,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7342,7 +7322,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7356,10 +7336,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45776</v>
+        <v>46106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7371,8 +7351,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7415,7 +7400,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7429,10 +7414,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45929</v>
+        <v>46106</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7444,8 +7429,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7488,7 +7478,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7502,10 +7492,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44687</v>
+        <v>45889</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7519,11 +7509,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7566,7 +7556,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7580,10 +7570,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45932</v>
+        <v>45889</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7595,8 +7585,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7639,7 +7634,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7653,10 +7648,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45385</v>
+        <v>46108</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7669,7 +7664,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7712,7 +7707,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7726,10 +7721,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45945</v>
+        <v>45890</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7747,7 +7742,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7790,7 +7785,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7804,10 +7799,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45492</v>
+        <v>46111</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7820,7 +7815,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7863,7 +7858,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7877,10 +7872,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45667</v>
+        <v>46111</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7892,13 +7887,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7941,7 +7931,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5897-2026</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7955,10 +7945,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46052</v>
+        <v>46111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7971,7 +7961,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8014,7 +8004,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8028,10 +8018,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45299</v>
+        <v>46111</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8044,7 +8034,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8087,7 +8077,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8101,10 +8091,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45958</v>
+        <v>46113</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8116,8 +8106,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8160,7 +8155,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8174,10 +8169,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45874</v>
+        <v>45642</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8190,7 +8185,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8233,7 +8228,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8247,10 +8242,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45281</v>
+        <v>46119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8263,7 +8258,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8306,7 +8301,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8320,10 +8315,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46059</v>
+        <v>44970</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8336,7 +8331,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>8.4</v>
+        <v>0.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8379,7 +8374,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8393,10 +8388,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45960</v>
+        <v>45514</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8408,13 +8403,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8457,7 +8447,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8471,10 +8461,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46059</v>
+        <v>45539</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8486,8 +8476,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8530,7 +8525,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8544,10 +8539,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45719</v>
+        <v>45113</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8560,7 +8555,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8603,7 +8598,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8617,10 +8612,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44615</v>
+        <v>46129</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8632,8 +8627,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45974</v>
+        <v>45699</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8705,8 +8705,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8749,7 +8754,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8763,10 +8768,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44970</v>
+        <v>45883</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8779,7 +8784,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.2</v>
+        <v>4.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8822,7 +8827,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44856</v>
+        <v>44990</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8852,7 +8857,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8895,7 +8900,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8909,10 +8914,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44860</v>
+        <v>45098</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8924,8 +8929,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8968,7 +8978,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8982,10 +8992,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46072</v>
+        <v>45918</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8997,8 +9007,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9041,7 +9056,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9051,14 +9066,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45091</v>
+        <v>44832</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9071,7 +9086,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9114,7 +9129,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9128,10 +9143,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45335</v>
+        <v>45091</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9144,7 +9159,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9187,7 +9202,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9201,10 +9216,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45196</v>
+        <v>45763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9217,7 +9232,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9260,7 +9275,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9274,10 +9289,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46001</v>
+        <v>45667</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9295,7 +9310,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9338,7 +9353,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9348,14 +9363,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46087</v>
+        <v>45924</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9367,8 +9382,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9411,7 +9431,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9425,10 +9445,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45713</v>
+        <v>45288</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9441,7 +9461,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9484,7 +9504,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9498,10 +9518,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44827</v>
+        <v>45110</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9514,7 +9534,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9557,7 +9577,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9571,10 +9591,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46008</v>
+        <v>45800</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9586,13 +9606,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9635,7 +9650,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9649,10 +9664,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45492</v>
+        <v>45924</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9664,8 +9679,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9708,7 +9728,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9722,10 +9742,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46093</v>
+        <v>45924</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9737,8 +9757,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9781,7 +9806,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9795,10 +9820,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46093</v>
+        <v>45924</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9812,11 +9837,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9859,7 +9884,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9873,10 +9898,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45098</v>
+        <v>45043</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9888,13 +9913,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9937,7 +9957,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9951,10 +9971,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44990</v>
+        <v>45180</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9967,7 +9987,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10010,7 +10030,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10024,10 +10044,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45621</v>
+        <v>45492</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10040,7 +10060,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10083,7 +10103,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10097,10 +10117,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46100</v>
+        <v>44908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10112,13 +10132,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10161,7 +10176,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10175,10 +10190,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45628</v>
+        <v>45929</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10191,7 +10206,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10234,7 +10249,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10248,10 +10263,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46101</v>
+        <v>45110</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10264,7 +10279,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10307,7 +10322,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10321,10 +10336,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46101</v>
+        <v>45149</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10337,7 +10352,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10380,7 +10395,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10390,14 +10405,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46106</v>
+        <v>45149</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10409,13 +10424,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10458,7 +10468,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10468,14 +10478,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46106</v>
+        <v>45109</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10487,13 +10497,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10536,7 +10541,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10550,10 +10555,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45086</v>
+        <v>45932</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10566,7 +10571,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10609,7 +10614,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10623,10 +10628,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46106</v>
+        <v>45110</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10638,13 +10643,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10687,7 +10687,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10701,10 +10701,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46108</v>
+        <v>45110</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10760,7 +10760,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45758</v>
+        <v>45111</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10789,13 +10789,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10838,7 +10833,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10852,10 +10847,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45758</v>
+        <v>46163</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10873,7 +10868,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10916,7 +10911,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10930,10 +10925,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44937</v>
+        <v>46163</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10945,8 +10940,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10989,7 +10989,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46111</v>
+        <v>46168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11062,7 +11062,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11076,10 +11076,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46111</v>
+        <v>46168</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11135,7 +11135,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46111</v>
+        <v>46168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11208,7 +11208,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45713</v>
+        <v>45309</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11281,7 +11281,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46111</v>
+        <v>45492</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11354,7 +11354,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46113</v>
+        <v>45945</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11446,10 +11446,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46119</v>
+        <v>45096</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11519,10 +11519,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45539</v>
+        <v>45175</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11536,11 +11536,11 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11583,7 +11583,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46129</v>
+        <v>45022</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11612,13 +11612,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11661,7 +11656,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11675,10 +11670,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44587</v>
+        <v>45462</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11690,13 +11685,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11739,7 +11729,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11753,10 +11743,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45299</v>
+        <v>45469</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11769,7 +11759,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11812,7 +11802,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11826,10 +11816,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45196</v>
+        <v>45469</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11842,7 +11832,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11885,7 +11875,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11899,10 +11889,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45883</v>
+        <v>46182</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11915,7 +11905,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11958,7 +11948,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11972,10 +11962,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45763</v>
+        <v>45958</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11988,7 +11978,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12031,7 +12021,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12041,14 +12031,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44701</v>
+        <v>46189</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12061,7 +12051,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12104,7 +12094,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12118,10 +12108,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44698</v>
+        <v>45960</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12133,8 +12123,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12177,7 +12172,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12191,10 +12186,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45800</v>
+        <v>45713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12207,7 +12202,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12250,7 +12245,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12264,10 +12259,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44497</v>
+        <v>45196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12280,7 +12275,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12323,7 +12318,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12337,10 +12332,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45224</v>
+        <v>44844</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12353,7 +12348,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12396,7 +12391,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12410,10 +12405,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45145</v>
+        <v>45091</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12426,7 +12421,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12469,7 +12464,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12483,10 +12478,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45408</v>
+        <v>45974</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12498,13 +12493,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12547,7 +12537,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12561,10 +12551,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45356</v>
+        <v>46246</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12576,8 +12566,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12620,7 +12615,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12634,10 +12629,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45149</v>
+        <v>46246</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12649,8 +12644,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12693,7 +12693,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12703,14 +12703,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45149</v>
+        <v>46247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12722,8 +12722,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12766,7 +12771,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12780,10 +12785,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45281</v>
+        <v>45420</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12795,8 +12800,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12839,7 +12849,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12853,10 +12863,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44895</v>
+        <v>44701</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12869,7 +12879,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12912,7 +12922,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12926,10 +12936,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44844</v>
+        <v>44698</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12942,7 +12952,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12985,7 +12995,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12995,14 +13005,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44832</v>
+        <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13015,7 +13025,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13058,7 +13068,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13072,10 +13082,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45469</v>
+        <v>45299</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13088,7 +13098,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13131,7 +13141,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13145,10 +13155,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45469</v>
+        <v>45370</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13161,7 +13171,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13204,7 +13214,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13218,10 +13228,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45313</v>
+        <v>46203</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13233,8 +13243,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13277,7 +13292,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13291,10 +13306,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13306,13 +13321,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13355,7 +13365,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13369,10 +13379,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46163</v>
+        <v>45313</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13384,13 +13394,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13433,7 +13438,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13447,10 +13452,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46168</v>
+        <v>45448</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13462,8 +13467,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13506,7 +13516,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13516,14 +13526,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44687</v>
+        <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13535,8 +13545,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13579,7 +13594,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13589,14 +13604,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45043</v>
+        <v>44687</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13609,7 +13624,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13652,7 +13667,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13666,10 +13681,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46168</v>
+        <v>46008</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13681,8 +13696,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13725,7 +13745,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13739,10 +13759,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46168</v>
+        <v>45196</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13755,7 +13775,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13798,7 +13818,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13812,10 +13832,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45215</v>
+        <v>44827</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13828,7 +13848,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13871,7 +13891,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13885,10 +13905,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44957</v>
+        <v>45314</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13901,7 +13921,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13944,7 +13964,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13958,10 +13978,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45022</v>
+        <v>45687</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13974,7 +13994,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14017,7 +14037,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14031,10 +14051,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44496</v>
+        <v>44909</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14090,7 +14110,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14104,10 +14124,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45096</v>
+        <v>45385</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14120,7 +14140,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14163,7 +14183,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14177,10 +14197,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45110</v>
+        <v>44995</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14193,7 +14213,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14236,7 +14256,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14250,10 +14270,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45110</v>
+        <v>44887</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14266,7 +14286,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14309,7 +14329,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14323,10 +14343,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46182</v>
+        <v>46280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14339,7 +14359,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14382,7 +14402,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14392,14 +14412,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46189</v>
+        <v>45215</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14412,7 +14432,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14455,7 +14475,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14469,10 +14489,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45140</v>
+        <v>45281</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14485,7 +14505,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14528,7 +14548,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14542,10 +14562,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45314</v>
+        <v>46281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14558,7 +14578,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14601,7 +14621,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14615,10 +14635,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44995</v>
+        <v>44812</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14631,7 +14651,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14674,7 +14694,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14688,10 +14708,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46246</v>
+        <v>45140</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14703,13 +14723,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14752,7 +14767,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 38149-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14766,10 +14781,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45370</v>
+        <v>46281</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14825,7 +14840,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14839,10 +14854,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46246</v>
+        <v>44995</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14854,13 +14869,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14903,7 +14913,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14917,10 +14927,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46247</v>
+        <v>45224</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14932,13 +14942,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14981,7 +14986,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14995,10 +15000,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44743</v>
+        <v>45281</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15011,7 +15016,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15054,7 +15059,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15068,10 +15073,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45099</v>
+        <v>44937</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15084,7 +15089,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15127,7 +15132,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15141,10 +15146,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44812</v>
+        <v>45145</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15157,7 +15162,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15200,7 +15205,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15214,10 +15219,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45621</v>
+        <v>45435</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15230,7 +15235,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15273,7 +15278,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 5897-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15287,10 +15292,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45091</v>
+        <v>46052</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15303,7 +15308,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15346,7 +15351,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15360,10 +15365,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44894</v>
+        <v>44642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15376,7 +15381,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15419,7 +15424,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15433,10 +15438,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46258</v>
+        <v>46059</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15449,7 +15454,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15492,7 +15497,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15506,10 +15511,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44909</v>
+        <v>46059</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15522,7 +15527,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15565,7 +15570,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15579,10 +15584,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46203</v>
+        <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15594,13 +15599,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>2.9</v>
+        <v>21.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15657,10 +15657,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45288</v>
+        <v>45719</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15733,7 +15733,7 @@
         <v>45224</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15803,10 +15803,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46168</v>
+        <v>45156</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15876,10 +15876,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45448</v>
+        <v>45621</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15891,13 +15891,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15940,7 +15935,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15954,10 +15949,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45175</v>
+        <v>45621</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15969,13 +15964,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16018,7 +16008,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16032,10 +16022,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45110</v>
+        <v>45299</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16048,7 +16038,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16091,7 +16081,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16105,10 +16095,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45514</v>
+        <v>45356</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16121,7 +16111,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16164,7 +16154,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16178,10 +16168,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45156</v>
+        <v>44887</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16194,7 +16184,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16237,7 +16227,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16251,10 +16241,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44995</v>
+        <v>44743</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16267,7 +16257,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16310,7 +16300,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16324,10 +16314,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44642</v>
+        <v>45628</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16340,7 +16330,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16383,7 +16373,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16393,14 +16383,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45109</v>
+        <v>44978</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16413,7 +16403,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16456,7 +16446,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16466,14 +16456,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45313</v>
+        <v>45758</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16485,8 +16475,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>11.7</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16529,7 +16524,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16543,10 +16538,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45288</v>
+        <v>45758</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16558,8 +16553,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16602,7 +16602,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16612,14 +16612,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45639</v>
+        <v>45313</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.1</v>
+        <v>11.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16675,7 +16675,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16689,10 +16689,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46280</v>
+        <v>45639</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16748,7 +16748,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38146-2026</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16762,10 +16762,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46281</v>
+        <v>45595</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16838,7 +16838,7 @@
         <v>45635</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 38149-2026</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16904,14 +16904,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46281</v>
+        <v>45800</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16967,7 +16967,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16981,10 +16981,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45595</v>
+        <v>45817</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17055,7 +17055,7 @@
         <v>44623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45372</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44459</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 9277-2023</t>
+          <t>A 30080-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44980</v>
+        <v>45110</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,20 +1706,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1730,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1746,888 +1746,888 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 9277-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44980</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 23455-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 19729-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 52041-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45223</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 31736-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 36670-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Almrostöra</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 20063-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45772</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>3.4</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Skinntagging</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 19729-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 30080-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45110</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 23455-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 55928-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 52041-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45223</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 31736-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 36670-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Almrostöra</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44536</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>44467</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44595</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44659</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38210-2022</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44812</v>
+        <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3919,7 +3919,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44530</v>
+        <v>44818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3992,7 +3992,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 38210-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44818</v>
+        <v>44812</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4065,7 +4065,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45272</v>
+        <v>45420</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,8 +4094,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4138,7 +4143,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4152,10 +4157,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45398</v>
+        <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4167,13 +4172,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4216,7 +4216,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44856</v>
+        <v>45180</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45335</v>
+        <v>45469</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4362,7 +4362,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44860</v>
+        <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44895</v>
+        <v>45110</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4508,7 +4508,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45288</v>
+        <v>44908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44496</v>
+        <v>45113</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45469</v>
+        <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44895</v>
+        <v>44978</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45469</v>
+        <v>44937</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45086</v>
+        <v>45435</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44587</v>
+        <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4973,11 +4973,6 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -5024,7 +5019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5038,10 +5033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44937</v>
+        <v>45309</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5054,7 +5049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5097,7 +5092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5111,10 +5106,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45408</v>
+        <v>45699</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5132,7 +5127,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5175,7 +5170,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5185,14 +5180,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44946</v>
+        <v>45462</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5205,7 +5200,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5248,7 +5243,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5262,10 +5257,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45820</v>
+        <v>45398</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -5326,7 +5321,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5340,10 +5335,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45824</v>
+        <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5356,7 +5351,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5399,7 +5394,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46072</v>
+        <v>44887</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5429,7 +5424,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5472,7 +5467,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5486,10 +5481,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44973</v>
+        <v>44887</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5502,7 +5497,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5545,7 +5540,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5559,10 +5554,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45763</v>
+        <v>45111</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5575,7 +5570,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5618,7 +5613,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5632,10 +5627,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45554</v>
+        <v>45272</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5648,7 +5643,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5691,7 +5686,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5705,10 +5700,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45839</v>
+        <v>45687</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5721,7 +5716,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5764,7 +5759,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5778,10 +5773,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45839</v>
+        <v>44973</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5794,7 +5789,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5837,7 +5832,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5851,10 +5846,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44953</v>
+        <v>45469</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5867,7 +5862,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5910,7 +5905,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5920,14 +5915,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46087</v>
+        <v>45385</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5940,7 +5935,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5983,7 +5978,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5997,10 +5992,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44615</v>
+        <v>45492</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6013,7 +6008,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6056,7 +6051,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6070,10 +6065,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45840</v>
+        <v>45667</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6085,8 +6080,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6129,7 +6129,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46093</v>
+        <v>45281</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6216,10 +6216,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45874</v>
+        <v>45299</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6275,7 +6275,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46093</v>
+        <v>44615</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6304,13 +6304,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6353,7 +6348,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6367,10 +6362,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44894</v>
+        <v>44970</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6383,7 +6378,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6426,7 +6421,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6440,10 +6435,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45713</v>
+        <v>45883</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6456,7 +6451,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6499,7 +6494,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6513,10 +6508,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45776</v>
+        <v>44856</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6529,7 +6524,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6572,7 +6567,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6586,10 +6581,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46101</v>
+        <v>45763</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6602,7 +6597,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6645,7 +6640,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6659,10 +6654,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46101</v>
+        <v>44860</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6675,7 +6670,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6718,7 +6713,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6732,10 +6727,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46100</v>
+        <v>45091</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6747,13 +6742,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6796,7 +6786,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6810,10 +6800,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44687</v>
+        <v>45889</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6827,11 +6817,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6874,7 +6864,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6884,14 +6874,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45258</v>
+        <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6903,8 +6893,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6947,7 +6942,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6961,10 +6956,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45099</v>
+        <v>45335</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6977,7 +6972,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7020,7 +7015,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7037,7 +7032,7 @@
         <v>45890</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7055,7 +7050,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7098,7 +7093,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7112,10 +7107,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44497</v>
+        <v>45890</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7127,8 +7122,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46106</v>
+        <v>45874</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7200,13 +7200,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7249,7 +7244,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7263,10 +7258,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44957</v>
+        <v>45196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7279,7 +7274,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7322,7 +7317,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7336,10 +7331,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46106</v>
+        <v>45800</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7351,13 +7346,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7400,7 +7390,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7414,10 +7404,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46106</v>
+        <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7429,13 +7419,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7478,7 +7463,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7492,10 +7477,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45889</v>
+        <v>45713</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7507,13 +7492,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7556,7 +7536,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7570,10 +7550,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45889</v>
+        <v>44827</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7585,13 +7565,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7634,7 +7609,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7648,10 +7623,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46108</v>
+        <v>45492</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7664,7 +7639,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7707,7 +7682,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7721,10 +7696,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45890</v>
+        <v>45098</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7742,7 +7717,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7785,7 +7760,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7799,10 +7774,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46111</v>
+        <v>44990</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7815,7 +7790,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7858,7 +7833,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7872,10 +7847,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46111</v>
+        <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7887,8 +7862,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7931,7 +7911,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7945,10 +7925,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46111</v>
+        <v>45621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7961,7 +7941,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8004,7 +7984,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8018,10 +7998,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46111</v>
+        <v>45924</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8033,8 +8013,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8077,7 +8062,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8091,10 +8076,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46113</v>
+        <v>45924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8108,11 +8093,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8155,7 +8140,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8169,10 +8154,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45642</v>
+        <v>45924</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8184,8 +8169,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8228,7 +8218,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8242,10 +8232,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46119</v>
+        <v>45924</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8257,8 +8247,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8301,7 +8296,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8315,10 +8310,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44970</v>
+        <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8331,7 +8326,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8374,7 +8369,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8388,10 +8383,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45514</v>
+        <v>45929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8404,7 +8399,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8447,7 +8442,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8461,10 +8456,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45539</v>
+        <v>45086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8476,13 +8471,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8525,7 +8515,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8539,10 +8529,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45113</v>
+        <v>45932</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8555,7 +8545,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8598,7 +8588,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8612,10 +8602,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46129</v>
+        <v>45758</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8633,7 +8623,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8676,7 +8666,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8690,10 +8680,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45699</v>
+        <v>45758</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8711,7 +8701,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8754,7 +8744,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8768,10 +8758,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45883</v>
+        <v>44937</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8784,7 +8774,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8827,7 +8817,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8841,10 +8831,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44990</v>
+        <v>45713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8857,7 +8847,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8900,7 +8890,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8914,10 +8904,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45098</v>
+        <v>45945</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8978,7 +8968,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8992,10 +8982,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45918</v>
+        <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9013,7 +9003,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9056,7 +9046,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9066,14 +9056,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44832</v>
+        <v>45958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9086,7 +9076,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9129,7 +9119,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9143,10 +9133,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45091</v>
+        <v>45960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9158,8 +9148,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9202,7 +9197,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9216,10 +9211,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45763</v>
+        <v>45299</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9232,7 +9227,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9275,7 +9270,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45667</v>
+        <v>45196</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9304,13 +9299,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9353,7 +9343,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9367,10 +9357,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45924</v>
+        <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9382,13 +9372,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9431,7 +9416,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9445,10 +9430,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45288</v>
+        <v>44701</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9461,7 +9446,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9504,7 +9489,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9518,10 +9503,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45110</v>
+        <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9534,7 +9519,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9577,7 +9562,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9591,10 +9576,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45800</v>
+        <v>44497</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9607,7 +9592,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9650,7 +9635,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9664,10 +9649,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45924</v>
+        <v>46163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9681,11 +9666,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9728,7 +9713,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9742,10 +9727,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45924</v>
+        <v>45224</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9757,13 +9742,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9806,7 +9786,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9820,10 +9800,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45924</v>
+        <v>45145</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9835,13 +9815,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9884,7 +9859,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9898,10 +9873,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45043</v>
+        <v>46163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9913,8 +9888,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9957,7 +9937,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9971,10 +9951,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45180</v>
+        <v>46001</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9986,8 +9966,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10030,7 +10015,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10044,10 +10029,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45492</v>
+        <v>45408</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10059,8 +10044,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10103,7 +10093,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10117,10 +10107,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44908</v>
+        <v>45356</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10133,7 +10123,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10176,7 +10166,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10190,10 +10180,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45929</v>
+        <v>45149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10206,7 +10196,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10249,7 +10239,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10259,14 +10249,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45110</v>
+        <v>45149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10279,7 +10269,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10322,7 +10312,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10336,10 +10326,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45149</v>
+        <v>46168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10352,7 +10342,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10395,7 +10385,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10405,14 +10395,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45149</v>
+        <v>46008</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10424,8 +10414,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10468,7 +10463,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10478,14 +10473,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45109</v>
+        <v>46168</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10498,7 +10493,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10541,7 +10536,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10555,10 +10550,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45932</v>
+        <v>46168</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10571,7 +10566,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10614,7 +10609,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10628,10 +10623,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45110</v>
+        <v>45281</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10644,7 +10639,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10687,7 +10682,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10701,10 +10696,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45110</v>
+        <v>44895</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10717,7 +10712,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10760,7 +10755,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10774,10 +10769,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45111</v>
+        <v>44844</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10790,7 +10785,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10833,7 +10828,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10843,14 +10838,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46163</v>
+        <v>44832</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10862,13 +10857,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10911,7 +10901,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10925,10 +10915,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46163</v>
+        <v>45469</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10940,13 +10930,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10989,7 +10974,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11003,10 +10988,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46168</v>
+        <v>45469</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11019,7 +11004,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11062,7 +11047,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11076,10 +11061,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46168</v>
+        <v>45313</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11092,7 +11077,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11135,7 +11120,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11145,14 +11130,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46168</v>
+        <v>44687</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11165,7 +11150,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11208,7 +11193,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11222,10 +11207,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45309</v>
+        <v>45043</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11238,7 +11223,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11281,7 +11266,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 5897-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11295,10 +11280,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45492</v>
+        <v>46052</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11311,7 +11296,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11354,7 +11339,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11368,10 +11353,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45945</v>
+        <v>45215</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11383,13 +11368,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11432,7 +11412,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11446,10 +11426,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45096</v>
+        <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11462,7 +11442,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11505,7 +11485,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11519,10 +11499,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45175</v>
+        <v>44957</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11534,13 +11514,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11583,7 +11558,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11597,10 +11572,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45022</v>
+        <v>46059</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11613,7 +11588,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11656,7 +11631,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11670,10 +11645,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45462</v>
+        <v>45719</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11686,7 +11661,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11729,7 +11704,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11743,10 +11718,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45469</v>
+        <v>45022</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11759,7 +11734,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11802,7 +11777,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11816,10 +11791,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45469</v>
+        <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11832,7 +11807,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11875,7 +11850,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11889,10 +11864,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46182</v>
+        <v>46072</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11905,7 +11880,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11948,7 +11923,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11962,10 +11937,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45958</v>
+        <v>44496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11978,7 +11953,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12021,7 +11996,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12031,14 +12006,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46189</v>
+        <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12051,7 +12026,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12094,7 +12069,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12108,10 +12083,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45960</v>
+        <v>45110</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12123,13 +12098,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12172,7 +12142,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12186,10 +12156,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45713</v>
+        <v>45110</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12202,7 +12172,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12245,7 +12215,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12255,14 +12225,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45196</v>
+        <v>46087</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12275,7 +12245,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12318,7 +12288,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12328,14 +12298,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44844</v>
+        <v>46189</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12348,7 +12318,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12391,7 +12361,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12405,10 +12375,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45091</v>
+        <v>46093</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12421,7 +12391,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12464,7 +12434,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12478,10 +12448,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45974</v>
+        <v>46093</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12493,8 +12463,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12537,7 +12512,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12551,10 +12526,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46246</v>
+        <v>46100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12572,7 +12547,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12615,7 +12590,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12629,10 +12604,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46246</v>
+        <v>46101</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12644,13 +12619,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12693,7 +12663,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12707,10 +12677,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46247</v>
+        <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12722,13 +12692,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12771,7 +12736,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12785,10 +12750,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45420</v>
+        <v>46106</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12806,7 +12771,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12849,7 +12814,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12863,10 +12828,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44701</v>
+        <v>46106</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12878,8 +12843,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12922,7 +12892,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12936,10 +12906,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44698</v>
+        <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12951,8 +12921,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12995,7 +12970,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13009,10 +12984,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46258</v>
+        <v>46108</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13025,7 +13000,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13068,7 +13043,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13082,10 +13057,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45299</v>
+        <v>45140</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13141,7 +13116,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13155,10 +13130,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45370</v>
+        <v>45314</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13171,7 +13146,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13214,7 +13189,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13228,10 +13203,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46203</v>
+        <v>46111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13243,13 +13218,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13292,7 +13262,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13306,10 +13276,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46168</v>
+        <v>46111</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13322,7 +13292,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13365,7 +13335,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13379,10 +13349,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45313</v>
+        <v>44995</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13395,7 +13365,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>13.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13438,7 +13408,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13452,10 +13422,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45448</v>
+        <v>46111</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13467,13 +13437,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13516,7 +13481,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13530,10 +13495,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46001</v>
+        <v>46111</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13545,13 +13510,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13594,7 +13554,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13604,14 +13564,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44687</v>
+        <v>46113</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13623,8 +13583,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13667,7 +13632,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13681,10 +13646,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46008</v>
+        <v>46119</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13696,13 +13661,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13745,7 +13705,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13759,10 +13719,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45196</v>
+        <v>45370</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13775,7 +13735,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13818,7 +13778,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13832,10 +13792,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44827</v>
+        <v>45539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13847,8 +13807,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13891,7 +13856,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13905,10 +13870,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45314</v>
+        <v>46129</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13920,8 +13885,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13964,7 +13934,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13978,10 +13948,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45687</v>
+        <v>44743</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13994,7 +13964,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14037,7 +14007,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14051,10 +14021,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44909</v>
+        <v>46246</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14066,8 +14036,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14110,7 +14085,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14124,10 +14099,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45385</v>
+        <v>45099</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14140,7 +14115,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14183,7 +14158,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14197,10 +14172,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44995</v>
+        <v>44812</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14213,7 +14188,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14256,7 +14231,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14270,10 +14245,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44887</v>
+        <v>46246</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14285,8 +14260,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14329,7 +14309,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14343,10 +14323,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46280</v>
+        <v>45621</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14359,7 +14339,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14402,7 +14382,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14416,10 +14396,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45215</v>
+        <v>45091</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14432,7 +14412,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.4</v>
+        <v>21.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14475,7 +14455,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14489,10 +14469,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45281</v>
+        <v>44894</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14505,7 +14485,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14548,7 +14528,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 38146-2026</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14562,10 +14542,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46281</v>
+        <v>46247</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14577,8 +14557,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14621,7 +14606,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14635,10 +14620,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44812</v>
+        <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14651,7 +14636,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14694,7 +14679,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14708,10 +14693,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45140</v>
+        <v>45288</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14724,7 +14709,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14767,7 +14752,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 38149-2026</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14781,10 +14766,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46281</v>
+        <v>45224</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14797,7 +14782,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14840,7 +14825,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14854,10 +14839,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44995</v>
+        <v>45448</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14869,8 +14854,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14913,7 +14903,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14927,10 +14917,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45224</v>
+        <v>45175</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14942,8 +14932,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14986,7 +14981,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15000,10 +14995,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45281</v>
+        <v>45110</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15016,7 +15011,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15059,7 +15054,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15073,10 +15068,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44937</v>
+        <v>46258</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15089,7 +15084,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15132,7 +15127,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15146,10 +15141,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45145</v>
+        <v>46203</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15161,8 +15156,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15205,7 +15205,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15219,10 +15219,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45435</v>
+        <v>45514</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15278,7 +15278,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 5897-2026</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15292,10 +15292,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46052</v>
+        <v>45156</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15365,10 +15365,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44642</v>
+        <v>44995</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15424,7 +15424,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15438,10 +15438,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46059</v>
+        <v>44642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15497,7 +15497,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46059</v>
+        <v>46168</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15570,7 +15570,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15580,14 +15580,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45091</v>
+        <v>45109</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>21.6</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15653,14 +15653,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45719</v>
+        <v>45313</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>11.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15716,7 +15716,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15730,10 +15730,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45224</v>
+        <v>45288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15803,10 +15803,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45156</v>
+        <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15862,7 +15862,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15876,10 +15876,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45621</v>
+        <v>45635</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15935,7 +15935,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15949,10 +15949,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45621</v>
+        <v>45595</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16008,7 +16008,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16022,10 +16022,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45299</v>
+        <v>46280</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16081,7 +16081,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 38149-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16095,10 +16095,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45356</v>
+        <v>46281</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16164,14 +16164,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44887</v>
+        <v>45800</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16227,7 +16227,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16241,10 +16241,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44743</v>
+        <v>46281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16300,7 +16300,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16310,14 +16310,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45628</v>
+        <v>44946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16373,7 +16373,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16387,10 +16387,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44978</v>
+        <v>45817</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16446,7 +16446,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16460,10 +16460,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45758</v>
+        <v>45820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16524,7 +16524,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16538,10 +16538,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45758</v>
+        <v>45839</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16553,13 +16553,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16602,7 +16597,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16612,14 +16607,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45313</v>
+        <v>45839</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16632,7 +16627,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16675,7 +16670,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16689,10 +16684,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45639</v>
+        <v>44953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16705,7 +16700,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16748,7 +16743,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16762,10 +16757,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45595</v>
+        <v>45840</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16778,7 +16773,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16821,7 +16816,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16831,14 +16826,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45635</v>
+        <v>45258</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16851,7 +16846,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>9.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16894,7 +16889,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16904,14 +16899,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45800</v>
+        <v>45776</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16924,7 +16919,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16967,7 +16962,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16981,10 +16976,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45817</v>
+        <v>44687</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16996,8 +16991,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17055,7 +17055,7 @@
         <v>44623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45372</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44459</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45110</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>46163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>46135</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45772</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44799</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44536</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44560</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>44467</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44595</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44659</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>44818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>44812</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45420</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>45763</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45180</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45469</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45110</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>44908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45113</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>44978</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>44937</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45435</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45309</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45699</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45462</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45398</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44895</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44887</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44887</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45111</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45272</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>45687</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44973</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45469</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>45385</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45492</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45667</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>45281</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>45299</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44615</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44970</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45883</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44856</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>45763</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44860</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>45091</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>45889</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45335</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45890</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>45890</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45874</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>45196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45800</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>45713</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>44827</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45492</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45098</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44990</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45924</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45924</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45924</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45924</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>45628</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>45086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45932</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45758</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45758</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44937</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45945</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45299</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45196</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44701</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44497</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>46163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45224</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45145</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>46163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>46001</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45408</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45356</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>45149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>46168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>46008</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>46168</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>46168</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>45281</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44895</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44844</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44832</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45469</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>45469</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45313</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44687</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45043</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>46052</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>45215</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44957</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>46059</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45719</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>45022</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>46072</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45110</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45110</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>46087</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>46189</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46093</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46093</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>46100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>46101</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>46106</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>46106</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>46106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>46108</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45140</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45314</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>46111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>46111</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44995</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>46111</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46111</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>46113</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>46119</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45370</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>46129</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44743</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46246</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45099</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44812</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>46246</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45621</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>45091</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>44894</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>46247</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45288</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45224</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45448</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45175</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45110</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>46258</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>46203</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45514</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45156</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44995</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>44642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>46168</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45109</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45313</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45635</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45595</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>46280</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>46281</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45800</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>46281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45817</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45839</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45839</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45840</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45258</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45776</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44687</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45372</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE216"/>
+  <dimension ref="A1:AE213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50318-2021</t>
+          <t>A 30080-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44459</v>
+        <v>45110</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1633,50 +1633,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 50318-2021 artfynd.xlsx", "A 50318-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 50318-2021 karta.png", "A 50318-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 50318-2021 georefererad karta.tif", "A 50318-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/knärot/A 50318-2021 karta knärot.png", "A 50318-2021")</f>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 50318-2021 FSC-klagomål.docx", "A 50318-2021")</f>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 50318-2021 FSC-klagomål mail.docx", "A 50318-2021")</f>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 50318-2021 tillsynsbegäran.docx", "A 50318-2021")</f>
-        <v/>
-      </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 50318-2021 tillsynsbegäran mail.docx", "A 50318-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30080-2023</t>
+          <t>A 19729-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1690,10 +1686,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45110</v>
+        <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,10 +1702,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1718,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1730,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1742,46 +1738,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55928-2025</t>
+          <t>A 23455-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45973</v>
+        <v>46163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1816,16 +1812,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1840,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1849,264 +1845,264 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 9277-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>44980</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>1.3</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 23455-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19729-2026</t>
+          <t>A 31736-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2116,14 +2112,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46135</v>
+        <v>46227</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,13 +2132,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2176,35 +2172,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
     </row>
@@ -2228,7 +2224,7 @@
         <v>45223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2312,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 31736-2026</t>
+          <t>A 36670-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2326,14 +2322,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46227</v>
+        <v>46272</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2346,23 +2342,23 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -2370,10 +2366,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2386,42 +2382,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Almrostöra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 36670-2026</t>
+          <t>A 20063-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2431,14 +2427,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46272</v>
+        <v>45772</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2451,7 +2447,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2460,13 +2456,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2478,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2491,59 +2487,59 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Almrostöra</t>
+          <t>Skinntagging</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20063-2025</t>
+          <t>S 725-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45772</v>
+        <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2555,17 +2551,22 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>520.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2580,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2596,59 +2597,59 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skinntagging</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/S 725-2026 artfynd.xlsx", "S 725-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/S 725-2026 karta.png", "S 725-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/S 725-2026 georefererad karta.tif", "S 725-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/S 725-2026 FSC-klagomål.docx", "S 725-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/S 725-2026 FSC-klagomål mail.docx", "S 725-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/S 725-2026 tillsynsbegäran.docx", "S 725-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/S 725-2026 tillsynsbegäran mail.docx", "S 725-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S 725-2026</t>
+          <t>A 74438-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46093</v>
+        <v>44560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2660,19 +2661,14 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>520.8</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2696,52 +2692,20 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/S 725-2026 artfynd.xlsx", "S 725-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/S 725-2026 karta.png", "S 725-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/S 725-2026 georefererad karta.tif", "S 725-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/S 725-2026 FSC-klagomål.docx", "S 725-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/S 725-2026 FSC-klagomål mail.docx", "S 725-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/S 725-2026 tillsynsbegäran.docx", "S 725-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/S 725-2026 tillsynsbegäran mail.docx", "S 725-2026")</f>
-        <v/>
-      </c>
+      <c r="V21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 74438-2021</t>
+          <t>A 35607-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2755,10 +2719,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44560</v>
+        <v>44799</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2771,7 +2735,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2814,7 +2778,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35607-2022</t>
+          <t>A 29874-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2828,10 +2792,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44799</v>
+        <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2844,7 +2808,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2887,7 +2851,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 29874-2022</t>
+          <t>A 70412-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2901,10 +2865,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44756</v>
+        <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2917,7 +2881,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2960,7 +2924,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 70412-2021</t>
+          <t>A 74491-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2974,10 +2938,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44536</v>
+        <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2990,7 +2954,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3033,7 +2997,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 74491-2021</t>
+          <t>A 6251-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3047,10 +3011,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44560</v>
+        <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3062,8 +3026,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3106,7 +3075,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6251-2022</t>
+          <t>A 52537-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3120,10 +3089,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44600</v>
+        <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3135,13 +3104,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3184,7 +3148,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52537-2022</t>
+          <t>A 52971-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3198,10 +3162,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44874</v>
+        <v>44467</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3214,7 +3178,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3257,7 +3221,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52971-2021</t>
+          <t>A 5594-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3271,10 +3235,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44467</v>
+        <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3287,7 +3251,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3330,7 +3294,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5594-2022</t>
+          <t>A 5600-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3347,7 +3311,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3360,7 +3324,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3403,7 +3367,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5600-2022</t>
+          <t>A 15415-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3417,10 +3381,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44595</v>
+        <v>44659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3432,8 +3396,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>8.9</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3476,7 +3445,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15415-2022</t>
+          <t>A 72213-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3490,10 +3459,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44659</v>
+        <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3505,13 +3474,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3554,7 +3518,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 72213-2021</t>
+          <t>A 24976-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3568,10 +3532,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44544</v>
+        <v>44728</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3584,7 +3548,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3627,7 +3591,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24976-2022</t>
+          <t>A 4409-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3641,10 +3605,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44728</v>
+        <v>44589</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3657,7 +3621,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3700,7 +3664,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50741-2021</t>
+          <t>A 38210-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3714,10 +3678,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44460</v>
+        <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3730,7 +3694,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3773,7 +3737,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4409-2022</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3787,10 +3751,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44589</v>
+        <v>44530</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3803,7 +3767,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3846,7 +3810,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3860,10 +3824,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44530</v>
+        <v>44818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3876,7 +3840,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3919,7 +3883,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3933,10 +3897,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44818</v>
+        <v>45469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3949,7 +3913,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3992,7 +3956,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38210-2022</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4006,10 +3970,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44812</v>
+        <v>45420</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4021,8 +3985,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4065,7 +4034,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4079,10 +4048,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45420</v>
+        <v>45435</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4094,13 +4063,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4143,7 +4107,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4157,10 +4121,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45763</v>
+        <v>45554</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4173,7 +4137,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4216,7 +4180,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4230,10 +4194,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45180</v>
+        <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4246,7 +4210,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4289,7 +4253,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4303,10 +4267,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45469</v>
+        <v>44908</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4319,7 +4283,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4362,7 +4326,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4376,10 +4340,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45554</v>
+        <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4392,7 +4356,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4435,7 +4399,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4449,10 +4413,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45110</v>
+        <v>45642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4465,7 +4429,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4508,7 +4472,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4522,10 +4486,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44908</v>
+        <v>44978</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4538,7 +4502,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4581,7 +4545,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4595,10 +4559,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45113</v>
+        <v>44937</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4611,7 +4575,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4654,7 +4618,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4668,10 +4632,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45642</v>
+        <v>45091</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4684,7 +4648,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4727,7 +4691,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4741,10 +4705,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44978</v>
+        <v>45763</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4757,7 +4721,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4800,7 +4764,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4814,10 +4778,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44937</v>
+        <v>45180</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4830,7 +4794,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4873,7 +4837,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4887,10 +4851,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45435</v>
+        <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4903,7 +4867,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4946,7 +4910,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4960,10 +4924,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45091</v>
+        <v>45699</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4975,8 +4939,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5019,7 +4988,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5033,10 +5002,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45309</v>
+        <v>45462</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5049,7 +5018,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5092,7 +5061,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5106,10 +5075,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45699</v>
+        <v>45398</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,11 +5092,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5170,7 +5139,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5184,10 +5153,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45462</v>
+        <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5200,7 +5169,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5243,7 +5212,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5257,10 +5226,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45398</v>
+        <v>44887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5272,13 +5241,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5321,7 +5285,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5335,10 +5299,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44895</v>
+        <v>44887</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5351,7 +5315,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5394,7 +5358,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5408,10 +5372,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44887</v>
+        <v>45687</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5424,7 +5388,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5467,7 +5431,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5481,10 +5445,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44887</v>
+        <v>45111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5497,7 +5461,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5540,7 +5504,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5554,10 +5518,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45111</v>
+        <v>45272</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5570,7 +5534,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5613,7 +5577,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5627,10 +5591,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45272</v>
+        <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5643,7 +5607,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5686,7 +5650,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5700,10 +5664,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45687</v>
+        <v>45469</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5716,7 +5680,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5759,7 +5723,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5773,10 +5737,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44973</v>
+        <v>45385</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5789,7 +5753,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5832,7 +5796,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5846,10 +5810,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45469</v>
+        <v>45492</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5862,7 +5826,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5905,7 +5869,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5919,10 +5883,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45385</v>
+        <v>45667</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5934,8 +5898,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5978,7 +5947,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5992,10 +5961,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45492</v>
+        <v>45299</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6008,7 +5977,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6051,7 +6020,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6065,10 +6034,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45667</v>
+        <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6080,13 +6049,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6129,7 +6093,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6143,10 +6107,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45281</v>
+        <v>45889</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6158,8 +6122,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6202,7 +6171,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6216,10 +6185,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45299</v>
+        <v>45889</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6231,8 +6200,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6275,7 +6249,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6289,10 +6263,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44615</v>
+        <v>45890</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6304,8 +6278,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6348,7 +6327,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6362,10 +6341,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44970</v>
+        <v>45890</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6377,8 +6356,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6421,7 +6405,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6435,10 +6419,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45883</v>
+        <v>44615</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6451,7 +6435,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6494,7 +6478,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6508,10 +6492,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44856</v>
+        <v>45883</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6524,7 +6508,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6584,7 +6568,7 @@
         <v>45763</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6640,7 +6624,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6654,10 +6638,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44860</v>
+        <v>45874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6670,7 +6654,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6713,7 +6697,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6727,10 +6711,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45091</v>
+        <v>45824</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6743,7 +6727,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6786,7 +6770,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6800,10 +6784,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45889</v>
+        <v>45800</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6815,13 +6799,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6864,7 +6843,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6878,10 +6857,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45889</v>
+        <v>44970</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6893,13 +6872,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6942,7 +6916,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6956,10 +6930,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45335</v>
+        <v>44856</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6972,7 +6946,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7015,7 +6989,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7029,10 +7003,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45890</v>
+        <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7044,13 +7018,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7093,7 +7062,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7107,10 +7076,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45890</v>
+        <v>45918</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7128,7 +7097,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7171,7 +7140,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7185,10 +7154,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45874</v>
+        <v>45091</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7201,7 +7170,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7244,7 +7213,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7258,10 +7227,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45196</v>
+        <v>45924</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7273,8 +7242,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7317,7 +7291,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7331,10 +7305,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45800</v>
+        <v>45924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7346,8 +7320,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7390,7 +7369,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7404,10 +7383,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45824</v>
+        <v>45335</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7420,7 +7399,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7463,7 +7442,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7477,10 +7456,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45713</v>
+        <v>45924</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7492,8 +7471,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7536,7 +7520,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7550,10 +7534,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44827</v>
+        <v>45924</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7565,8 +7549,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7609,7 +7598,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7623,10 +7612,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45492</v>
+        <v>45196</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7639,7 +7628,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7682,7 +7671,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7696,10 +7685,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45098</v>
+        <v>45929</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7711,13 +7700,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7760,7 +7744,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7774,10 +7758,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44990</v>
+        <v>45932</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7790,7 +7774,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7833,7 +7817,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7847,10 +7831,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45918</v>
+        <v>45713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7862,13 +7846,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7911,7 +7890,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7925,10 +7904,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45621</v>
+        <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7941,7 +7920,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7984,7 +7963,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7998,10 +7977,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45924</v>
+        <v>45492</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8013,13 +7992,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8062,7 +8036,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8076,10 +8050,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45924</v>
+        <v>45945</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8093,11 +8067,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8140,7 +8114,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8154,10 +8128,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45924</v>
+        <v>45098</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8171,11 +8145,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8218,7 +8192,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8232,10 +8206,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45924</v>
+        <v>44990</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8247,13 +8221,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8296,7 +8265,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8310,10 +8279,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45628</v>
+        <v>45621</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8326,7 +8295,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8369,7 +8338,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8383,10 +8352,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45929</v>
+        <v>45958</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8399,7 +8368,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8442,7 +8411,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8456,10 +8425,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45086</v>
+        <v>45628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8472,7 +8441,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8515,7 +8484,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8529,10 +8498,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45932</v>
+        <v>45960</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8544,8 +8513,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8588,7 +8562,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8602,10 +8576,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45758</v>
+        <v>46163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8623,7 +8597,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8666,7 +8640,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8680,10 +8654,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45758</v>
+        <v>45086</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8695,13 +8669,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8744,7 +8713,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8758,10 +8727,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44937</v>
+        <v>46163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8773,8 +8742,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8817,7 +8791,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8831,10 +8805,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45713</v>
+        <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8846,8 +8820,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8890,7 +8869,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8904,10 +8883,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45945</v>
+        <v>45758</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8925,7 +8904,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8968,7 +8947,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8982,10 +8961,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44587</v>
+        <v>44937</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8997,13 +8976,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9046,7 +9020,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9060,10 +9034,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45958</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9076,7 +9050,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9119,7 +9093,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9133,10 +9107,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45960</v>
+        <v>45713</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9148,13 +9122,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9197,7 +9166,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9211,10 +9180,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45299</v>
+        <v>46168</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9227,7 +9196,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9270,7 +9239,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9284,10 +9253,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45196</v>
+        <v>46168</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9300,7 +9269,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9343,7 +9312,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9357,10 +9326,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45974</v>
+        <v>46168</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9373,7 +9342,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9416,7 +9385,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9430,10 +9399,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44701</v>
+        <v>44587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9445,8 +9414,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9489,7 +9463,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9503,10 +9477,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44698</v>
+        <v>46001</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9518,8 +9492,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9562,7 +9541,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9576,10 +9555,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44497</v>
+        <v>45299</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9592,7 +9571,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9635,7 +9614,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9649,10 +9628,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46163</v>
+        <v>45196</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9664,13 +9643,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9713,7 +9687,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9727,10 +9701,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45224</v>
+        <v>46008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9742,8 +9716,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9786,7 +9765,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9800,10 +9779,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45145</v>
+        <v>44701</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9816,7 +9795,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9859,7 +9838,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9873,10 +9852,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46163</v>
+        <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9888,13 +9867,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9937,7 +9911,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9951,10 +9925,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46001</v>
+        <v>46182</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9966,13 +9940,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10015,7 +9984,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10025,14 +9994,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45408</v>
+        <v>46189</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10044,13 +10013,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10093,7 +10057,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10107,10 +10071,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45356</v>
+        <v>44497</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10123,7 +10087,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10166,7 +10130,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10180,10 +10144,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45149</v>
+        <v>45224</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10196,7 +10160,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10239,7 +10203,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10249,14 +10213,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45149</v>
+        <v>45145</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10269,7 +10233,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10312,7 +10276,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10326,10 +10290,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46168</v>
+        <v>46059</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10342,7 +10306,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10385,7 +10349,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10399,10 +10363,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46008</v>
+        <v>46059</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10414,13 +10378,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10463,7 +10422,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10477,10 +10436,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46168</v>
+        <v>45719</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10493,7 +10452,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10536,7 +10495,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10550,10 +10509,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46168</v>
+        <v>45408</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10565,8 +10524,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10609,7 +10573,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10623,10 +10587,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45281</v>
+        <v>45356</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10639,7 +10603,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10682,7 +10646,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10696,10 +10660,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44895</v>
+        <v>45149</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10712,7 +10676,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10755,7 +10719,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10765,14 +10729,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44844</v>
+        <v>45149</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10785,7 +10749,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10828,7 +10792,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10838,14 +10802,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44832</v>
+        <v>46072</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10858,7 +10822,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10901,7 +10865,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10915,10 +10879,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45469</v>
+        <v>45281</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10931,7 +10895,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10974,7 +10938,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10984,14 +10948,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45469</v>
+        <v>46087</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11004,7 +10968,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11047,7 +11011,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11061,10 +11025,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45313</v>
+        <v>44895</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11077,7 +11041,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11120,7 +11084,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11130,14 +11094,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44687</v>
+        <v>44844</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11150,7 +11114,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11193,7 +11157,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11203,14 +11167,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45043</v>
+        <v>44832</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11223,7 +11187,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11266,7 +11230,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 5897-2026</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11280,10 +11244,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46052</v>
+        <v>46093</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11296,7 +11260,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11339,7 +11303,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11353,10 +11317,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45215</v>
+        <v>46093</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11368,8 +11332,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11412,7 +11381,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11426,10 +11395,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46059</v>
+        <v>46246</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11441,8 +11410,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11485,7 +11459,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11499,10 +11473,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44957</v>
+        <v>45469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11515,7 +11489,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11558,7 +11532,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11572,10 +11546,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46059</v>
+        <v>45469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11588,7 +11562,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11631,7 +11605,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11645,10 +11619,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45719</v>
+        <v>45313</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11661,7 +11635,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11704,7 +11678,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11718,10 +11692,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45022</v>
+        <v>46100</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11733,8 +11707,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11777,7 +11756,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11791,10 +11770,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46182</v>
+        <v>46101</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11807,7 +11786,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11850,7 +11829,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11864,10 +11843,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46072</v>
+        <v>46101</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11880,7 +11859,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11923,7 +11902,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11937,10 +11916,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44496</v>
+        <v>46246</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11952,8 +11931,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11996,7 +11980,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12010,10 +11994,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45096</v>
+        <v>46106</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12025,8 +12009,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12069,7 +12058,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12083,10 +12072,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45110</v>
+        <v>46106</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12098,8 +12087,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12142,7 +12136,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12156,10 +12150,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45110</v>
+        <v>46106</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12171,8 +12165,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12215,7 +12214,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12225,14 +12224,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12245,7 +12244,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12288,7 +12287,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12298,14 +12297,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46189</v>
+        <v>46111</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12318,7 +12317,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12361,7 +12360,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12375,10 +12374,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46093</v>
+        <v>46111</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12391,7 +12390,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12434,7 +12433,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12448,10 +12447,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46093</v>
+        <v>46111</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12463,13 +12462,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12512,7 +12506,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12522,14 +12516,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46100</v>
+        <v>44687</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12541,13 +12535,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12590,7 +12579,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12604,10 +12593,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46101</v>
+        <v>45043</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12620,7 +12609,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5.9</v>
+        <v>2.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12663,7 +12652,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12677,10 +12666,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12693,7 +12682,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12736,7 +12725,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12750,10 +12739,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12771,7 +12760,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12814,7 +12803,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12828,10 +12817,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46106</v>
+        <v>46247</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12849,7 +12838,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12892,7 +12881,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12906,10 +12895,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12921,13 +12910,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12970,7 +12954,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12984,10 +12968,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46108</v>
+        <v>45215</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13000,7 +12984,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13043,7 +13027,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13057,10 +13041,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45140</v>
+        <v>45539</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13072,8 +13056,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13116,7 +13105,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13130,10 +13119,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45314</v>
+        <v>44957</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13146,7 +13135,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13189,7 +13178,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13203,10 +13192,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46111</v>
+        <v>46129</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13218,8 +13207,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13276,10 +13270,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46111</v>
+        <v>45022</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13292,7 +13286,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13335,7 +13329,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13349,10 +13343,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44995</v>
+        <v>44496</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13365,7 +13359,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>13.5</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13408,7 +13402,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13422,10 +13416,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46111</v>
+        <v>45096</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13438,7 +13432,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13481,7 +13475,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13495,10 +13489,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46111</v>
+        <v>45110</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13554,7 +13548,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13568,10 +13562,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46113</v>
+        <v>45110</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13583,13 +13577,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13632,7 +13621,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13646,10 +13635,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46119</v>
+        <v>46258</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13662,7 +13651,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13705,7 +13694,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13719,10 +13708,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45370</v>
+        <v>45140</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13735,7 +13724,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13778,7 +13767,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13792,10 +13781,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45539</v>
+        <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13809,11 +13798,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>8.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13856,7 +13845,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13870,10 +13859,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46129</v>
+        <v>45314</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13885,13 +13874,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13934,7 +13918,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13948,10 +13932,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44743</v>
+        <v>44995</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13964,7 +13948,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14007,7 +13991,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14021,10 +14005,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46246</v>
+        <v>46168</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14036,13 +14020,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14085,7 +14064,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14099,10 +14078,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45099</v>
+        <v>45370</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14115,7 +14094,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14158,7 +14137,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14172,10 +14151,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44812</v>
+        <v>44743</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14188,7 +14167,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14231,7 +14210,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14245,10 +14224,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46246</v>
+        <v>45099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14260,13 +14239,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14309,7 +14283,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14323,10 +14297,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45621</v>
+        <v>44812</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14339,7 +14313,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14382,7 +14356,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14396,10 +14370,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45091</v>
+        <v>45621</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14412,7 +14386,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>21.6</v>
+        <v>4.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14455,7 +14429,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14469,10 +14443,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44894</v>
+        <v>45091</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14485,7 +14459,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>21.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14528,7 +14502,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14542,10 +14516,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46247</v>
+        <v>44894</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14557,13 +14531,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14623,7 +14592,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14696,7 +14665,7 @@
         <v>45288</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14769,7 +14738,7 @@
         <v>45224</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14825,7 +14794,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14839,10 +14808,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45448</v>
+        <v>46280</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14854,13 +14823,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14903,7 +14867,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14917,10 +14881,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45175</v>
+        <v>45448</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14934,11 +14898,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14981,7 +14945,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14995,10 +14959,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45110</v>
+        <v>45175</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15010,8 +14974,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15054,7 +15023,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15068,10 +15037,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46258</v>
+        <v>45110</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15127,7 +15096,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15141,10 +15110,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46203</v>
+        <v>45514</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15156,13 +15125,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15205,7 +15169,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15219,10 +15183,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45514</v>
+        <v>45156</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15235,7 +15199,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15278,7 +15242,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15292,10 +15256,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45156</v>
+        <v>44995</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15308,7 +15272,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15351,7 +15315,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15365,10 +15329,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44995</v>
+        <v>44642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15381,7 +15345,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15424,7 +15388,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15434,14 +15398,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44642</v>
+        <v>45109</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15454,7 +15418,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15497,7 +15461,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15507,14 +15471,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46168</v>
+        <v>45313</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15527,7 +15491,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.6</v>
+        <v>11.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15570,7 +15534,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15580,14 +15544,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45109</v>
+        <v>45288</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15600,7 +15564,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15643,7 +15607,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15653,14 +15617,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45313</v>
+        <v>46281</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15673,7 +15637,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>11.7</v>
+        <v>2.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15716,7 +15680,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 38149-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15730,10 +15694,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45288</v>
+        <v>46281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15746,7 +15710,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15806,7 +15770,7 @@
         <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15879,7 +15843,7 @@
         <v>45635</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15952,7 +15916,7 @@
         <v>45595</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16008,7 +15972,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16018,14 +15982,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46280</v>
+        <v>45800</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16038,7 +16002,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16081,7 +16045,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 38149-2026</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16091,14 +16055,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46281</v>
+        <v>44946</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16111,7 +16075,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16154,7 +16118,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16164,14 +16128,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45800</v>
+        <v>45817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16184,7 +16148,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16227,7 +16191,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 38146-2026</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16241,10 +16205,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46281</v>
+        <v>45820</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16256,8 +16220,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16300,7 +16269,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16310,14 +16279,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44946</v>
+        <v>45839</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16330,7 +16299,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16373,7 +16342,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16387,10 +16356,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45817</v>
+        <v>45839</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16403,7 +16372,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16446,7 +16415,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16460,10 +16429,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45820</v>
+        <v>44953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16475,13 +16444,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16524,7 +16488,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16538,10 +16502,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16554,7 +16518,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16597,7 +16561,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16607,14 +16571,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45839</v>
+        <v>45258</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16627,7 +16591,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16670,7 +16634,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16684,10 +16648,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44953</v>
+        <v>45776</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16700,7 +16664,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16743,7 +16707,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16757,10 +16721,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45840</v>
+        <v>44687</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16772,8 +16736,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16816,24 +16785,22 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>S 1236-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v/>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45258</v>
+        <v>44623</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16846,7 +16813,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16886,27 +16853,27 @@
       </c>
       <c r="V212" s="2" t="inlineStr"/>
     </row>
-    <row r="213" ht="15" customHeight="1">
+    <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>S 839-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45776</v>
+        <v>45372</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16919,7 +16886,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>19.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16958,228 +16925,6 @@
         <v>0</v>
       </c>
       <c r="V213" s="2" t="inlineStr"/>
-    </row>
-    <row r="214" ht="15" customHeight="1">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>A 18704-2022</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D214" s="1" t="n">
-        <v>44687</v>
-      </c>
-      <c r="E214" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J214" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" t="n">
-        <v>0</v>
-      </c>
-      <c r="L214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M214" t="n">
-        <v>0</v>
-      </c>
-      <c r="N214" t="n">
-        <v>0</v>
-      </c>
-      <c r="O214" t="n">
-        <v>0</v>
-      </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0</v>
-      </c>
-      <c r="S214" t="n">
-        <v>0</v>
-      </c>
-      <c r="T214" t="n">
-        <v>0</v>
-      </c>
-      <c r="U214" t="n">
-        <v>0</v>
-      </c>
-      <c r="V214" s="2" t="inlineStr"/>
-    </row>
-    <row r="215" ht="15" customHeight="1">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>S 1236-2022</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v/>
-      </c>
-      <c r="D215" s="1" t="n">
-        <v>44623</v>
-      </c>
-      <c r="E215" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I215" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J215" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" t="n">
-        <v>0</v>
-      </c>
-      <c r="L215" t="n">
-        <v>0</v>
-      </c>
-      <c r="M215" t="n">
-        <v>0</v>
-      </c>
-      <c r="N215" t="n">
-        <v>0</v>
-      </c>
-      <c r="O215" t="n">
-        <v>0</v>
-      </c>
-      <c r="P215" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0</v>
-      </c>
-      <c r="S215" t="n">
-        <v>0</v>
-      </c>
-      <c r="T215" t="n">
-        <v>0</v>
-      </c>
-      <c r="U215" t="n">
-        <v>0</v>
-      </c>
-      <c r="V215" s="2" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>S 839-2024</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D216" s="1" t="n">
-        <v>45372</v>
-      </c>
-      <c r="E216" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I216" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J216" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" t="n">
-        <v>0</v>
-      </c>
-      <c r="L216" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" t="n">
-        <v>0</v>
-      </c>
-      <c r="N216" t="n">
-        <v>0</v>
-      </c>
-      <c r="O216" t="n">
-        <v>0</v>
-      </c>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" t="n">
-        <v>0</v>
-      </c>
-      <c r="T216" t="n">
-        <v>0</v>
-      </c>
-      <c r="U216" t="n">
-        <v>0</v>
-      </c>
-      <c r="V216" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE213"/>
+  <dimension ref="A1:AE216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>45110</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 19729-2026</t>
+          <t>A 9277-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46135</v>
+        <v>44980</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1738,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
@@ -1746,779 +1746,779 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 52041-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45223</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 36670-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Almrostöra</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 20063-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45772</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skinntagging</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 19729-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 23455-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I18" t="n">
         <v>1.1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 55928-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 31736-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9277-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44980</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 31736-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Dvärghäxört</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 52041-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45223</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 36670-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Almrostöra</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 20063-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45772</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Skinntagging</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 74438-2021</t>
+          <t>A 35607-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44560</v>
+        <v>44799</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 35607-2022</t>
+          <t>A 74438-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44799</v>
+        <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2795,7 +2795,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44467</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44728</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4409-2022</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44589</v>
+        <v>45699</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,8 +3620,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3664,7 +3669,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38210-2022</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3678,10 +3683,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44812</v>
+        <v>45595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3694,7 +3699,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3737,7 +3742,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3751,10 +3756,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44530</v>
+        <v>45635</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3767,7 +3772,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3810,7 +3815,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 4409-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3824,10 +3829,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44818</v>
+        <v>44589</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3840,7 +3845,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3883,7 +3888,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 38210-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3897,10 +3902,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45469</v>
+        <v>44812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3913,7 +3918,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3956,7 +3961,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3970,10 +3975,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45420</v>
+        <v>44990</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3985,13 +3990,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45435</v>
+        <v>44530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4107,7 +4107,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45554</v>
+        <v>45098</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,8 +4136,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4180,7 +4185,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4194,10 +4199,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45110</v>
+        <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4210,7 +4215,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4253,7 +4258,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4263,14 +4268,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44908</v>
+        <v>44832</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4283,7 +4288,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4326,7 +4331,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4340,10 +4345,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45113</v>
+        <v>45091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4356,7 +4361,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4399,7 +4404,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4413,10 +4418,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45642</v>
+        <v>45667</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,8 +4433,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4472,7 +4482,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4486,10 +4496,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44978</v>
+        <v>45272</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4502,7 +4512,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4545,7 +4555,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4559,10 +4569,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44937</v>
+        <v>45335</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4575,7 +4585,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4618,7 +4628,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4632,10 +4642,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45091</v>
+        <v>45288</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4648,7 +4658,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4691,7 +4701,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4705,10 +4715,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45763</v>
+        <v>45398</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,8 +4730,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4764,7 +4779,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4778,10 +4793,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45180</v>
+        <v>44856</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4794,7 +4809,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4837,7 +4852,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4851,10 +4866,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45309</v>
+        <v>45110</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4867,7 +4882,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4910,7 +4925,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4924,10 +4939,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45699</v>
+        <v>45043</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,13 +4954,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4988,7 +4998,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5002,10 +5012,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45462</v>
+        <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5018,7 +5028,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5061,7 +5071,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45398</v>
+        <v>45492</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5090,13 +5100,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5139,7 +5144,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5153,10 +5158,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44895</v>
+        <v>44860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5169,7 +5174,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5212,7 +5217,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5226,10 +5231,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44887</v>
+        <v>44908</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5242,7 +5247,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5285,7 +5290,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5299,10 +5304,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44887</v>
+        <v>45824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5315,7 +5320,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5358,7 +5363,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5372,10 +5377,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45687</v>
+        <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5388,7 +5393,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5431,7 +5436,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5445,10 +5450,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45111</v>
+        <v>45110</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5504,7 +5509,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5518,10 +5523,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45272</v>
+        <v>45149</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5534,7 +5539,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5577,7 +5582,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5587,14 +5592,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44973</v>
+        <v>45149</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5607,7 +5612,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.8</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5650,7 +5655,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45469</v>
+        <v>45288</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5680,7 +5685,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5723,7 +5728,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5737,10 +5742,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45385</v>
+        <v>45874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5753,7 +5758,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5796,7 +5801,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5810,10 +5815,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45492</v>
+        <v>45890</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5825,8 +5830,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5869,7 +5879,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5879,14 +5889,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45667</v>
+        <v>45109</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5898,13 +5908,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5947,7 +5952,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5961,10 +5966,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45299</v>
+        <v>45889</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5976,8 +5981,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6020,7 +6030,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6034,10 +6044,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45281</v>
+        <v>45889</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6049,8 +6059,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6093,7 +6108,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6107,10 +6122,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6128,7 +6143,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6171,7 +6186,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6185,10 +6200,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45889</v>
+        <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6200,13 +6215,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6249,7 +6259,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6263,10 +6273,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45890</v>
+        <v>45110</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6278,13 +6288,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6327,7 +6332,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6341,10 +6346,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45890</v>
+        <v>44496</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6356,13 +6361,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44615</v>
+        <v>45111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45883</v>
+        <v>45469</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6551,7 +6551,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45763</v>
+        <v>44895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6624,7 +6624,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45874</v>
+        <v>45800</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6697,7 +6697,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45824</v>
+        <v>45469</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6770,7 +6770,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45800</v>
+        <v>45309</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6843,7 +6843,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44970</v>
+        <v>45492</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6916,7 +6916,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6930,10 +6930,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44856</v>
+        <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6945,8 +6945,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6989,7 +6994,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7003,10 +7008,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44860</v>
+        <v>45096</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7024,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7062,7 +7067,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7076,10 +7081,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45918</v>
+        <v>45086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7091,13 +7096,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7140,7 +7140,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45091</v>
+        <v>45924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7167,6 +7167,11 @@
       <c r="G82" t="inlineStr">
         <is>
           <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7213,7 +7218,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7230,7 +7235,7 @@
         <v>45924</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7248,7 +7253,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7308,7 +7313,7 @@
         <v>45924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7369,7 +7374,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7383,10 +7388,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45335</v>
+        <v>45924</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7398,8 +7403,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7442,7 +7452,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7456,10 +7466,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45924</v>
+        <v>44587</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7473,11 +7483,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7520,7 +7530,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7534,10 +7544,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45924</v>
+        <v>45175</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7551,11 +7561,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7598,7 +7608,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7612,10 +7622,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45196</v>
+        <v>45929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7628,7 +7638,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7671,7 +7681,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7685,10 +7695,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45929</v>
+        <v>45022</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7701,7 +7711,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7744,7 +7754,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7758,10 +7768,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45932</v>
+        <v>45462</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7774,7 +7784,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7817,7 +7827,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7831,10 +7841,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45713</v>
+        <v>45469</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7847,7 +7857,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7890,7 +7900,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7904,10 +7914,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44827</v>
+        <v>45469</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7920,7 +7930,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7963,7 +7973,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7977,10 +7987,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45492</v>
+        <v>45932</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7993,7 +8003,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8036,7 +8046,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8050,10 +8060,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45945</v>
+        <v>44937</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8065,13 +8075,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8114,7 +8119,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8128,10 +8133,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45098</v>
+        <v>45408</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8149,7 +8154,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8192,7 +8197,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8206,10 +8211,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44990</v>
+        <v>45945</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8221,8 +8226,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8265,7 +8275,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8279,10 +8289,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45621</v>
+        <v>45817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8295,7 +8305,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8338,7 +8348,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8352,10 +8362,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45958</v>
+        <v>44973</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8368,7 +8378,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8411,7 +8421,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8425,10 +8435,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45628</v>
+        <v>45713</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8441,7 +8451,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8484,7 +8494,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8498,10 +8508,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45960</v>
+        <v>45763</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8513,13 +8523,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8562,7 +8567,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8576,10 +8581,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46163</v>
+        <v>45196</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8591,13 +8596,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8640,7 +8640,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45086</v>
+        <v>45554</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8713,7 +8713,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8723,14 +8723,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46163</v>
+        <v>44946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8742,13 +8742,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8791,7 +8786,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8805,10 +8800,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45758</v>
+        <v>44844</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8820,13 +8815,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8869,7 +8859,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8883,10 +8873,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45758</v>
+        <v>45958</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8898,13 +8888,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8947,7 +8932,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8961,10 +8946,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44937</v>
+        <v>45091</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8977,7 +8962,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9020,7 +9005,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9034,10 +9019,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>44615</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9050,7 +9035,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9093,7 +9078,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9107,10 +9092,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45713</v>
+        <v>45960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9122,8 +9107,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9166,7 +9156,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9180,10 +9170,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46168</v>
+        <v>45820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9195,8 +9185,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9239,7 +9234,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9253,10 +9248,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46168</v>
+        <v>44894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9269,7 +9264,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9312,7 +9307,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9326,10 +9321,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46168</v>
+        <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9342,7 +9337,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9385,7 +9380,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9399,10 +9394,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44587</v>
+        <v>45974</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9414,13 +9409,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9463,7 +9453,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9477,10 +9467,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46001</v>
+        <v>45420</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9498,7 +9488,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9541,7 +9531,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9555,10 +9545,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45299</v>
+        <v>45099</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9571,7 +9561,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9614,7 +9604,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9628,10 +9618,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45196</v>
+        <v>44497</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9644,7 +9634,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9687,7 +9677,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9701,10 +9691,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46008</v>
+        <v>44957</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9716,13 +9706,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9765,7 +9750,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9779,10 +9764,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44701</v>
+        <v>45642</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9795,7 +9780,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9838,7 +9823,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9852,10 +9837,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44698</v>
+        <v>44701</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9868,7 +9853,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9911,7 +9896,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9925,10 +9910,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46182</v>
+        <v>44970</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9941,7 +9926,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9984,7 +9969,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9994,14 +9979,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46189</v>
+        <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10014,7 +9999,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10057,7 +10042,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10071,10 +10056,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44497</v>
+        <v>45514</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10087,7 +10072,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10130,7 +10115,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10144,10 +10129,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45224</v>
+        <v>45113</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10203,7 +10188,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10217,10 +10202,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45145</v>
+        <v>46001</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10230,6 +10215,11 @@
       <c r="G123" t="inlineStr">
         <is>
           <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -10276,7 +10266,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10290,10 +10280,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46059</v>
+        <v>45299</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10306,7 +10296,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>8.4</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10349,7 +10339,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10363,10 +10353,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46059</v>
+        <v>45370</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10379,7 +10369,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10422,7 +10412,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10436,10 +10426,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45719</v>
+        <v>46008</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10451,8 +10441,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10495,7 +10490,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10509,10 +10504,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45408</v>
+        <v>45839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10524,13 +10519,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10573,7 +10563,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10587,10 +10577,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45356</v>
+        <v>45839</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10646,7 +10636,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10660,10 +10650,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45149</v>
+        <v>45313</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10676,7 +10666,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10719,7 +10709,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10729,14 +10719,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45149</v>
+        <v>44953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10749,7 +10739,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10792,7 +10782,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10806,10 +10796,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46072</v>
+        <v>45840</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10822,7 +10812,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10865,7 +10855,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10879,10 +10869,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45281</v>
+        <v>45448</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10894,8 +10884,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10938,7 +10933,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10952,10 +10947,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46087</v>
+        <v>44687</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10968,7 +10963,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11011,7 +11006,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11025,10 +11020,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44895</v>
+        <v>45196</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11041,7 +11036,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11084,7 +11079,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11098,10 +11093,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44844</v>
+        <v>44827</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11114,7 +11109,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11157,7 +11152,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11167,14 +11162,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44832</v>
+        <v>45314</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11187,7 +11182,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11230,7 +11225,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11244,10 +11239,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46093</v>
+        <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11260,7 +11255,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11303,7 +11298,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11317,10 +11312,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46093</v>
+        <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11332,13 +11327,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11381,7 +11371,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11395,10 +11385,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46246</v>
+        <v>45719</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11410,13 +11400,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11459,7 +11444,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11473,10 +11458,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45469</v>
+        <v>45687</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11489,7 +11474,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11532,7 +11517,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 38149-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11546,10 +11531,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45469</v>
+        <v>46281</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11562,7 +11547,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11605,7 +11590,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11619,10 +11604,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45313</v>
+        <v>46072</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11678,7 +11663,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11692,10 +11677,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46100</v>
+        <v>44909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11707,13 +11692,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11756,7 +11736,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11770,10 +11750,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46101</v>
+        <v>46246</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11785,8 +11765,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11829,7 +11814,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11843,10 +11828,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46101</v>
+        <v>45385</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11859,7 +11844,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11902,7 +11887,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11916,10 +11901,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46246</v>
+        <v>44995</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11931,13 +11916,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11980,7 +11960,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11994,10 +11974,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46106</v>
+        <v>44887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12007,11 +11987,6 @@
       <c r="G147" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -12058,7 +12033,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 39335-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12072,10 +12047,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46106</v>
+        <v>46288</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12087,13 +12062,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12136,7 +12106,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 39263-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12150,10 +12120,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46106</v>
+        <v>46288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12171,7 +12141,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12214,7 +12184,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 39265-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12228,10 +12198,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46108</v>
+        <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12243,8 +12213,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12287,7 +12262,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12301,10 +12276,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46111</v>
+        <v>46281</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12317,7 +12292,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12360,7 +12335,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12374,10 +12349,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46111</v>
+        <v>46246</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12389,8 +12364,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12433,7 +12413,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12447,10 +12427,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46111</v>
+        <v>45215</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12463,7 +12443,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12506,7 +12486,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12520,10 +12500,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44687</v>
+        <v>46087</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12536,7 +12516,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12579,7 +12559,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12593,10 +12573,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45043</v>
+        <v>45281</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12609,7 +12589,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12652,7 +12632,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12666,10 +12646,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46111</v>
+        <v>44812</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12682,7 +12662,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12725,7 +12705,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12739,10 +12719,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46113</v>
+        <v>45140</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12754,13 +12734,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12803,7 +12778,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12817,10 +12792,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46247</v>
+        <v>46093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12832,13 +12807,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12881,7 +12851,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12895,10 +12865,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46119</v>
+        <v>46093</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12910,8 +12880,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12954,7 +12929,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12968,10 +12943,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45215</v>
+        <v>45776</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12984,7 +12959,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13027,7 +13002,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13041,10 +13016,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45539</v>
+        <v>44995</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13056,13 +13031,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13105,7 +13075,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13119,10 +13089,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44957</v>
+        <v>46101</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13135,7 +13105,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13178,7 +13148,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13192,10 +13162,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46129</v>
+        <v>45224</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13207,13 +13177,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13256,7 +13221,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13270,10 +13235,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45022</v>
+        <v>46101</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13286,7 +13251,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13329,7 +13294,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13343,10 +13308,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44496</v>
+        <v>46100</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13358,8 +13323,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13402,7 +13372,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13416,10 +13386,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45096</v>
+        <v>45281</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13432,7 +13402,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13475,7 +13445,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13489,10 +13459,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45110</v>
+        <v>44687</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13504,8 +13474,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13548,7 +13523,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13558,14 +13533,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45110</v>
+        <v>45258</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13578,7 +13553,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13621,7 +13596,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13635,10 +13610,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46258</v>
+        <v>46106</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13650,8 +13625,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13694,7 +13674,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13708,10 +13688,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45140</v>
+        <v>44937</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13724,7 +13704,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13767,7 +13747,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13781,10 +13761,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46203</v>
+        <v>46106</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13798,11 +13778,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13845,7 +13825,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13859,10 +13839,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45314</v>
+        <v>46106</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13874,8 +13854,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13918,7 +13903,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13932,10 +13917,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44995</v>
+        <v>46108</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13948,7 +13933,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13991,7 +13976,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14005,10 +13990,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46168</v>
+        <v>46111</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14021,7 +14006,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14064,7 +14049,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14078,10 +14063,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45370</v>
+        <v>46111</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14094,7 +14079,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14137,7 +14122,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14151,10 +14136,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44743</v>
+        <v>46111</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14167,7 +14152,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14210,7 +14195,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14224,10 +14209,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45099</v>
+        <v>46111</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14240,7 +14225,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14283,7 +14268,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14297,10 +14282,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44812</v>
+        <v>46113</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14312,8 +14297,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14356,7 +14346,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14370,10 +14360,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45621</v>
+        <v>45145</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14386,7 +14376,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14429,7 +14419,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14443,10 +14433,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45091</v>
+        <v>45435</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14459,7 +14449,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>21.6</v>
+        <v>0.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14502,7 +14492,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14516,10 +14506,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44894</v>
+        <v>46119</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14575,7 +14565,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14589,10 +14579,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44909</v>
+        <v>45539</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14604,8 +14594,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14648,7 +14643,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14662,10 +14657,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45288</v>
+        <v>44642</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14678,7 +14673,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14721,7 +14716,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14735,10 +14730,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45224</v>
+        <v>46129</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14750,8 +14745,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14794,7 +14794,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14808,10 +14808,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46280</v>
+        <v>45091</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>21.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14867,7 +14867,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14881,10 +14881,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45448</v>
+        <v>45224</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14896,13 +14896,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14945,7 +14940,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14959,10 +14954,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45175</v>
+        <v>45156</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14974,13 +14969,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15023,7 +15013,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15037,10 +15027,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45110</v>
+        <v>45883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15053,7 +15043,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15096,7 +15086,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15110,10 +15100,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45514</v>
+        <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15126,7 +15116,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15169,7 +15159,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15183,10 +15173,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45156</v>
+        <v>45621</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15199,7 +15189,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15242,7 +15232,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15256,10 +15246,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44995</v>
+        <v>45763</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15272,7 +15262,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15315,7 +15305,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15329,10 +15319,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44642</v>
+        <v>45299</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15345,7 +15335,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15388,7 +15378,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15398,14 +15388,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45109</v>
+        <v>45356</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15418,7 +15408,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15461,7 +15451,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15471,14 +15461,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45313</v>
+        <v>45800</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15491,7 +15481,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>11.7</v>
+        <v>2.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15534,7 +15524,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15548,10 +15538,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45288</v>
+        <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15564,7 +15554,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15607,7 +15597,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 38146-2026</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15621,10 +15611,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46281</v>
+        <v>44743</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15637,7 +15627,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15680,7 +15670,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38149-2026</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15694,10 +15684,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46281</v>
+        <v>45628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15710,7 +15700,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15753,7 +15743,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15767,10 +15757,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45639</v>
+        <v>44978</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15783,7 +15773,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15826,7 +15816,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15840,10 +15830,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45635</v>
+        <v>45758</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15855,8 +15845,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>9.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15899,7 +15894,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15913,10 +15908,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45595</v>
+        <v>45758</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15928,8 +15923,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15972,7 +15972,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15986,10 +15986,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45800</v>
+        <v>45313</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>11.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16045,7 +16045,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16055,14 +16055,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44946</v>
+        <v>45639</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16118,7 +16118,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16132,10 +16132,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45817</v>
+        <v>46163</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16147,8 +16147,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16191,7 +16196,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16205,10 +16210,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45820</v>
+        <v>46163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16226,7 +16231,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16269,7 +16274,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16283,10 +16288,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45839</v>
+        <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16299,7 +16304,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16342,7 +16347,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16356,10 +16361,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45839</v>
+        <v>46168</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16372,7 +16377,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16415,7 +16420,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16429,10 +16434,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44953</v>
+        <v>46168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16445,7 +16450,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16488,7 +16493,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16502,10 +16507,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45840</v>
+        <v>46182</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16518,7 +16523,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16561,7 +16566,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16571,14 +16576,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45258</v>
+        <v>46189</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16591,7 +16596,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16634,7 +16639,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16648,10 +16653,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45776</v>
+        <v>46247</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16663,8 +16668,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16707,7 +16717,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16721,10 +16731,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44687</v>
+        <v>46258</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16736,13 +16746,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16785,146 +16790,370 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
+          <t>A 29478-2026</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E212" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213" ht="15" customHeight="1">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>A 24144-2026</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="E213" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214" ht="15" customHeight="1">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>A 38007-2026</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E214" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215" ht="15" customHeight="1">
+      <c r="A215" t="inlineStr">
+        <is>
           <t>S 1236-2022</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C212" t="n">
+      <c r="C215" t="n">
         <v/>
       </c>
-      <c r="D212" s="1" t="n">
+      <c r="D215" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="E212" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I212" t="n">
+      <c r="E215" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
         <v>0.1</v>
       </c>
-      <c r="J212" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>0</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="n">
-        <v>0</v>
-      </c>
-      <c r="T212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="n">
-        <v>0</v>
-      </c>
-      <c r="V212" s="2" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0</v>
+      </c>
+      <c r="V215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>S 839-2024</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D213" s="1" t="n">
+      <c r="D216" s="1" t="n">
         <v>45372</v>
       </c>
-      <c r="E213" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I213" t="n">
+      <c r="E216" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
         <v>19.6</v>
       </c>
-      <c r="J213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" t="n">
-        <v>0</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="n">
-        <v>0</v>
-      </c>
-      <c r="T213" t="n">
-        <v>0</v>
-      </c>
-      <c r="U213" t="n">
-        <v>0</v>
-      </c>
-      <c r="V213" s="2" t="inlineStr"/>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>45110</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 9277-2023</t>
+          <t>A 19729-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44980</v>
+        <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1738,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
@@ -1746,31 +1746,31 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         <v>45973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52041-2023</t>
+          <t>A 9277-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,14 +1897,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45223</v>
+        <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,16 +1917,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1957,568 +1957,568 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 23455-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 52041-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45223</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 31736-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 36670-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>2.3</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Almrostöra</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 20063-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45772</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>3.4</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Skinntagging</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 19729-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 23455-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 31736-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>44799</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44467</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44728</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 4409-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45699</v>
+        <v>44589</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,13 +3620,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3669,7 +3664,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 38210-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3683,10 +3678,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45595</v>
+        <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3699,7 +3694,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3742,7 +3737,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3756,10 +3751,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45635</v>
+        <v>44530</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3772,7 +3767,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>9.199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3815,7 +3810,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4409-2022</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3829,10 +3824,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44589</v>
+        <v>44818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3845,7 +3840,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3888,7 +3883,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38210-2022</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3902,10 +3897,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44812</v>
+        <v>45469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3918,7 +3913,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3961,7 +3956,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3975,10 +3970,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44990</v>
+        <v>45435</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3991,7 +3986,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4034,7 +4029,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44530</v>
+        <v>45763</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4064,7 +4059,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4107,7 +4102,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4121,10 +4116,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45098</v>
+        <v>45180</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,13 +4131,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4185,7 +4175,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4199,10 +4189,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44818</v>
+        <v>45554</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4215,7 +4205,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4258,7 +4248,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4268,14 +4258,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44832</v>
+        <v>45420</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4287,8 +4277,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4331,7 +4326,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4345,10 +4340,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45091</v>
+        <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4404,7 +4399,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4418,10 +4413,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45667</v>
+        <v>44908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4431,11 +4426,6 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4482,7 +4472,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4496,10 +4486,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45272</v>
+        <v>45113</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4512,7 +4502,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4555,7 +4545,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4569,10 +4559,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45335</v>
+        <v>45642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4585,7 +4575,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4628,7 +4618,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4642,10 +4632,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45288</v>
+        <v>44978</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4658,7 +4648,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4701,7 +4691,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4715,10 +4705,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45398</v>
+        <v>44937</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4728,11 +4718,6 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -4779,7 +4764,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4793,10 +4778,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44856</v>
+        <v>45091</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4809,7 +4794,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4852,7 +4837,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4866,10 +4851,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45110</v>
+        <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4882,7 +4867,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4925,7 +4910,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4939,10 +4924,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45043</v>
+        <v>45699</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4954,8 +4939,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4998,7 +4988,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5012,10 +5002,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45180</v>
+        <v>45462</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5028,7 +5018,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5071,7 +5061,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45492</v>
+        <v>45398</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5100,8 +5090,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5144,7 +5139,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5158,10 +5153,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44860</v>
+        <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5174,7 +5169,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5217,7 +5212,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5231,10 +5226,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44908</v>
+        <v>44887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5247,7 +5242,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5290,7 +5285,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5304,10 +5299,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45824</v>
+        <v>44887</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5320,7 +5315,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5363,7 +5358,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5377,10 +5372,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44895</v>
+        <v>45687</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5393,7 +5388,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5436,7 +5431,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5450,10 +5445,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45110</v>
+        <v>45272</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5466,7 +5461,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5509,7 +5504,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5523,10 +5518,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45149</v>
+        <v>45111</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5539,7 +5534,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5582,7 +5577,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5592,14 +5587,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45149</v>
+        <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5612,7 +5607,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5655,7 +5650,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45288</v>
+        <v>45469</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5685,7 +5680,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5728,7 +5723,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5742,10 +5737,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45874</v>
+        <v>45385</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5758,7 +5753,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5801,7 +5796,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5815,10 +5810,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45890</v>
+        <v>45492</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5830,13 +5825,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5879,7 +5869,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5889,14 +5879,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45109</v>
+        <v>45667</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5908,8 +5898,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5952,7 +5947,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5966,10 +5961,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45889</v>
+        <v>45299</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5981,13 +5976,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6030,7 +6020,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6047,7 +6037,7 @@
         <v>45889</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6065,7 +6055,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6108,7 +6098,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6122,10 +6112,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45890</v>
+        <v>45889</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6186,7 +6176,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6200,10 +6190,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45110</v>
+        <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6216,7 +6206,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6259,7 +6249,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6273,10 +6263,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45110</v>
+        <v>45890</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6288,8 +6278,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6332,7 +6327,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6346,10 +6341,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44496</v>
+        <v>45890</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6361,8 +6356,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45111</v>
+        <v>44615</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45469</v>
+        <v>45874</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6551,7 +6551,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44895</v>
+        <v>44970</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6624,7 +6624,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45800</v>
+        <v>44856</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6697,7 +6697,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45469</v>
+        <v>44860</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6770,7 +6770,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45309</v>
+        <v>45091</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6843,7 +6843,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45492</v>
+        <v>45824</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6916,7 +6916,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6930,10 +6930,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45918</v>
+        <v>45883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6945,13 +6945,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6994,7 +6989,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7008,10 +7003,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45096</v>
+        <v>45763</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7024,7 +7019,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7067,7 +7062,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7081,10 +7076,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45086</v>
+        <v>45918</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7096,8 +7091,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7140,7 +7140,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45924</v>
+        <v>45335</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7169,13 +7169,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7218,7 +7213,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7232,10 +7227,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45924</v>
+        <v>45196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7247,13 +7242,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7296,7 +7286,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7313,7 +7303,7 @@
         <v>45924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7331,7 +7321,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7374,7 +7364,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7391,7 +7381,7 @@
         <v>45924</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7409,7 +7399,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7452,7 +7442,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7466,10 +7456,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44587</v>
+        <v>45924</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7483,11 +7473,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7530,7 +7520,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7544,10 +7534,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45175</v>
+        <v>45924</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7561,11 +7551,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7625,7 +7615,7 @@
         <v>45929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7681,7 +7671,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7695,10 +7685,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45022</v>
+        <v>45932</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7711,7 +7701,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7754,7 +7744,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7768,10 +7758,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45462</v>
+        <v>45713</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7784,7 +7774,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7827,7 +7817,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7841,10 +7831,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45469</v>
+        <v>44827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7857,7 +7847,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7900,7 +7890,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7914,10 +7904,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45469</v>
+        <v>45492</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7930,7 +7920,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7973,7 +7963,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7987,10 +7977,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45932</v>
+        <v>45945</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8002,8 +7992,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8046,7 +8041,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8060,10 +8055,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44937</v>
+        <v>45098</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8075,8 +8070,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8119,7 +8119,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45408</v>
+        <v>44990</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8148,13 +8148,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8197,7 +8192,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8211,10 +8206,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45945</v>
+        <v>45800</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8226,13 +8221,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8275,7 +8265,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8289,10 +8279,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45817</v>
+        <v>45621</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8305,7 +8295,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8348,7 +8338,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8362,10 +8352,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44973</v>
+        <v>45628</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8378,7 +8368,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8421,7 +8411,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8435,10 +8425,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45713</v>
+        <v>45086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8451,7 +8441,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8494,7 +8484,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8508,10 +8498,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45763</v>
+        <v>45958</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8524,7 +8514,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8567,7 +8557,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8581,10 +8571,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45196</v>
+        <v>45960</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8596,8 +8586,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8640,7 +8635,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8654,10 +8649,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45554</v>
+        <v>45758</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8669,8 +8664,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8713,7 +8713,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8723,14 +8723,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44946</v>
+        <v>45758</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8742,8 +8742,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>7.3</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8786,7 +8791,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8800,10 +8805,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44844</v>
+        <v>44937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8859,7 +8864,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8873,10 +8878,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45958</v>
+        <v>45713</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8889,7 +8894,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8932,7 +8937,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8946,10 +8951,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45091</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8962,7 +8967,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9005,7 +9010,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9019,10 +9024,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44615</v>
+        <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9034,8 +9039,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9078,7 +9088,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9092,10 +9102,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45960</v>
+        <v>46001</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9109,11 +9119,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9156,7 +9166,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9170,10 +9180,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45820</v>
+        <v>45299</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9185,13 +9195,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9234,7 +9239,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9248,10 +9253,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44894</v>
+        <v>45196</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9264,7 +9269,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9307,7 +9312,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9321,10 +9326,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45713</v>
+        <v>46008</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9334,6 +9339,11 @@
       <c r="G111" t="inlineStr">
         <is>
           <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -9380,7 +9390,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9394,10 +9404,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45974</v>
+        <v>44701</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9410,7 +9420,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9453,7 +9463,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9467,10 +9477,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45420</v>
+        <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9482,13 +9492,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9531,7 +9536,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9545,10 +9550,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45099</v>
+        <v>46163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9560,8 +9565,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9621,7 +9631,7 @@
         <v>44497</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9677,7 +9687,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9691,10 +9701,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44957</v>
+        <v>46163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9706,8 +9716,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9750,7 +9765,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9764,10 +9779,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45642</v>
+        <v>45224</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9780,7 +9795,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9823,7 +9838,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9837,10 +9852,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44701</v>
+        <v>45145</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9853,7 +9868,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9896,7 +9911,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9910,10 +9925,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44970</v>
+        <v>45408</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9925,8 +9940,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9969,7 +9989,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9983,10 +10003,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44698</v>
+        <v>46168</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9999,7 +10019,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10042,7 +10062,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10056,10 +10076,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45514</v>
+        <v>45356</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10072,7 +10092,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10115,7 +10135,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10129,10 +10149,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45113</v>
+        <v>45149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10145,7 +10165,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10188,7 +10208,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10198,14 +10218,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46001</v>
+        <v>45149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10217,13 +10237,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10266,7 +10281,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10280,10 +10295,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45299</v>
+        <v>46059</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10296,7 +10311,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10339,7 +10354,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10353,10 +10368,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45370</v>
+        <v>46059</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10369,7 +10384,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10412,7 +10427,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10426,10 +10441,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46008</v>
+        <v>45719</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10441,13 +10456,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10490,7 +10500,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10504,10 +10514,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45839</v>
+        <v>46168</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10520,7 +10530,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10563,7 +10573,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10577,10 +10587,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45839</v>
+        <v>46168</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10593,7 +10603,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10636,7 +10646,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10650,10 +10660,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45313</v>
+        <v>45281</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10666,7 +10676,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10709,7 +10719,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10723,10 +10733,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44953</v>
+        <v>44895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10739,7 +10749,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10782,7 +10792,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10796,10 +10806,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45840</v>
+        <v>44844</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10812,7 +10822,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10855,7 +10865,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10869,10 +10879,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45448</v>
+        <v>46072</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10884,13 +10894,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10933,7 +10938,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10947,10 +10952,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44687</v>
+        <v>44832</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10963,7 +10968,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11006,7 +11011,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11020,10 +11025,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45196</v>
+        <v>45469</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11036,7 +11041,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11079,7 +11084,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11093,10 +11098,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44827</v>
+        <v>45469</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11109,7 +11114,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11152,7 +11157,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11166,10 +11171,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45314</v>
+        <v>45313</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11182,7 +11187,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11225,7 +11230,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11235,14 +11240,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46059</v>
+        <v>46087</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11255,7 +11260,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11298,7 +11303,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46059</v>
+        <v>46093</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11328,7 +11333,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11371,7 +11376,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11385,10 +11390,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45719</v>
+        <v>46093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11400,8 +11405,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11444,7 +11454,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11458,10 +11468,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45687</v>
+        <v>46100</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11471,6 +11481,11 @@
       <c r="G140" t="inlineStr">
         <is>
           <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -11517,7 +11532,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 38149-2026</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11527,14 +11542,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46281</v>
+        <v>44687</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11547,7 +11562,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11590,7 +11605,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11604,10 +11619,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46072</v>
+        <v>45043</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11620,7 +11635,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11663,7 +11678,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11677,10 +11692,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44909</v>
+        <v>46182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11693,7 +11708,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11736,7 +11751,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11750,10 +11765,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46246</v>
+        <v>46101</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11765,13 +11780,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11814,7 +11824,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11828,10 +11838,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45385</v>
+        <v>46101</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11844,7 +11854,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11887,7 +11897,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11901,10 +11911,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44995</v>
+        <v>46106</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11916,8 +11926,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11960,7 +11975,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11974,10 +11989,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44887</v>
+        <v>46106</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11989,8 +12004,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12033,7 +12053,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 39335-2026</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12043,14 +12063,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46288</v>
+        <v>46189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12063,7 +12083,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12106,7 +12126,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 39263-2026</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12120,10 +12140,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46288</v>
+        <v>46106</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12141,7 +12161,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12184,7 +12204,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39265-2026</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12198,10 +12218,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46288</v>
+        <v>46108</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12213,13 +12233,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12262,7 +12277,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 38146-2026</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12276,10 +12291,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46281</v>
+        <v>45215</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12292,7 +12307,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12335,7 +12350,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12349,10 +12364,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46246</v>
+        <v>46111</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12364,13 +12379,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12413,7 +12423,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12427,10 +12437,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45215</v>
+        <v>46111</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12443,7 +12453,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12486,7 +12496,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12496,14 +12506,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12516,7 +12526,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12559,7 +12569,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12573,10 +12583,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45281</v>
+        <v>46111</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12589,7 +12599,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12632,7 +12642,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12646,10 +12656,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44812</v>
+        <v>46113</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12661,8 +12671,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12705,7 +12720,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12719,10 +12734,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45140</v>
+        <v>44957</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12735,7 +12750,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12778,7 +12793,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12792,10 +12807,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46093</v>
+        <v>45022</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12808,7 +12823,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12851,7 +12866,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12865,10 +12880,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46093</v>
+        <v>46119</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12880,13 +12895,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12929,7 +12939,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12943,10 +12953,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45776</v>
+        <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12958,8 +12968,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13002,7 +13017,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13016,10 +13031,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44995</v>
+        <v>46129</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13031,8 +13046,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13075,7 +13095,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13089,10 +13109,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46101</v>
+        <v>44496</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13105,7 +13125,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13148,7 +13168,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13162,10 +13182,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45224</v>
+        <v>45096</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13178,7 +13198,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13221,7 +13241,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13235,10 +13255,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46101</v>
+        <v>45110</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13251,7 +13271,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13294,7 +13314,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13308,10 +13328,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46100</v>
+        <v>45110</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13323,13 +13343,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13372,7 +13387,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13386,10 +13401,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45281</v>
+        <v>45140</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13402,7 +13417,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13445,7 +13460,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13459,10 +13474,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44687</v>
+        <v>45314</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13474,13 +13489,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13523,7 +13533,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13533,14 +13543,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45258</v>
+        <v>44995</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13553,7 +13563,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13596,7 +13606,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13610,10 +13620,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46106</v>
+        <v>45370</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13625,13 +13635,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13674,7 +13679,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13688,10 +13693,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44937</v>
+        <v>44743</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13704,7 +13709,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13747,7 +13752,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13761,10 +13766,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46106</v>
+        <v>45099</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13776,13 +13781,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46106</v>
+        <v>44812</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13854,13 +13854,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13903,7 +13898,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13917,10 +13912,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46108</v>
+        <v>46258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13933,7 +13928,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13976,7 +13971,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13990,10 +13985,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46111</v>
+        <v>45621</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14006,7 +14001,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14049,7 +14044,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14063,10 +14058,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46111</v>
+        <v>45091</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14079,7 +14074,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>21.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14122,7 +14117,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14136,10 +14131,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46111</v>
+        <v>46203</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14151,8 +14146,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14195,7 +14195,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46111</v>
+        <v>44894</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14268,7 +14268,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14282,10 +14282,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46113</v>
+        <v>44909</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14297,13 +14297,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14346,7 +14341,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14360,10 +14355,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45145</v>
+        <v>46168</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14376,7 +14371,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14419,7 +14414,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14433,10 +14428,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45435</v>
+        <v>45288</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14449,7 +14444,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14492,7 +14487,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14506,10 +14501,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46119</v>
+        <v>45224</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14522,7 +14517,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14565,7 +14560,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14579,10 +14574,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45539</v>
+        <v>45448</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14600,7 +14595,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>8.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14643,7 +14638,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14657,10 +14652,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44642</v>
+        <v>45175</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14672,8 +14667,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14716,7 +14716,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14730,10 +14730,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46129</v>
+        <v>45110</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14745,13 +14745,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14794,7 +14789,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14808,10 +14803,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45091</v>
+        <v>45514</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14824,7 +14819,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>21.6</v>
+        <v>1.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14867,7 +14862,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14881,10 +14876,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45224</v>
+        <v>45156</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14897,7 +14892,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14940,7 +14935,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14954,10 +14949,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45156</v>
+        <v>44995</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14970,7 +14965,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15013,7 +15008,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15027,10 +15022,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45883</v>
+        <v>44642</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15043,7 +15038,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15086,7 +15081,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15096,14 +15091,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45621</v>
+        <v>45109</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15116,7 +15111,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15159,7 +15154,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15169,14 +15164,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45621</v>
+        <v>45313</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15189,7 +15184,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.7</v>
+        <v>11.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15232,7 +15227,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15246,10 +15241,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45763</v>
+        <v>45288</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15262,7 +15257,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15305,7 +15300,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15319,10 +15314,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45299</v>
+        <v>46280</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15335,7 +15330,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15378,7 +15373,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15392,10 +15387,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45356</v>
+        <v>45639</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15408,7 +15403,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15451,7 +15446,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15465,10 +15460,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45800</v>
+        <v>45635</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15481,7 +15476,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15524,7 +15519,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15538,10 +15533,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44887</v>
+        <v>45595</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15554,7 +15549,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15597,7 +15592,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15611,10 +15606,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44743</v>
+        <v>46281</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15627,7 +15622,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15670,7 +15665,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 38149-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15684,10 +15679,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45628</v>
+        <v>46281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15700,7 +15695,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15743,7 +15738,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15757,10 +15752,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44978</v>
+        <v>46247</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15770,6 +15765,11 @@
       <c r="G198" t="inlineStr">
         <is>
           <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I198" t="n">
@@ -15816,7 +15816,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 39263-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45758</v>
+        <v>46288</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15894,7 +15894,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 39265-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15908,10 +15908,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45758</v>
+        <v>46288</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15972,7 +15972,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15982,14 +15982,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45313</v>
+        <v>46246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16001,8 +16001,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>11.7</v>
+        <v>4.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16045,7 +16050,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 39335-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16059,10 +16064,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45639</v>
+        <v>46288</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16075,7 +16080,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16118,7 +16123,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16132,10 +16137,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46163</v>
+        <v>46246</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16153,7 +16158,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16196,7 +16201,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16206,14 +16211,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46163</v>
+        <v>45800</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16225,13 +16230,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16274,7 +16274,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16284,14 +16284,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46168</v>
+        <v>44946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16347,7 +16347,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16361,10 +16361,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46168</v>
+        <v>45817</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16420,7 +16420,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16434,10 +16434,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46168</v>
+        <v>45820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16449,8 +16449,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16493,7 +16498,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16507,10 +16512,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46182</v>
+        <v>45839</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16523,7 +16528,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16566,7 +16571,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16576,14 +16581,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46189</v>
+        <v>45839</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16596,7 +16601,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16639,7 +16644,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16653,10 +16658,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46247</v>
+        <v>44953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16668,13 +16673,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16717,7 +16717,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46258</v>
+        <v>45840</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16790,7 +16790,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16800,14 +16800,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46203</v>
+        <v>45258</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16819,13 +16819,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16868,7 +16863,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16882,10 +16877,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46168</v>
+        <v>45776</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16898,7 +16893,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16941,7 +16936,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16955,10 +16950,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46280</v>
+        <v>44687</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16970,8 +16965,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>44623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45372</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30080-2023</t>
+          <t>A 9277-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,14 +1577,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45110</v>
+        <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1621,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1637,358 +1637,358 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 19729-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 30080-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45110</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 19729-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 55928-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 9277-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44980</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>46163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52041-2023</t>
+          <t>A 20063-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2112,14 +2112,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45223</v>
+        <v>45772</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2168,357 +2168,357 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skinntagging</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 52041-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45223</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 52041-2023 artfynd.xlsx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 52041-2023 karta.png", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 52041-2023 georefererad karta.tif", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 52041-2023 FSC-klagomål.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 52041-2023 FSC-klagomål mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 52041-2023 tillsynsbegäran.docx", "A 52041-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 52041-2023 tillsynsbegäran mail.docx", "A 52041-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 31736-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>46227</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>2.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Dvärghäxört</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 31736-2026 artfynd.xlsx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 31736-2026 karta.png", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 31736-2026 georefererad karta.tif", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 31736-2026 FSC-klagomål.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 31736-2026 FSC-klagomål mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 31736-2026 tillsynsbegäran.docx", "A 31736-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 31736-2026 tillsynsbegäran mail.docx", "A 31736-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 36670-2026</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2.3</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Almrostöra</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 36670-2026 artfynd.xlsx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 36670-2026 karta.png", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 36670-2026 georefererad karta.tif", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 36670-2026 FSC-klagomål.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 36670-2026 FSC-klagomål mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 36670-2026 tillsynsbegäran.docx", "A 36670-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 36670-2026 tillsynsbegäran mail.docx", "A 36670-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 20063-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45772</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Skinntagging</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35607-2022</t>
+          <t>A 74438-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44799</v>
+        <v>44560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 74438-2021</t>
+          <t>A 35607-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44560</v>
+        <v>44799</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2795,7 +2795,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44467</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44728</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44589</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44530</v>
+        <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3810,7 +3810,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44818</v>
+        <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45469</v>
+        <v>45272</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45435</v>
+        <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45763</v>
+        <v>45398</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4058,8 +4058,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4102,7 +4107,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4116,10 +4121,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45180</v>
+        <v>44856</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4132,7 +4137,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4175,7 +4180,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4189,10 +4194,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45554</v>
+        <v>44860</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4205,7 +4210,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4248,7 +4253,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4262,10 +4267,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45420</v>
+        <v>44895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4277,13 +4282,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45110</v>
+        <v>45288</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44908</v>
+        <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45113</v>
+        <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45642</v>
+        <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44978</v>
+        <v>45824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44937</v>
+        <v>45469</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4764,7 +4764,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45091</v>
+        <v>45874</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4837,7 +4837,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45309</v>
+        <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,8 +4866,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4910,7 +4915,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4924,10 +4929,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45699</v>
+        <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4945,7 +4950,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4988,7 +4993,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5002,10 +5007,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45462</v>
+        <v>45889</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5017,8 +5022,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5061,7 +5071,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45398</v>
+        <v>45890</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5092,11 +5102,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5139,7 +5149,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5149,14 +5159,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44895</v>
+        <v>45800</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5169,7 +5179,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5212,7 +5222,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5226,10 +5236,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44887</v>
+        <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5242,7 +5252,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5285,7 +5295,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5299,10 +5309,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44887</v>
+        <v>44587</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5314,8 +5324,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5358,7 +5373,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5372,10 +5387,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45687</v>
+        <v>46059</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5388,7 +5403,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5431,7 +5446,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5445,10 +5460,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45272</v>
+        <v>46059</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5461,7 +5476,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5504,7 +5519,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5518,10 +5533,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45111</v>
+        <v>45719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5534,7 +5549,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5577,7 +5592,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5591,10 +5606,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44973</v>
+        <v>45918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5606,8 +5621,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5650,7 +5670,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5664,10 +5684,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45469</v>
+        <v>44937</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5680,7 +5700,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5723,7 +5743,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5737,10 +5757,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45385</v>
+        <v>45924</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5752,8 +5772,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5796,7 +5821,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5810,10 +5835,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45492</v>
+        <v>45924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5825,8 +5850,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5869,7 +5899,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5883,10 +5913,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45667</v>
+        <v>45924</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5900,11 +5930,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5947,7 +5977,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5961,10 +5991,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45299</v>
+        <v>45924</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5976,8 +6006,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6020,7 +6055,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6034,10 +6069,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45889</v>
+        <v>45408</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6055,7 +6090,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6098,7 +6133,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6112,10 +6147,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45889</v>
+        <v>46072</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6127,13 +6162,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6176,7 +6206,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6190,10 +6220,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45281</v>
+        <v>45929</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6206,7 +6236,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6249,7 +6279,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6263,10 +6293,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45890</v>
+        <v>44973</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6278,13 +6308,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6327,7 +6352,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6337,14 +6362,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45890</v>
+        <v>46087</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6356,13 +6381,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6405,7 +6425,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6419,10 +6439,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44615</v>
+        <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6435,7 +6455,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6478,7 +6498,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6492,10 +6512,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45874</v>
+        <v>45763</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6508,7 +6528,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6551,7 +6571,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6565,10 +6585,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44970</v>
+        <v>46093</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6581,7 +6601,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6624,7 +6644,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6638,10 +6658,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44856</v>
+        <v>46093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6653,8 +6673,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6697,7 +6722,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6711,10 +6736,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44860</v>
+        <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6727,7 +6752,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6770,7 +6795,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6784,10 +6809,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45091</v>
+        <v>46101</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6800,7 +6825,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6843,7 +6868,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6857,10 +6882,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45824</v>
+        <v>44615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6873,7 +6898,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6916,7 +6941,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6930,10 +6955,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45883</v>
+        <v>45945</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6945,8 +6970,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6989,7 +7019,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7003,10 +7033,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45763</v>
+        <v>46101</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7019,7 +7049,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7062,7 +7092,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7076,10 +7106,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45918</v>
+        <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7097,7 +7127,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7140,7 +7170,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7154,10 +7184,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45335</v>
+        <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7169,8 +7199,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7213,7 +7248,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7227,10 +7262,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45196</v>
+        <v>44894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7243,7 +7278,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7286,7 +7321,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7300,10 +7335,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45924</v>
+        <v>46106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7317,11 +7352,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7364,7 +7399,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7378,10 +7413,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45924</v>
+        <v>46106</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7395,11 +7430,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7442,7 +7477,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7456,10 +7491,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45924</v>
+        <v>46108</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7471,13 +7506,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7520,7 +7550,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7534,10 +7564,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45924</v>
+        <v>46111</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7549,13 +7579,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7598,7 +7623,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7612,10 +7637,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45929</v>
+        <v>46111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7628,7 +7653,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7671,7 +7696,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7685,10 +7710,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45932</v>
+        <v>46111</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7701,7 +7726,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7744,7 +7769,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7758,10 +7783,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45713</v>
+        <v>46111</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7774,7 +7799,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7817,7 +7842,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7831,10 +7856,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44827</v>
+        <v>45713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7847,7 +7872,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7890,7 +7915,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7904,10 +7929,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45492</v>
+        <v>46113</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7919,8 +7944,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7963,7 +7993,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7977,10 +8007,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45945</v>
+        <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7992,13 +8022,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8041,7 +8066,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8055,10 +8080,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45098</v>
+        <v>45960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8072,11 +8097,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8119,7 +8144,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8133,10 +8158,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44990</v>
+        <v>46119</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8149,7 +8174,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8192,7 +8217,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8206,10 +8231,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45800</v>
+        <v>45099</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8222,7 +8247,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8265,7 +8290,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8279,10 +8304,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45621</v>
+        <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8295,7 +8320,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8338,7 +8363,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8352,10 +8377,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45628</v>
+        <v>44957</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8368,7 +8393,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8411,7 +8436,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8425,10 +8450,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45086</v>
+        <v>45539</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8440,8 +8465,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8484,7 +8514,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8498,10 +8528,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45958</v>
+        <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8514,7 +8544,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8557,7 +8587,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8571,10 +8601,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45960</v>
+        <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8586,13 +8616,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8635,7 +8660,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8649,10 +8674,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45758</v>
+        <v>45817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8664,13 +8689,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8713,7 +8733,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8727,10 +8747,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45758</v>
+        <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8742,13 +8762,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8791,7 +8806,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8805,10 +8820,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44937</v>
+        <v>46129</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8820,8 +8835,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8864,7 +8884,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8878,10 +8898,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45713</v>
+        <v>45514</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8894,7 +8914,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8937,7 +8957,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8951,10 +8971,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45974</v>
+        <v>45113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8967,7 +8987,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9010,7 +9030,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9024,10 +9044,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44587</v>
+        <v>45883</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9039,13 +9059,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9088,7 +9103,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9102,10 +9117,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46001</v>
+        <v>45699</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9123,7 +9138,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9166,7 +9181,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9180,10 +9195,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45299</v>
+        <v>45763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9196,7 +9211,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9239,7 +9254,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9253,10 +9268,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45196</v>
+        <v>44990</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9269,7 +9284,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9312,7 +9327,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9322,14 +9337,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46008</v>
+        <v>44946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9341,13 +9356,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9390,7 +9400,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9404,10 +9414,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44701</v>
+        <v>45098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9419,8 +9429,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9463,7 +9478,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9473,14 +9488,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44698</v>
+        <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9493,7 +9508,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9536,7 +9551,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9550,10 +9565,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46163</v>
+        <v>46001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9571,7 +9586,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9614,7 +9629,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9628,10 +9643,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44497</v>
+        <v>45091</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9644,7 +9659,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9687,7 +9702,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9701,10 +9716,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46163</v>
+        <v>45800</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9716,13 +9731,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9765,7 +9775,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9779,10 +9789,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45224</v>
+        <v>45667</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9794,8 +9804,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9838,7 +9853,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9852,10 +9867,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45145</v>
+        <v>46008</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9867,8 +9882,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9911,7 +9931,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9925,10 +9945,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45408</v>
+        <v>45820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9946,7 +9966,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9989,7 +10009,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10003,10 +10023,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46168</v>
+        <v>45288</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10019,7 +10039,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10062,7 +10082,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10076,10 +10096,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45356</v>
+        <v>45110</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10092,7 +10112,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10135,7 +10155,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10149,10 +10169,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45149</v>
+        <v>45043</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10165,7 +10185,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10208,7 +10228,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10218,14 +10238,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45149</v>
+        <v>45180</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10238,7 +10258,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10281,7 +10301,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10295,10 +10315,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46059</v>
+        <v>45492</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10311,7 +10331,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10354,7 +10374,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10368,10 +10388,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46059</v>
+        <v>44908</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10384,7 +10404,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10427,7 +10447,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10441,10 +10461,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45719</v>
+        <v>45110</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10457,7 +10477,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10500,7 +10520,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10514,10 +10534,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46168</v>
+        <v>45149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10530,7 +10550,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10573,7 +10593,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10583,14 +10603,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46168</v>
+        <v>45149</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10603,7 +10623,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10646,7 +10666,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10660,10 +10680,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45281</v>
+        <v>45839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10676,7 +10696,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10719,7 +10739,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10733,10 +10753,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44895</v>
+        <v>45839</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10749,7 +10769,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10792,7 +10812,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10802,14 +10822,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44844</v>
+        <v>45109</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10822,7 +10842,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10865,7 +10885,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10879,10 +10899,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46072</v>
+        <v>44953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10895,7 +10915,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10938,7 +10958,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10948,14 +10968,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44832</v>
+        <v>45110</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10968,7 +10988,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11011,7 +11031,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11025,10 +11045,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45469</v>
+        <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11084,7 +11104,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11098,10 +11118,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45469</v>
+        <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11114,7 +11134,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11157,7 +11177,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11171,10 +11191,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45313</v>
+        <v>45111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11187,7 +11207,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11230,7 +11250,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11240,14 +11260,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46087</v>
+        <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11259,8 +11279,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11303,7 +11328,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11317,10 +11342,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46093</v>
+        <v>46163</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11332,8 +11357,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11376,7 +11406,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11390,10 +11420,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46093</v>
+        <v>46168</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11405,13 +11435,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11454,7 +11479,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11468,10 +11493,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46100</v>
+        <v>46168</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11483,13 +11508,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11532,7 +11552,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11542,14 +11562,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44687</v>
+        <v>45776</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11562,7 +11582,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11605,7 +11625,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11619,10 +11639,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45043</v>
+        <v>44687</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11634,8 +11654,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11678,7 +11703,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11688,14 +11713,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46182</v>
+        <v>45258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11708,7 +11733,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11751,7 +11776,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11765,10 +11790,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46101</v>
+        <v>46168</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11781,7 +11806,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11824,7 +11849,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11838,10 +11863,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46101</v>
+        <v>45309</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11854,7 +11879,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11897,7 +11922,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11911,10 +11936,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46106</v>
+        <v>45492</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11926,13 +11951,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11975,7 +11995,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11989,10 +12009,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46106</v>
+        <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12004,13 +12024,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12053,7 +12068,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12063,14 +12078,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46189</v>
+        <v>45175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12082,8 +12097,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12126,7 +12146,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12140,10 +12160,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46106</v>
+        <v>46182</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12155,13 +12175,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12204,7 +12219,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12218,10 +12233,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46108</v>
+        <v>45022</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12234,7 +12249,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12277,7 +12292,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12291,10 +12306,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45215</v>
+        <v>45462</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12307,7 +12322,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12350,7 +12365,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12364,10 +12379,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46111</v>
+        <v>45469</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12380,7 +12395,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12423,7 +12438,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12437,10 +12452,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46111</v>
+        <v>45469</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12453,7 +12468,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12496,7 +12511,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12506,14 +12521,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46111</v>
+        <v>46189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12526,7 +12541,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12569,7 +12584,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12583,10 +12598,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46111</v>
+        <v>45713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12599,7 +12614,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12642,7 +12657,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12656,10 +12671,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46113</v>
+        <v>45196</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12671,13 +12686,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12720,7 +12730,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12734,10 +12744,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44957</v>
+        <v>44844</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12750,7 +12760,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12793,7 +12803,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12807,10 +12817,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45022</v>
+        <v>45091</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12823,7 +12833,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12866,7 +12876,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12880,10 +12890,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46119</v>
+        <v>46258</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12896,7 +12906,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12939,7 +12949,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12953,10 +12963,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45539</v>
+        <v>45420</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12974,7 +12984,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13017,7 +13027,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13031,10 +13041,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46129</v>
+        <v>46203</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13048,11 +13058,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13095,7 +13105,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13109,10 +13119,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44496</v>
+        <v>46168</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13125,7 +13135,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13168,7 +13178,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13182,10 +13192,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45096</v>
+        <v>44701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13198,7 +13208,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13241,7 +13251,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13255,10 +13265,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45110</v>
+        <v>44698</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13271,7 +13281,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13314,7 +13324,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13328,10 +13338,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45110</v>
+        <v>45299</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13344,7 +13354,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13387,7 +13397,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13401,10 +13411,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45140</v>
+        <v>45370</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13417,7 +13427,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13460,7 +13470,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13474,10 +13484,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45314</v>
+        <v>45313</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13490,7 +13500,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13533,7 +13543,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13547,10 +13557,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44995</v>
+        <v>45448</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13562,8 +13572,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13606,7 +13621,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13616,14 +13631,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45370</v>
+        <v>44687</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13636,7 +13651,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13679,7 +13694,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13693,10 +13708,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44743</v>
+        <v>46280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13709,7 +13724,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13752,7 +13767,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13766,10 +13781,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45099</v>
+        <v>45196</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13782,7 +13797,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13825,7 +13840,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13839,10 +13854,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44812</v>
+        <v>44827</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13855,7 +13870,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13898,7 +13913,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13912,10 +13927,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46258</v>
+        <v>45314</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13928,7 +13943,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13971,7 +13986,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13985,10 +14000,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45621</v>
+        <v>45687</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14001,7 +14016,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14044,7 +14059,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14058,10 +14073,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45091</v>
+        <v>44909</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14074,7 +14089,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>21.6</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14117,7 +14132,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14131,10 +14146,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46203</v>
+        <v>45385</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14146,13 +14161,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14195,7 +14205,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14209,10 +14219,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44894</v>
+        <v>44995</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14225,7 +14235,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14268,7 +14278,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14282,10 +14292,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44909</v>
+        <v>44887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14298,7 +14308,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14341,7 +14351,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 38149-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14355,10 +14365,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46168</v>
+        <v>46281</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14371,7 +14381,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14414,7 +14424,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14428,10 +14438,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45288</v>
+        <v>45215</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14444,7 +14454,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14487,7 +14497,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 39263-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14501,10 +14511,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45224</v>
+        <v>46288</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14516,8 +14526,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14560,7 +14575,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 39265-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14574,10 +14589,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45448</v>
+        <v>46288</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14595,7 +14610,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14638,7 +14653,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14652,10 +14667,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45175</v>
+        <v>46281</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14667,13 +14682,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14716,7 +14726,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14730,10 +14740,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45110</v>
+        <v>45281</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14746,7 +14756,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14789,7 +14799,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14803,10 +14813,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45514</v>
+        <v>44812</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14819,7 +14829,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14862,7 +14872,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14876,10 +14886,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45156</v>
+        <v>45140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14892,7 +14902,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14935,7 +14945,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 39888-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14949,10 +14959,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44995</v>
+        <v>46290</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14965,7 +14975,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15008,7 +15018,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15022,10 +15032,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44642</v>
+        <v>44995</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15038,7 +15048,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15081,7 +15091,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15091,14 +15101,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45109</v>
+        <v>46246</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15110,8 +15120,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15154,7 +15169,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15164,14 +15179,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45313</v>
+        <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15184,7 +15199,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15227,7 +15242,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15241,10 +15256,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45288</v>
+        <v>46247</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15256,8 +15271,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15300,7 +15320,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15314,10 +15334,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46280</v>
+        <v>46246</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15329,8 +15349,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15373,7 +15398,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15387,10 +15412,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45639</v>
+        <v>45281</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15403,7 +15428,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15446,7 +15471,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15460,10 +15485,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45635</v>
+        <v>44937</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15476,7 +15501,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15519,7 +15544,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15533,10 +15558,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45595</v>
+        <v>45145</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15549,7 +15574,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15592,7 +15617,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 38146-2026</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15606,10 +15631,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46281</v>
+        <v>45435</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15622,7 +15647,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15665,7 +15690,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38149-2026</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15679,10 +15704,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46281</v>
+        <v>44642</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15695,7 +15720,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15738,7 +15763,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15752,10 +15777,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46247</v>
+        <v>45091</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15767,13 +15792,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>21.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15816,7 +15836,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 39263-2026</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15830,10 +15850,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46288</v>
+        <v>45224</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15845,13 +15865,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15894,7 +15909,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 39265-2026</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15908,10 +15923,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46288</v>
+        <v>45156</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15923,13 +15938,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15972,7 +15982,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15986,10 +15996,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46246</v>
+        <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16001,13 +16011,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16050,7 +16055,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 39335-2026</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16064,10 +16069,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46288</v>
+        <v>45621</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16080,7 +16085,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16123,7 +16128,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16137,10 +16142,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46246</v>
+        <v>45299</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16152,13 +16157,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16201,7 +16201,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16211,14 +16211,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45800</v>
+        <v>45356</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16274,7 +16274,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16284,14 +16284,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44946</v>
+        <v>44887</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16347,7 +16347,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16361,10 +16361,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45817</v>
+        <v>44743</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16420,7 +16420,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16434,10 +16434,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45820</v>
+        <v>45628</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16449,13 +16449,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16498,7 +16493,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16512,10 +16507,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45839</v>
+        <v>44978</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16528,7 +16523,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16571,7 +16566,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16585,10 +16580,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45839</v>
+        <v>45758</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16600,8 +16595,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16644,7 +16644,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16658,10 +16658,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44953</v>
+        <v>45758</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16673,8 +16673,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16717,7 +16722,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16727,14 +16732,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45840</v>
+        <v>45313</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16747,7 +16752,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>11.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16790,7 +16795,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16800,14 +16805,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45258</v>
+        <v>45639</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16820,7 +16825,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16863,7 +16868,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16877,10 +16882,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45776</v>
+        <v>45595</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16893,7 +16898,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16936,7 +16941,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16950,10 +16955,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44687</v>
+        <v>45635</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16965,13 +16970,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>44623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45372</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46135</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>45110</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>46163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45772</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>44560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44799</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44467</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44728</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44589</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45272</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45398</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44856</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>44860</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>44895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45288</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>45824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>45469</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45874</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45889</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45890</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45800</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44587</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>46059</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>46059</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44937</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45924</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45924</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45924</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45408</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>46072</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45929</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44973</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>46087</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45763</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46093</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>46093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>46101</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45945</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46101</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>46106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>46106</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46108</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>46111</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>46111</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>46111</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>46113</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>46119</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45099</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44957</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>45539</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>46129</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45514</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45883</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45699</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44990</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45091</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45800</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45667</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>46008</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45288</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45110</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45043</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45180</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45492</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44908</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45110</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>45149</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45839</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45109</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>44953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45110</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>46163</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>46168</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>46168</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45776</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44687</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46168</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45309</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45492</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>46182</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45022</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45462</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45469</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45469</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>46189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45196</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44844</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>45091</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>46258</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45420</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46203</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>46168</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44698</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45299</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45370</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45313</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45448</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44687</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>46280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45196</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44827</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45314</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45687</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44909</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45385</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44995</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>46281</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45215</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46288</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>46288</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>46281</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45281</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44812</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>46290</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>44995</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>46246</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>46247</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>46246</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45281</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>44937</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45145</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45435</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44642</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45091</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45224</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45156</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45621</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45299</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45356</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>44887</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44743</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45628</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44978</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45758</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45758</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45313</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45639</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45595</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45635</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>44623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45372</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46135</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>45110</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>46163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45772</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>44560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44799</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44467</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44595</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44728</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44589</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45272</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45398</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44856</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>44860</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>44895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45288</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44895</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>45824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>45469</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45874</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45889</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45890</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45800</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44587</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>46059</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>46059</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44937</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45924</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45924</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45924</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45408</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>46072</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45929</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44973</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>46087</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45763</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46093</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>46093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>46101</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45945</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46101</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>46106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>46106</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46108</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>46111</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>46111</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>46111</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>46113</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>46119</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45099</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44957</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>45539</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>46129</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45514</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45883</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45699</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44990</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45091</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45800</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45667</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>46008</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45288</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45110</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45043</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45180</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45492</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44908</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45110</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>45149</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45839</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45109</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>44953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45110</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45840</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>46163</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>46168</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>46168</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45776</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44687</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45258</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46168</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45309</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45492</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>46182</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45022</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45462</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45469</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45469</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>46189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45196</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44844</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>45091</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>46258</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45420</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46203</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>46168</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44698</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45299</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45370</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45313</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45448</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44687</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>46280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45196</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44827</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45314</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45687</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44909</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45385</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44995</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>46281</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45215</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46288</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>46288</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>46281</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45281</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44812</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>46290</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>44995</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>46246</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>46247</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>46246</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45281</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>44937</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45145</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45435</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44642</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45091</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45224</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45156</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45621</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45299</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45356</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>44887</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44743</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45628</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44978</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45758</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45758</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45313</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45639</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45595</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45635</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>44623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45372</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE216"/>
+  <dimension ref="A1:AE215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 9277-2023</t>
+          <t>A 30080-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,14 +1577,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44980</v>
+        <v>45110</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -1621,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1637,573 +1637,573 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 20063-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45772</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Skinntagging</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 55928-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 19729-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9277-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44980</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 55928-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 23455-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="I16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 55928-2025 artfynd.xlsx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 55928-2025 karta.png", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 55928-2025 georefererad karta.tif", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 55928-2025 FSC-klagomål.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 55928-2025 FSC-klagomål mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 55928-2025 tillsynsbegäran.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 55928-2025 tillsynsbegäran mail.docx", "A 55928-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 19729-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 30080-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45110</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 23455-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 23455-2026 artfynd.xlsx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 23455-2026 karta.png", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 23455-2026 georefererad karta.tif", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 23455-2026 FSC-klagomål.docx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 23455-2026 FSC-klagomål mail.docx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 23455-2026 tillsynsbegäran.docx", "A 23455-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 23455-2026 tillsynsbegäran mail.docx", "A 23455-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 20063-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45772</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skinntagging</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 20063-2025 artfynd.xlsx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 20063-2025 karta.png", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 20063-2025 georefererad karta.tif", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 20063-2025 FSC-klagomål.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 20063-2025 FSC-klagomål mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 20063-2025 tillsynsbegäran.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 20063-2025 tillsynsbegäran mail.docx", "A 20063-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>44560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44799</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52971-2021</t>
+          <t>A 5594-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44467</v>
+        <v>44595</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5594-2022</t>
+          <t>A 5600-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3238,7 +3238,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3294,7 +3294,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5600-2022</t>
+          <t>A 15415-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44595</v>
+        <v>44659</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3323,8 +3323,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>8.9</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3367,7 +3372,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15415-2022</t>
+          <t>A 72213-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3381,10 +3386,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44659</v>
+        <v>44544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,13 +3401,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 72213-2021</t>
+          <t>A 24976-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44544</v>
+        <v>44728</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24976-2022</t>
+          <t>A 4409-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44728</v>
+        <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3591,7 +3591,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4409-2022</t>
+          <t>A 38210-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44589</v>
+        <v>44812</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3664,7 +3664,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38210-2022</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44812</v>
+        <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44530</v>
+        <v>45469</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45272</v>
+        <v>45420</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,8 +3912,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3956,7 +3961,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3970,10 +3975,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45335</v>
+        <v>45435</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3986,7 +3991,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4029,7 +4034,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4043,10 +4048,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45398</v>
+        <v>45763</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4058,13 +4063,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4107,7 +4107,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44856</v>
+        <v>45180</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4180,7 +4180,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44860</v>
+        <v>44908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4253,7 +4253,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44895</v>
+        <v>45113</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45288</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 8701-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44496</v>
+        <v>44978</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45469</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44895</v>
+        <v>45554</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45824</v>
+        <v>45110</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4691,7 +4691,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45469</v>
+        <v>45824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4764,7 +4764,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45874</v>
+        <v>45091</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4837,7 +4837,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45890</v>
+        <v>46008</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4868,11 +4868,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45889</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45890</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5159,14 +5159,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45800</v>
+        <v>45890</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5178,8 +5178,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5222,7 +5227,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5232,14 +5237,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45086</v>
+        <v>45800</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5252,7 +5257,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5295,7 +5300,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5309,10 +5314,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44587</v>
+        <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5324,13 +5329,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5373,7 +5373,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46059</v>
+        <v>45699</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5402,8 +5402,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5446,7 +5451,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5460,10 +5465,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46059</v>
+        <v>45462</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5476,7 +5481,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5519,7 +5524,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5533,10 +5538,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45719</v>
+        <v>45398</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5548,8 +5553,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5592,7 +5602,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5602,14 +5612,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45918</v>
+        <v>44946</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5621,13 +5631,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5670,7 +5675,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5684,10 +5689,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44937</v>
+        <v>45817</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5700,7 +5705,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5743,7 +5748,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5757,10 +5762,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45924</v>
+        <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5774,11 +5779,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5821,7 +5826,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5835,10 +5840,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45924</v>
+        <v>45820</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5852,11 +5857,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5899,7 +5904,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5913,10 +5918,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45924</v>
+        <v>44895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5928,13 +5933,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45924</v>
+        <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6006,13 +6006,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6055,7 +6050,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 55247-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6069,10 +6064,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45408</v>
+        <v>44887</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6084,13 +6079,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6133,7 +6123,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6147,10 +6137,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46072</v>
+        <v>45272</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6163,7 +6153,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6206,7 +6196,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6220,10 +6210,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45929</v>
+        <v>45924</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6235,8 +6225,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6279,7 +6274,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6293,10 +6288,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44973</v>
+        <v>45924</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6308,8 +6303,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6362,14 +6362,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46087</v>
+        <v>45687</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45932</v>
+        <v>45924</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6454,8 +6454,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6498,7 +6503,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6512,10 +6517,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45763</v>
+        <v>45924</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6527,8 +6532,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6571,7 +6581,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6585,10 +6595,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46093</v>
+        <v>45111</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6601,7 +6611,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6644,7 +6654,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6658,10 +6668,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46093</v>
+        <v>45929</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6673,13 +6683,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6722,7 +6727,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6736,10 +6741,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45554</v>
+        <v>45932</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6752,7 +6757,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6795,7 +6800,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6809,10 +6814,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46101</v>
+        <v>44973</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6825,7 +6830,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6868,7 +6873,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6882,10 +6887,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44615</v>
+        <v>45839</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6898,7 +6903,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6941,7 +6946,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6955,10 +6960,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45945</v>
+        <v>45839</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6970,13 +6975,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46101</v>
+        <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46100</v>
+        <v>44953</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7121,13 +7121,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7170,7 +7165,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7184,10 +7179,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46106</v>
+        <v>45840</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7197,11 +7192,6 @@
       <c r="G82" t="inlineStr">
         <is>
           <t>SKARA</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7248,7 +7238,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7262,10 +7252,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44894</v>
+        <v>45945</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7277,8 +7267,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7321,7 +7316,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7331,14 +7326,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46106</v>
+        <v>45258</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7350,13 +7345,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7399,7 +7389,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7413,10 +7403,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46106</v>
+        <v>45776</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7428,13 +7418,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7477,7 +7462,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7491,10 +7476,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46108</v>
+        <v>44687</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7506,8 +7491,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7550,7 +7540,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7564,10 +7554,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46111</v>
+        <v>45958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7580,7 +7570,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7623,7 +7613,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7637,10 +7627,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46111</v>
+        <v>45960</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7652,8 +7642,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7696,7 +7691,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7710,10 +7705,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46111</v>
+        <v>45385</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7726,7 +7721,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7769,7 +7764,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7783,10 +7778,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46111</v>
+        <v>45974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7799,7 +7794,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7842,7 +7837,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7856,10 +7851,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45713</v>
+        <v>45874</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7872,7 +7867,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7915,7 +7910,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7929,10 +7924,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46113</v>
+        <v>45492</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7944,13 +7939,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7993,7 +7983,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8007,10 +7997,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45958</v>
+        <v>45667</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8022,8 +8012,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8066,7 +8061,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 515-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8080,10 +8075,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45960</v>
+        <v>45299</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8095,13 +8090,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8144,7 +8134,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8158,10 +8148,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46119</v>
+        <v>45281</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8174,7 +8164,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8217,7 +8207,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8231,10 +8221,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45099</v>
+        <v>44615</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8247,7 +8237,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8290,7 +8280,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8304,10 +8294,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44497</v>
+        <v>46001</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8319,8 +8309,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8363,7 +8358,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44957</v>
+        <v>46059</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8393,7 +8388,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8436,7 +8431,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8450,10 +8445,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45539</v>
+        <v>46059</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8465,13 +8460,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8514,7 +8504,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8528,10 +8518,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45642</v>
+        <v>44970</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8544,7 +8534,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8587,7 +8577,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8601,10 +8591,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45974</v>
+        <v>45719</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8617,7 +8607,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8660,7 +8650,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8674,10 +8664,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45817</v>
+        <v>44856</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8690,7 +8680,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8733,7 +8723,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8747,10 +8737,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44970</v>
+        <v>44860</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8763,7 +8753,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8806,7 +8796,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8820,10 +8810,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46129</v>
+        <v>45091</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8835,13 +8825,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8884,7 +8869,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32668-2024</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8898,10 +8883,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45514</v>
+        <v>45335</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8914,7 +8899,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8957,7 +8942,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8971,10 +8956,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45113</v>
+        <v>46072</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8987,7 +8972,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9030,7 +9015,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9044,10 +9029,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45883</v>
+        <v>45196</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9060,7 +9045,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9103,7 +9088,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9113,14 +9098,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45699</v>
+        <v>46087</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9132,13 +9117,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9181,7 +9161,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9195,10 +9175,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45763</v>
+        <v>45713</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9211,7 +9191,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9254,7 +9234,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9268,10 +9248,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44990</v>
+        <v>44827</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9284,7 +9264,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9327,7 +9307,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9337,14 +9317,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44946</v>
+        <v>45492</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9357,7 +9337,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9400,7 +9380,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9414,10 +9394,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45098</v>
+        <v>46093</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9429,13 +9409,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9478,7 +9453,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9488,14 +9463,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44832</v>
+        <v>46093</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9507,8 +9482,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9551,7 +9531,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9565,10 +9545,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46001</v>
+        <v>45098</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9586,7 +9566,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9629,7 +9609,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9643,10 +9623,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45091</v>
+        <v>44990</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9659,7 +9639,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9702,7 +9682,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 55211-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9716,10 +9696,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45800</v>
+        <v>45621</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9732,7 +9712,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9775,7 +9755,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9789,10 +9769,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45667</v>
+        <v>46100</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9810,7 +9790,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9853,7 +9833,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9867,10 +9847,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46008</v>
+        <v>46101</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9882,13 +9862,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9931,7 +9906,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9945,10 +9920,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45820</v>
+        <v>46101</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9960,13 +9935,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10009,7 +9979,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 65095-2023</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10023,10 +9993,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45288</v>
+        <v>46106</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10038,8 +10008,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10082,7 +10057,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30085-2023</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10096,10 +10071,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45110</v>
+        <v>46106</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10111,8 +10086,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10155,7 +10135,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10169,10 +10149,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45043</v>
+        <v>46106</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10184,8 +10164,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10228,7 +10213,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 56922-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10242,10 +10227,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45180</v>
+        <v>45628</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10258,7 +10243,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10301,7 +10286,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10315,10 +10300,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45492</v>
+        <v>46108</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10331,7 +10316,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10374,7 +10359,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10388,10 +10373,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44908</v>
+        <v>46111</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10404,7 +10389,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10447,7 +10432,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10461,10 +10446,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45110</v>
+        <v>46111</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10477,7 +10462,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10520,7 +10505,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10534,10 +10519,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45149</v>
+        <v>46111</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10550,7 +10535,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10593,7 +10578,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10603,14 +10588,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45149</v>
+        <v>45086</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10623,7 +10608,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10666,7 +10651,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10680,10 +10665,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45839</v>
+        <v>46111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10696,7 +10681,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10739,7 +10724,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10753,10 +10738,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45839</v>
+        <v>46113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10768,8 +10753,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10812,7 +10802,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30019-2023</t>
+          <t>A 17705-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10822,14 +10812,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45109</v>
+        <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10841,8 +10831,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10885,7 +10880,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 17709-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10899,10 +10894,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44953</v>
+        <v>45758</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10914,8 +10909,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10958,7 +10958,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10972,10 +10972,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45110</v>
+        <v>44937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11031,7 +11031,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11045,10 +11045,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45110</v>
+        <v>46119</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11104,7 +11104,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11118,10 +11118,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45840</v>
+        <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45111</v>
+        <v>45539</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11206,8 +11206,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11250,7 +11255,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11264,10 +11269,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46163</v>
+        <v>46129</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11285,7 +11290,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11328,7 +11333,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11342,10 +11347,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46163</v>
+        <v>44587</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11363,7 +11368,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11406,7 +11411,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11420,10 +11425,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46168</v>
+        <v>45299</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11436,7 +11441,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11479,7 +11484,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11493,10 +11498,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46168</v>
+        <v>45196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11509,7 +11514,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11552,7 +11557,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11566,10 +11571,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45776</v>
+        <v>45883</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11582,7 +11587,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11625,7 +11630,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11639,10 +11644,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44687</v>
+        <v>45763</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11654,13 +11659,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11703,7 +11703,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11713,14 +11713,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45258</v>
+        <v>44701</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11776,7 +11776,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11790,10 +11790,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46168</v>
+        <v>44698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11849,7 +11849,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11863,10 +11863,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45309</v>
+        <v>45800</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11922,7 +11922,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45492</v>
+        <v>44497</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11995,7 +11995,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45096</v>
+        <v>45224</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12068,7 +12068,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 41602-2023</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45175</v>
+        <v>45145</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12097,13 +12097,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12146,7 +12141,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12160,10 +12155,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46182</v>
+        <v>45408</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12175,8 +12170,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12219,7 +12219,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 8781-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12233,10 +12233,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45022</v>
+        <v>45356</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12292,7 +12292,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45462</v>
+        <v>45149</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12365,7 +12365,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12375,14 +12375,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45469</v>
+        <v>45149</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12438,7 +12438,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12452,10 +12452,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45469</v>
+        <v>45281</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12511,7 +12511,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12521,14 +12521,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46189</v>
+        <v>44895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12598,10 +12598,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45713</v>
+        <v>44844</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12657,7 +12657,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12667,14 +12667,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45196</v>
+        <v>44832</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12730,7 +12730,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12744,10 +12744,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44844</v>
+        <v>46163</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12759,8 +12759,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12803,7 +12808,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12817,10 +12822,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45091</v>
+        <v>45469</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12833,7 +12838,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12876,7 +12881,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12890,10 +12895,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46258</v>
+        <v>45469</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12906,7 +12911,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12949,7 +12954,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12963,10 +12968,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45420</v>
+        <v>45313</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12978,13 +12983,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13027,7 +13027,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46203</v>
+        <v>46163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13058,11 +13058,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13105,7 +13105,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24144-2026</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13122,7 +13122,7 @@
         <v>46168</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13192,10 +13192,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44701</v>
+        <v>46168</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13251,7 +13251,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13265,10 +13265,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44698</v>
+        <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 18701-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13334,14 +13334,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45299</v>
+        <v>44687</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13397,7 +13397,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45370</v>
+        <v>45043</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13470,7 +13470,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45313</v>
+        <v>45215</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13543,7 +13543,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22870-2024</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45448</v>
+        <v>44957</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13572,13 +13572,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13621,7 +13616,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 18701-2022</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13631,14 +13626,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44687</v>
+        <v>45022</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13651,7 +13646,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13694,7 +13689,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38007-2026</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13708,10 +13703,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46280</v>
+        <v>44496</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13724,7 +13719,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13767,7 +13762,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13781,10 +13776,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45196</v>
+        <v>46182</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13797,7 +13792,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13840,7 +13835,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13854,10 +13849,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44827</v>
+        <v>45096</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13870,7 +13865,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13913,7 +13908,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13927,10 +13922,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45314</v>
+        <v>45110</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13943,7 +13938,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13986,7 +13981,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14000,10 +13995,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45687</v>
+        <v>45110</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14016,7 +14011,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14059,7 +14054,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14069,14 +14064,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44909</v>
+        <v>46189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14089,7 +14084,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14132,7 +14127,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14146,10 +14141,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45385</v>
+        <v>45140</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14162,7 +14157,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14205,7 +14200,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14219,10 +14214,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44995</v>
+        <v>45314</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14235,7 +14230,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>13.5</v>
+        <v>0.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14278,7 +14273,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14292,10 +14287,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44887</v>
+        <v>44995</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14308,7 +14303,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14351,7 +14346,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 38149-2026</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14365,10 +14360,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46281</v>
+        <v>45370</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14424,7 +14419,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 27668-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14438,10 +14433,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45215</v>
+        <v>44743</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14454,7 +14449,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14497,7 +14492,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 39263-2026</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14511,10 +14506,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46288</v>
+        <v>45099</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14526,13 +14521,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14575,7 +14565,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 39265-2026</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14589,10 +14579,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46288</v>
+        <v>44812</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14604,13 +14594,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14653,7 +14638,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38146-2026</t>
+          <t>A 55202-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14667,10 +14652,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46281</v>
+        <v>45621</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14683,7 +14668,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14726,7 +14711,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14740,10 +14725,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45281</v>
+        <v>45091</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14756,7 +14741,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.3</v>
+        <v>21.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14799,7 +14784,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14813,10 +14798,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44812</v>
+        <v>44894</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14829,7 +14814,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14872,7 +14857,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14886,10 +14871,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45140</v>
+        <v>46258</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14945,7 +14930,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 39888-2026</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14959,10 +14944,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46290</v>
+        <v>44909</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15018,7 +15003,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 11900-2023</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15032,10 +15017,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44995</v>
+        <v>46203</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15047,8 +15032,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15091,7 +15081,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 33219-2026</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15105,10 +15095,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46246</v>
+        <v>45288</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15120,13 +15110,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15169,7 +15154,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15186,7 +15171,7 @@
         <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15199,7 +15184,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15242,7 +15227,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 33469-2026</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15256,10 +15241,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46247</v>
+        <v>46168</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15271,13 +15256,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15320,7 +15300,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 33190-2026</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15334,10 +15314,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46246</v>
+        <v>45448</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15351,11 +15331,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15398,7 +15378,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15412,10 +15392,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45281</v>
+        <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15427,8 +15407,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15471,7 +15456,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15485,10 +15470,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44937</v>
+        <v>45110</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15501,7 +15486,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15544,7 +15529,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15558,10 +15543,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45145</v>
+        <v>45514</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15574,7 +15559,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15617,7 +15602,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15631,10 +15616,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45435</v>
+        <v>45156</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15647,7 +15632,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15690,7 +15675,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 12889-2022</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15704,10 +15689,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44642</v>
+        <v>44995</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15720,7 +15705,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15763,7 +15748,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15777,10 +15762,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45091</v>
+        <v>44642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15793,7 +15778,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>21.6</v>
+        <v>1.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15836,7 +15821,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15846,14 +15831,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45224</v>
+        <v>45109</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15866,7 +15851,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15909,7 +15894,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37460-2023</t>
+          <t>A 2590-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15919,14 +15904,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45156</v>
+        <v>45313</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15939,7 +15924,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.6</v>
+        <v>11.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15982,7 +15967,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15996,10 +15981,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45621</v>
+        <v>45288</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16012,7 +15997,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16055,7 +16040,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 38007-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16069,10 +16054,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45621</v>
+        <v>46280</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16085,7 +16070,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16128,7 +16113,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 59841-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16142,10 +16127,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45299</v>
+        <v>45639</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16158,7 +16143,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16201,7 +16186,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 58683-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16215,10 +16200,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45356</v>
+        <v>45635</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16231,7 +16216,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16274,7 +16259,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 49435-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16288,10 +16273,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44887</v>
+        <v>45595</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16304,7 +16289,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16347,7 +16332,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 38146-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16361,10 +16346,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44743</v>
+        <v>46281</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16377,7 +16362,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16420,7 +16405,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 38149-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16434,10 +16419,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45628</v>
+        <v>46281</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16450,7 +16435,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16493,7 +16478,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 39263-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16507,10 +16492,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44978</v>
+        <v>46288</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16522,8 +16507,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16566,7 +16556,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 39265-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16580,10 +16570,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45758</v>
+        <v>46288</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16601,7 +16591,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16644,7 +16634,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 33190-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16658,10 +16648,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45758</v>
+        <v>46246</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16675,11 +16665,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16722,7 +16712,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 2590-2024</t>
+          <t>A 33219-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16732,14 +16722,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45313</v>
+        <v>46246</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16751,8 +16741,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>11.7</v>
+        <v>3.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16795,7 +16790,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 59841-2024</t>
+          <t>A 33469-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16809,10 +16804,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45639</v>
+        <v>46247</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16824,8 +16819,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16868,7 +16868,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 49435-2024</t>
+          <t>A 39888-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16882,10 +16882,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45595</v>
+        <v>46290</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16941,24 +16941,22 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 58683-2024</t>
+          <t>S 1236-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v/>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45635</v>
+        <v>44623</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16971,7 +16969,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>9.199999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17011,10 +17009,10 @@
       </c>
       <c r="V214" s="2" t="inlineStr"/>
     </row>
-    <row r="215" ht="15" customHeight="1">
+    <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>S 1236-2022</t>
+          <t>S 839-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17022,14 +17020,16 @@
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C215" t="n">
-        <v/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44623</v>
+        <v>45372</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.1</v>
+        <v>19.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17081,79 +17081,6 @@
         <v>0</v>
       </c>
       <c r="V215" s="2" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>S 839-2024</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D216" s="1" t="n">
-        <v>45372</v>
-      </c>
-      <c r="E216" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I216" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J216" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" t="n">
-        <v>0</v>
-      </c>
-      <c r="L216" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" t="n">
-        <v>0</v>
-      </c>
-      <c r="N216" t="n">
-        <v>0</v>
-      </c>
-      <c r="O216" t="n">
-        <v>0</v>
-      </c>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" t="n">
-        <v>0</v>
-      </c>
-      <c r="T216" t="n">
-        <v>0</v>
-      </c>
-      <c r="U216" t="n">
-        <v>0</v>
-      </c>
-      <c r="V216" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SKARA.xlsx
+++ b/Översikt SKARA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE215"/>
+  <dimension ref="A1:AE222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45750</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45841</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>44614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>44714</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45043</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45915</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30080-2023</t>
+          <t>A 9277-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,14 +1577,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45110</v>
+        <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1621,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1637,35 +1637,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v>45772</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 19729-2026</t>
+          <t>A 30080-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46135</v>
+        <v>45110</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,20 +1917,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1953,147 +1953,147 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 30080-2023 artfynd.xlsx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 30080-2023 karta.png", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 30080-2023 georefererad karta.tif", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 30080-2023 FSC-klagomål.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 30080-2023 FSC-klagomål mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 30080-2023 tillsynsbegäran.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 30080-2023 tillsynsbegäran mail.docx", "A 30080-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 19729-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKARA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 19729-2026 artfynd.xlsx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 19729-2026 karta.png", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 19729-2026 georefererad karta.tif", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 19729-2026 FSC-klagomål.docx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 19729-2026 FSC-klagomål mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 19729-2026 tillsynsbegäran.docx", "A 19729-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 19729-2026 tillsynsbegäran mail.docx", "A 19729-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9277-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44980</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SKARA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/artfynd/A 9277-2023 artfynd.xlsx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor/A 9277-2023 karta.png", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/kartor_geotiff/A 9277-2023 georefererad karta.tif", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomål/A 9277-2023 FSC-klagomål.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/klagomålsmail/A 9277-2023 FSC-klagomål mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsyn/A 9277-2023 tillsynsbegäran.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1495/tillsynsmail/A 9277-2023 tillsynsbegäran mail.docx", "A 9277-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>44560</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44799</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44536</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44600</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44595</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44595</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44659</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>44544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44728</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44812</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 68932-2021</t>
+          <t>A 40164-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44530</v>
+        <v>44818</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3737,7 +3737,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 40164-2022</t>
+          <t>A 68932-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44818</v>
+        <v>44530</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3810,7 +3810,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26567-2024</t>
+          <t>A 62890-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45469</v>
+        <v>45272</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18017-2024</t>
+          <t>A 5825-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45420</v>
+        <v>45335</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,13 +3912,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3961,7 +3956,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20470-2024</t>
+          <t>A 14844-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3975,10 +3970,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45435</v>
+        <v>45398</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,8 +3985,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18616-2025</t>
+          <t>A 48098-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45763</v>
+        <v>44856</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4107,7 +4107,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42301-2023</t>
+          <t>A 49002-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45180</v>
+        <v>44860</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59842-2022</t>
+          <t>A 57258-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44908</v>
+        <v>44895</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4253,7 +4253,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31128-2023</t>
+          <t>A 65124-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45113</v>
+        <v>45288</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60086-2024</t>
+          <t>A 60654-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8701-2023</t>
+          <t>A 26567-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44978</v>
+        <v>45469</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1567-2023</t>
+          <t>A 57238-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>44895</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40264-2024</t>
+          <t>A 29255-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45554</v>
+        <v>45824</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30083-2023</t>
+          <t>A 37032-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45110</v>
+        <v>45874</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4691,7 +4691,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29255-2025</t>
+          <t>A 39494-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45824</v>
+        <v>45890</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,8 +4720,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4764,7 +4769,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26084-2023</t>
+          <t>A 26575-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4778,10 +4783,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45091</v>
+        <v>45469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4794,7 +4799,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4837,7 +4842,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62779-2025</t>
+          <t>A 39365-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4851,10 +4856,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46008</v>
+        <v>45889</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4868,11 +4873,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4915,7 +4920,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39365-2025</t>
+          <t>A 39367-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4932,7 +4937,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4950,7 +4955,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4993,7 +4998,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39367-2025</t>
+          <t>A 39492-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5007,10 +5012,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5071,7 +5076,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39492-2025</t>
+          <t>A 25219-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5081,14 +5086,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45890</v>
+        <v>45800</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5100,13 +5105,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39494-2025</t>
+          <t>A 25176-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45890</v>
+        <v>45086</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5178,13 +5178,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5227,7 +5222,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25219-2025</t>
+          <t>A 3822-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5237,14 +5232,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45800</v>
+        <v>44587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5256,8 +5251,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2110-2024</t>
+          <t>A 28041-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45309</v>
+        <v>45817</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5373,7 +5373,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6366-2025</t>
+          <t>A 3144-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5383,14 +5383,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45699</v>
+        <v>44946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5402,13 +5402,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5451,7 +5446,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25153-2024</t>
+          <t>A 28738-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5465,10 +5460,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45462</v>
+        <v>45820</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5480,8 +5475,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5524,7 +5524,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14844-2024</t>
+          <t>A 1566-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5538,10 +5538,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45398</v>
+        <v>44937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5553,13 +5553,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5602,7 +5597,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3144-2023</t>
+          <t>A 44819-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5612,14 +5607,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44946</v>
+        <v>45918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5631,8 +5626,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28041-2025</t>
+          <t>A 16510-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45817</v>
+        <v>45408</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5704,8 +5704,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5748,7 +5753,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44819-2025</t>
+          <t>A 46155-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5762,10 +5767,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45918</v>
+        <v>45924</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5779,11 +5784,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5826,7 +5831,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28738-2025</t>
+          <t>A 46203-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5840,10 +5845,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45820</v>
+        <v>45924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5857,11 +5862,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5904,7 +5909,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57258-2022</t>
+          <t>A 46211-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5918,10 +5923,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44895</v>
+        <v>45924</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5933,8 +5938,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5977,7 +5987,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 55246-2022</t>
+          <t>A 46183-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5991,10 +6001,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44887</v>
+        <v>45924</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6006,8 +6016,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6050,7 +6065,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55247-2022</t>
+          <t>A 32844-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6064,10 +6079,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44887</v>
+        <v>45839</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6080,7 +6095,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6123,7 +6138,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62890-2023</t>
+          <t>A 32850-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6137,10 +6152,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45272</v>
+        <v>45839</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6153,7 +6168,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6196,7 +6211,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46155-2025</t>
+          <t>A 4306-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6210,10 +6225,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45924</v>
+        <v>44953</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6225,13 +6240,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6274,7 +6284,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46211-2025</t>
+          <t>A 47010-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6288,10 +6298,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45924</v>
+        <v>45929</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6303,13 +6313,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6352,7 +6357,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4542-2025</t>
+          <t>A 33095-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6366,10 +6371,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45687</v>
+        <v>45840</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6382,7 +6387,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6425,7 +6430,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46183-2025</t>
+          <t>A 7946-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6439,10 +6444,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45924</v>
+        <v>44973</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6454,13 +6459,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6503,7 +6503,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 46203-2025</t>
+          <t>A 48088-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45924</v>
+        <v>45932</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6532,13 +6532,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6581,7 +6576,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30479-2023</t>
+          <t>A 18616-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6595,10 +6590,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45111</v>
+        <v>45763</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6611,7 +6606,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6654,7 +6649,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47010-2025</t>
+          <t>A 20721-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6668,10 +6663,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45929</v>
+        <v>45776</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6684,7 +6679,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6727,7 +6722,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48088-2025</t>
+          <t>A 40264-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6741,10 +6736,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45932</v>
+        <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6757,7 +6752,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6800,7 +6795,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7946-2023</t>
+          <t>A 18704-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6814,10 +6809,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44973</v>
+        <v>44687</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6829,8 +6824,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32844-2025</t>
+          <t>A 60233-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6883,14 +6883,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45839</v>
+        <v>45258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32850-2025</t>
+          <t>A 9006-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45839</v>
+        <v>44615</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26575-2024</t>
+          <t>A 50590-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45469</v>
+        <v>45945</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7048,8 +7048,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7092,7 +7097,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4306-2023</t>
+          <t>A 56849-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7106,10 +7111,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44953</v>
+        <v>44894</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7122,7 +7127,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7165,7 +7170,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33095-2025</t>
+          <t>A 9118-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7179,10 +7184,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45840</v>
+        <v>45713</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7195,7 +7200,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7238,7 +7243,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50590-2025</t>
+          <t>A 53170-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7252,10 +7257,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45945</v>
+        <v>45958</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7267,13 +7272,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7316,7 +7316,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60233-2023</t>
+          <t>A 53527-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45258</v>
+        <v>45960</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7345,8 +7345,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7389,7 +7394,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20721-2025</t>
+          <t>A 28073-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7403,10 +7408,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45776</v>
+        <v>45099</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7419,7 +7424,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7462,7 +7467,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18704-2022</t>
+          <t>A 7522-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7476,10 +7481,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44687</v>
+        <v>46059</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7491,13 +7496,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7540,7 +7540,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53170-2025</t>
+          <t>A 7530-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45958</v>
+        <v>46059</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7613,7 +7613,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 53527-2025</t>
+          <t>A 10176-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45960</v>
+        <v>45719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7642,13 +7642,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7691,7 +7686,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12937-2024</t>
+          <t>A 60840-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7705,10 +7700,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45385</v>
+        <v>44497</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7721,7 +7716,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7764,7 +7759,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56274-2025</t>
+          <t>A 5559-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7778,10 +7773,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45974</v>
+        <v>44957</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7837,7 +7832,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37032-2025</t>
+          <t>A 56274-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7851,10 +7846,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45874</v>
+        <v>45974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7867,7 +7862,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7910,7 +7905,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30515-2024</t>
+          <t>A 60086-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7924,10 +7919,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45492</v>
+        <v>45642</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7940,7 +7935,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7983,7 +7978,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1198-2025</t>
+          <t>A 7233-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7997,10 +7992,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45667</v>
+        <v>44970</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8012,13 +8007,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8061,7 +8051,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 515-2024</t>
+          <t>A 32668-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8075,10 +8065,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45299</v>
+        <v>45514</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8091,7 +8081,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8134,7 +8124,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 64551-2023</t>
+          <t>A 9691-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8148,10 +8138,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45281</v>
+        <v>46072</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8164,7 +8154,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8207,7 +8197,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9006-2022</t>
+          <t>A 31128-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8221,10 +8211,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44615</v>
+        <v>45113</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8237,7 +8227,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8280,7 +8270,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61324-2025</t>
+          <t>A 6366-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8294,10 +8284,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46001</v>
+        <v>45699</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8315,7 +8305,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8358,7 +8348,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7522-2026</t>
+          <t>A 10827-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8372,10 +8362,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46059</v>
+        <v>44990</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8388,7 +8378,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.4</v>
+        <v>0.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8431,7 +8421,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7530-2026</t>
+          <t>A 27980-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8445,10 +8435,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46059</v>
+        <v>45098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8460,8 +8450,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8504,7 +8499,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7233-2023</t>
+          <t>A 42874-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8514,14 +8509,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44970</v>
+        <v>44832</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8534,7 +8529,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8577,7 +8572,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10176-2025</t>
+          <t>A 26091-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8591,10 +8586,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45719</v>
+        <v>45091</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8607,7 +8602,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8650,7 +8645,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48098-2022</t>
+          <t>A 1198-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8664,10 +8659,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44856</v>
+        <v>45667</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8679,8 +8674,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8723,7 +8723,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49002-2022</t>
+          <t>A 61324-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44860</v>
+        <v>46001</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8752,8 +8752,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8796,7 +8801,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26091-2023</t>
+          <t>A 12332-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8806,14 +8811,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45091</v>
+        <v>46087</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8826,7 +8831,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8869,7 +8874,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5825-2024</t>
+          <t>A 13276-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8883,10 +8888,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45335</v>
+        <v>46093</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8899,7 +8904,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8942,7 +8947,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9691-2026</t>
+          <t>A 62779-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8956,10 +8961,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46072</v>
+        <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8971,8 +8976,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9015,7 +9025,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 46185-2023</t>
+          <t>A 13063-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9029,10 +9039,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45196</v>
+        <v>46093</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9044,8 +9054,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9088,7 +9103,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12332-2026</t>
+          <t>A 14597-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9098,14 +9113,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46087</v>
+        <v>46101</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9118,7 +9133,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9161,7 +9176,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9117-2025</t>
+          <t>A 65095-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9175,10 +9190,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45713</v>
+        <v>45288</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9191,7 +9206,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9234,7 +9249,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 41562-2022</t>
+          <t>A 14577-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9248,10 +9263,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44827</v>
+        <v>46101</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9264,7 +9279,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9307,7 +9322,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30513-2024</t>
+          <t>A 14422-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9321,10 +9336,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45492</v>
+        <v>46100</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9336,8 +9351,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9380,7 +9400,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13276-2026</t>
+          <t>A 30085-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9394,10 +9414,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46093</v>
+        <v>45110</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9410,7 +9430,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9453,7 +9473,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13063-2026</t>
+          <t>A 18739-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9467,10 +9487,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46093</v>
+        <v>45043</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9482,13 +9502,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9531,7 +9546,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27980-2023</t>
+          <t>A 15429-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9545,10 +9560,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45098</v>
+        <v>46106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9566,7 +9581,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9609,7 +9624,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10827-2023</t>
+          <t>A 15438-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9623,10 +9638,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44990</v>
+        <v>46106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9638,8 +9653,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9682,7 +9702,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55211-2024</t>
+          <t>A 15425-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9696,10 +9716,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45621</v>
+        <v>46106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9711,8 +9731,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9755,7 +9780,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14422-2026</t>
+          <t>A 16085-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9769,10 +9794,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46100</v>
+        <v>46108</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9784,13 +9809,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9833,7 +9853,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 14597-2026</t>
+          <t>A 16199-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9847,10 +9867,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9863,7 +9883,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9906,7 +9926,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 14577-2026</t>
+          <t>A 16201-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9920,10 +9940,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9936,7 +9956,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9979,7 +9999,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15425-2026</t>
+          <t>A 16187-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9993,10 +10013,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10008,13 +10028,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10057,7 +10072,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 15438-2026</t>
+          <t>A 16198-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10071,10 +10086,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10086,13 +10101,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10135,7 +10145,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15429-2026</t>
+          <t>A 16755-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10149,10 +10159,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10170,7 +10180,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10213,7 +10223,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56922-2024</t>
+          <t>A 42301-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10227,10 +10237,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45628</v>
+        <v>45180</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10243,7 +10253,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10286,7 +10296,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16085-2026</t>
+          <t>A 30515-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10300,10 +10310,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46108</v>
+        <v>45492</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10316,7 +10326,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10359,7 +10369,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 16199-2026</t>
+          <t>A 17288-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10373,10 +10383,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10389,7 +10399,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10432,7 +10442,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 16201-2026</t>
+          <t>A 37036-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10446,10 +10456,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46111</v>
+        <v>45539</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10461,8 +10471,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10505,7 +10520,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16198-2026</t>
+          <t>A 59842-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10519,10 +10534,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46111</v>
+        <v>44908</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10535,7 +10550,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10578,7 +10593,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25176-2023</t>
+          <t>A 18890-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10592,10 +10607,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45086</v>
+        <v>46129</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10607,8 +10622,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10651,7 +10671,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16187-2026</t>
+          <t>A 30083-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10665,10 +10685,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46111</v>
+        <v>45110</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10681,7 +10701,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10724,7 +10744,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16755-2026</t>
+          <t>A 36041-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10738,10 +10758,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46113</v>
+        <v>45149</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10753,13 +10773,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10802,7 +10817,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17705-2025</t>
+          <t>A 36045-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10812,14 +10827,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45758</v>
+        <v>45149</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10831,13 +10846,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10880,7 +10890,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17709-2025</t>
+          <t>A 30019-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10890,14 +10900,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45758</v>
+        <v>45109</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10909,13 +10919,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10958,7 +10963,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1566-2023</t>
+          <t>A 30069-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10972,10 +10977,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44937</v>
+        <v>45110</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10988,7 +10993,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11031,7 +11036,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17288-2026</t>
+          <t>A 30079-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11045,10 +11050,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46119</v>
+        <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11061,7 +11066,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11104,7 +11109,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 9118-2025</t>
+          <t>A 30479-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11118,10 +11123,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45713</v>
+        <v>45111</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11134,7 +11139,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11177,7 +11182,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37036-2024</t>
+          <t>A 38548-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11191,10 +11196,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45539</v>
+        <v>45883</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11206,13 +11211,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11255,7 +11255,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18890-2026</t>
+          <t>A 18606-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11269,10 +11269,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46129</v>
+        <v>45763</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11284,13 +11284,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11333,7 +11328,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3822-2022</t>
+          <t>A 25407-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11347,10 +11342,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44587</v>
+        <v>45800</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11362,13 +11357,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11411,7 +11401,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 516-2024</t>
+          <t>A 2110-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11425,10 +11415,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45299</v>
+        <v>45309</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11441,7 +11431,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11484,7 +11474,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 46190-2023</t>
+          <t>A 30513-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11498,10 +11488,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45196</v>
+        <v>45492</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11514,7 +11504,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11557,7 +11547,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 38548-2025</t>
+          <t>A 27265-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11571,10 +11561,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45883</v>
+        <v>45096</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11587,7 +11577,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11630,7 +11620,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18606-2025</t>
+          <t>A 41602-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11644,10 +11634,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45763</v>
+        <v>45175</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11659,8 +11649,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11703,7 +11698,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 20870-2022</t>
+          <t>A 15927-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11717,10 +11712,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44701</v>
+        <v>45022</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11733,7 +11728,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11776,7 +11771,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 20098-2022</t>
+          <t>A 25153-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11790,10 +11785,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44698</v>
+        <v>45462</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11806,7 +11801,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11849,7 +11844,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 25407-2025</t>
+          <t>A 26480-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11863,10 +11858,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45800</v>
+        <v>45469</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11879,7 +11874,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11922,7 +11917,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60840-2021</t>
+          <t>A 26482-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11936,10 +11931,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44497</v>
+        <v>45469</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11952,7 +11947,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11995,7 +11990,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52383-2023</t>
+          <t>A 9117-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12009,10 +12004,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45224</v>
+        <v>45713</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12025,7 +12020,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12068,7 +12063,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35217-2023</t>
+          <t>A 46185-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12082,10 +12077,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45145</v>
+        <v>45196</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12098,7 +12093,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12141,7 +12136,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16510-2024</t>
+          <t>A 45159-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12155,10 +12150,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45408</v>
+        <v>44844</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12170,13 +12165,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12219,7 +12209,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8781-2024</t>
+          <t>A 26084-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12233,10 +12223,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45356</v>
+        <v>45091</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12249,7 +12239,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12292,7 +12282,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36041-2023</t>
+          <t>A 23457-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12306,10 +12296,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45149</v>
+        <v>46163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12321,8 +12311,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12365,7 +12360,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 36045-2023</t>
+          <t>A 18017-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12375,14 +12370,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45149</v>
+        <v>45420</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12394,8 +12389,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12438,7 +12438,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 64553-2023</t>
+          <t>A 23452-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12452,10 +12452,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45281</v>
+        <v>46163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12467,8 +12467,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12511,7 +12516,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 57238-2022</t>
+          <t>A 24142-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12525,10 +12530,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44895</v>
+        <v>46168</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12541,7 +12546,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12584,7 +12589,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 45159-2022</t>
+          <t>A 24143-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12598,10 +12603,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44844</v>
+        <v>46168</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12614,7 +12619,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12657,7 +12662,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 42874-2022</t>
+          <t>A 24145-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12667,14 +12672,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44832</v>
+        <v>46168</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12687,7 +12692,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12730,7 +12735,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23457-2026</t>
+          <t>A 20870-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12744,10 +12749,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46163</v>
+        <v>44701</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12759,13 +12764,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12808,7 +12808,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26480-2024</t>
+          <t>A 20098-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12822,10 +12822,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45469</v>
+        <v>44698</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12881,7 +12881,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26482-2024</t>
+          <t>A 516-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12895,10 +12895,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45469</v>
+        <v>45299</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12954,7 +12954,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 2472-2024</t>
+          <t>A 10913-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45313</v>
+        <v>45370</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13027,7 +13027,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 23452-2026</t>
+          <t>A 2472-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46163</v>
+        <v>45313</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13056,13 +13056,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13105,7 +13100,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24145-2026</t>
+          <t>A 26333-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13119,10 +13114,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13135,7 +13130,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13178,7 +13173,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24142-2026</t>
+          <t>A 27478-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13188,14 +13183,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13208,7 +13203,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13251,7 +13246,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24143-2026</t>
+          <t>A 22870-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13265,10 +13260,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46168</v>
+        <v>45448</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13280,8 +13275,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
         <v>44687</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 18739-2023</t>
+          <t>A 46190-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45043</v>
+        <v>45196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13470,7 +13470,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 50043-2023</t>
+          <t>A 41562-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45215</v>
+        <v>44827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13543,7 +13543,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5559-2023</t>
+          <t>A 2701-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44957</v>
+        <v>45314</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13616,7 +13616,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15927-2023</t>
+          <t>A 4542-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13630,10 +13630,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45022</v>
+        <v>45687</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13689,7 +13689,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 60654-2021</t>
+          <t>A 59996-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13703,10 +13703,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44496</v>
+        <v>44909</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 26333-2026</t>
+          <t>A 12937-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13776,10 +13776,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46182</v>
+        <v>45385</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13835,7 +13835,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 27265-2023</t>
+          <t>A 11902-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45096</v>
+        <v>44995</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13908,7 +13908,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30069-2023</t>
+          <t>A 55246-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45110</v>
+        <v>44887</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30079-2023</t>
+          <t>A 50043-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45110</v>
+        <v>45215</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14054,7 +14054,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27478-2026</t>
+          <t>A 64551-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14064,14 +14064,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46189</v>
+        <v>45281</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34569-2023</t>
+          <t>A 38205-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45140</v>
+        <v>44812</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14200,7 +14200,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 2701-2024</t>
+          <t>A 34569-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14214,10 +14214,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45314</v>
+        <v>45140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14273,7 +14273,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 11902-2023</t>
+          <t>A 11900-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14290,7 +14290,7 @@
         <v>44995</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>13.5</v>
+        <v>2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10913-2024</t>
+          <t>A 52383-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14360,10 +14360,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45370</v>
+        <v>45224</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 27668-2022</t>
+          <t>A 34752-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14433,10 +14433,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44743</v>
+        <v>46258</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28073-2023</t>
+          <t>A 64553-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14506,10 +14506,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45099</v>
+        <v>45281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 38205-2022</t>
+          <t>A 1567-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14579,10 +14579,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44812</v>
+        <v>44937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14638,7 +14638,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 55202-2024</t>
+          <t>A 29478-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14652,10 +14652,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45621</v>
+        <v>46203</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14667,8 +14667,13 @@
           <t>SKARA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14711,7 +14716,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26268-2023</t>
+          <t>A 24144-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14725,10 +14730,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45091</v>
+        <v>46168</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14741,7 +14746,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14784,7 +14789,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 56849-2022</t>
+          <t>A 35217-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14798,10 +14803,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44894</v>
+        <v>45145</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14814,7 +14819,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14857,7 +14862,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34752-2026</t>
+          <t>A 20470-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14871,10 +14876,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46258</v>
+        <v>45435</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14887,7 +14892,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14930,7 +14935,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 59996-2022</t>
+          <t>A 12889-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14944,10 +14949,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44909</v>
+        <v>44642</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14960,7 +14965,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15003,7 +15008,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 29478-2026</t>
+          <t>A 26268-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15017,10 +15022,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46203</v>
+        <v>45091</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15032,13 +15037,8 @@
           <t>SKARA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>2.9</v>
+        <v>21.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 65124-2023</t>
+          <t>A 52381-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45288</v>
+        <v>45224</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 52381-2023</t>
+          <t>A 37460-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15168,10 +15168,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45224</v>
+        <v>45156</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15227,7 +15227,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A